--- a/data/personalia/I SU.xlsx
+++ b/data/personalia/I SU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BB1F7A2-FFF0-4AEF-93BA-E2C17DBA1017}"/>
+  <xr:revisionPtr revIDLastSave="191" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4283878A-FAB5-40ED-9A4D-E8E126EEDD46}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Template Personalia" sheetId="1" r:id="rId1"/>
     <sheet name="LIST_DATA" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Template Personalia'!$A$1:$T$96</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -26,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="339">
   <si>
     <t>Wilayah</t>
   </si>
@@ -142,51 +145,6 @@
     <t>NIPP</t>
   </si>
   <si>
-    <t>II PD</t>
-  </si>
-  <si>
-    <t>IDRUS</t>
-  </si>
-  <si>
-    <t>MUHAMMAD SUBARI</t>
-  </si>
-  <si>
-    <t>EDO SAPUTRA</t>
-  </si>
-  <si>
-    <t>KHAHARDI ERNOF (STL)</t>
-  </si>
-  <si>
-    <t>HANDY ARIEF YANTO (STL)</t>
-  </si>
-  <si>
-    <t>ARNOF ZAHAR (STL)</t>
-  </si>
-  <si>
-    <t>ROZI SAPUTRA</t>
-  </si>
-  <si>
-    <t>RAFES ANTONI</t>
-  </si>
-  <si>
-    <t>ALMAN MARZUKI (STL)</t>
-  </si>
-  <si>
-    <t>RIZKI KURNIADI (STL)</t>
-  </si>
-  <si>
-    <t>FAJAR RACHMAT HARIANDO (STL)</t>
-  </si>
-  <si>
-    <t>RENGGA PUTRA GUCI</t>
-  </si>
-  <si>
-    <t>ROLI SAPUTRA (STL)</t>
-  </si>
-  <si>
-    <t>RAHMAN DONGAN HARAHAP</t>
-  </si>
-  <si>
     <t>Quality Controller</t>
   </si>
   <si>
@@ -199,76 +157,895 @@
     <t>Petugas Negative Check</t>
   </si>
   <si>
-    <t>PLT QC STL Prasarana</t>
-  </si>
-  <si>
-    <t>AM Fasilitas Jalan Rel, Jembatan dan Sintelis</t>
-  </si>
-  <si>
-    <t>Kepala UPT Resor STL Kelas C Pd</t>
-  </si>
-  <si>
-    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C Pd</t>
-  </si>
-  <si>
-    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C Pd</t>
-  </si>
-  <si>
-    <t>PNC Perbaikan UPT Resor STL Pd</t>
-  </si>
-  <si>
-    <t>PNC Preventif UPT Resor STL Pd</t>
-  </si>
-  <si>
-    <t>Pd</t>
-  </si>
-  <si>
-    <t>PMP.170873.125654</t>
-  </si>
-  <si>
-    <t>PRP.010789.45604</t>
-  </si>
-  <si>
-    <t>PRP.05031994.33019</t>
-  </si>
-  <si>
-    <t>PRP.300690.40876</t>
-  </si>
-  <si>
-    <t>PRP.090787.02294</t>
-  </si>
-  <si>
-    <t>PRP.161189.41063</t>
-  </si>
-  <si>
-    <t>PRP.170796.122707</t>
-  </si>
-  <si>
-    <t>PRP.160697.122708</t>
-  </si>
-  <si>
-    <t>PRP.150393.40884</t>
-  </si>
-  <si>
-    <t>PRP.141196.41062</t>
-  </si>
-  <si>
-    <t>PRP.230794.40882</t>
-  </si>
-  <si>
-    <t>PRP.260995.122706</t>
-  </si>
-  <si>
-    <t>PRP.300791.40676</t>
-  </si>
-  <si>
-    <t>PRP.080299.122705</t>
-  </si>
-  <si>
-    <t>PMP.010789.65223</t>
-  </si>
-  <si>
-    <t>PMP.050394.75603</t>
+    <t>I SU</t>
+  </si>
+  <si>
+    <t>GAGUK ANGGORO SISWANTO</t>
+  </si>
+  <si>
+    <t>M. USRIZA</t>
+  </si>
+  <si>
+    <t>ASRIZAL</t>
+  </si>
+  <si>
+    <t>DIDIK NURYANTO</t>
+  </si>
+  <si>
+    <t>ARI WANDANA</t>
+  </si>
+  <si>
+    <t>SETIO AJI SUNARTO</t>
+  </si>
+  <si>
+    <t>DEVI IINDRIANTO</t>
+  </si>
+  <si>
+    <t>DODDY L TOBING</t>
+  </si>
+  <si>
+    <t>MUKHSIN JAYAPUTRA</t>
+  </si>
+  <si>
+    <t>TIMBER T SITANGGANG</t>
+  </si>
+  <si>
+    <t>DICKY RAMADHAN</t>
+  </si>
+  <si>
+    <t>SARIS PRASETYO</t>
+  </si>
+  <si>
+    <t>REZA ALFARABY</t>
+  </si>
+  <si>
+    <t>RACHMAD HIDAYAT</t>
+  </si>
+  <si>
+    <t>DAVID P. TAMPUBOLON</t>
+  </si>
+  <si>
+    <t>ANDREA MAULANA TANOTO</t>
+  </si>
+  <si>
+    <t>RINALDI ANGGISTA</t>
+  </si>
+  <si>
+    <t>RAHMAN AFFANDI</t>
+  </si>
+  <si>
+    <t>CHRIS ANDAR SINAMBELA</t>
+  </si>
+  <si>
+    <t>HERU ASWANDI</t>
+  </si>
+  <si>
+    <t>TRIFAN</t>
+  </si>
+  <si>
+    <t>NURHADI</t>
+  </si>
+  <si>
+    <t>BAGINDA SH SILITONGA</t>
+  </si>
+  <si>
+    <t>ABIL QOSIM AL QUSYAIRI</t>
+  </si>
+  <si>
+    <t>AZFIANDA</t>
+  </si>
+  <si>
+    <t>MARWAN</t>
+  </si>
+  <si>
+    <t>EBIT DANIEL TAMBA</t>
+  </si>
+  <si>
+    <t>ANDIKA PUTRA</t>
+  </si>
+  <si>
+    <t>HAN HIZBULLAH SIREGAR</t>
+  </si>
+  <si>
+    <t>TRI ARDIANSA</t>
+  </si>
+  <si>
+    <t>AZMI ZUHAIRI</t>
+  </si>
+  <si>
+    <t>MUHAMMAD FAHMI SUDRIZA</t>
+  </si>
+  <si>
+    <t>RICKY ARIWIRANATA</t>
+  </si>
+  <si>
+    <t>ILHAM DANAL</t>
+  </si>
+  <si>
+    <t>ANDI KASDIANTO</t>
+  </si>
+  <si>
+    <t>ROBET SIANTURI</t>
+  </si>
+  <si>
+    <t>AHMAD MAULANA</t>
+  </si>
+  <si>
+    <t>ROFF RIBBI RATOMO WIJAYA</t>
+  </si>
+  <si>
+    <t>NIZAL MUHAMMAD</t>
+  </si>
+  <si>
+    <t>MUHAMMAD ZAFRY GULO</t>
+  </si>
+  <si>
+    <t>ABDUL FATTAH</t>
+  </si>
+  <si>
+    <t>IVAN ANDREANI</t>
+  </si>
+  <si>
+    <t>MARA FIRDAUS ANGGARA</t>
+  </si>
+  <si>
+    <t>YUDI KURNIAWAN</t>
+  </si>
+  <si>
+    <t>YOSAFAT MENDROFA</t>
+  </si>
+  <si>
+    <t>INDRA MUSANDI</t>
+  </si>
+  <si>
+    <t>JUBEL LUBIS</t>
+  </si>
+  <si>
+    <t>JONI PUTU WIJAYA</t>
+  </si>
+  <si>
+    <t>YONGKI SYAF PUTRA</t>
+  </si>
+  <si>
+    <t>TEGUH WASONO</t>
+  </si>
+  <si>
+    <t>HARIS NOVAN SYAHPUTRA</t>
+  </si>
+  <si>
+    <t>JEFRI ANTO</t>
+  </si>
+  <si>
+    <t>MUHAMMAD FAJRI</t>
+  </si>
+  <si>
+    <t>JAFER BETA SAPUTRA</t>
+  </si>
+  <si>
+    <t>ROYDI HAFIST</t>
+  </si>
+  <si>
+    <t>SYARIFUDEN</t>
+  </si>
+  <si>
+    <t>DEDI SAHPUTRA</t>
+  </si>
+  <si>
+    <t>FAHRIZAL FAUZI</t>
+  </si>
+  <si>
+    <t>YOKI MARTA</t>
+  </si>
+  <si>
+    <t>AJI PUTRA PERDANA</t>
+  </si>
+  <si>
+    <t>BENNI PERMANA</t>
+  </si>
+  <si>
+    <t>RISKY ENDAR SUBAGJA</t>
+  </si>
+  <si>
+    <t>HARDIANSYAH</t>
+  </si>
+  <si>
+    <t>HERI EFFENDI</t>
+  </si>
+  <si>
+    <t>MARTIN JULIUS GINTING</t>
+  </si>
+  <si>
+    <t>MUHAMMAD YUSUF</t>
+  </si>
+  <si>
+    <t>BUDI DARMAWAN</t>
+  </si>
+  <si>
+    <t>RANDI FEBRIANTO</t>
+  </si>
+  <si>
+    <t>YOKY ERLANG HERMAYANTO</t>
+  </si>
+  <si>
+    <t>ARDI YULIUS</t>
+  </si>
+  <si>
+    <t>BERI PRIMA PANJAITAN</t>
+  </si>
+  <si>
+    <t>EKO SUJIANTORO</t>
+  </si>
+  <si>
+    <t>IBRAHIM HUTAPEA</t>
+  </si>
+  <si>
+    <t>SARIFUDDIN</t>
+  </si>
+  <si>
+    <t>MUHAMMAD IQBAL</t>
+  </si>
+  <si>
+    <t>ALFI SYAHRIN</t>
+  </si>
+  <si>
+    <t>PANDU ZIKRULLAH</t>
+  </si>
+  <si>
+    <t>ADRIAN SUGANDHA PANJAITAN</t>
+  </si>
+  <si>
+    <t>DENI SAPUTRA</t>
+  </si>
+  <si>
+    <t>FACHRI JUNANDA NASUTION</t>
+  </si>
+  <si>
+    <t>REZKY AHMED YUHANDI</t>
+  </si>
+  <si>
+    <t>RUDI MAWARDI</t>
+  </si>
+  <si>
+    <t>ISNAN FERY OKTAVIANSYAH</t>
+  </si>
+  <si>
+    <t>DEDI SANJAYA</t>
+  </si>
+  <si>
+    <t>MUHAMMAD ILHAM ANGGARA</t>
+  </si>
+  <si>
+    <t>MIRZA NAUFAL</t>
+  </si>
+  <si>
+    <t>M YOGGI SAPUTRA</t>
+  </si>
+  <si>
+    <t>ZULIASFIKAL LUBIS</t>
+  </si>
+  <si>
+    <t>ERWIN SAPUTRA</t>
+  </si>
+  <si>
+    <t>IRFANDI</t>
+  </si>
+  <si>
+    <t>JAKA MULYANDA</t>
+  </si>
+  <si>
+    <t>JAYENDRA EKA PUTERA</t>
+  </si>
+  <si>
+    <t>MUHAMMAD ADY PRATAMA</t>
+  </si>
+  <si>
+    <t>ARIF SARMANDA HUSSEIN</t>
+  </si>
+  <si>
+    <t>ABDUL KADIR NASRUL</t>
+  </si>
+  <si>
+    <t>Kepala UPT Workshop</t>
+  </si>
+  <si>
+    <t>Kaur UPT Workshop</t>
+  </si>
+  <si>
+    <t>Teknisi</t>
+  </si>
+  <si>
+    <t>Manager STL Divre I SU</t>
+  </si>
+  <si>
+    <t>QC STL IA Mdn</t>
+  </si>
+  <si>
+    <t>QC STL IB Tbi</t>
+  </si>
+  <si>
+    <t>29 Agu 1973</t>
+  </si>
+  <si>
+    <t>QC STL IC Kis</t>
+  </si>
+  <si>
+    <t>AM Informasi dan Evaluasi Divre I SU</t>
+  </si>
+  <si>
+    <t>AM Kegiatan dan Pembiyaan Divre I SU</t>
+  </si>
+  <si>
+    <t>6 Okt 1989</t>
+  </si>
+  <si>
+    <t>AM Perencanaan Teknis Divre I SU</t>
+  </si>
+  <si>
+    <t>Kegiatan dan Pembiyaan Divre I SU</t>
+  </si>
+  <si>
+    <t>Kepala UPT Workshop STL Mdn</t>
+  </si>
+  <si>
+    <t>WS Mdn</t>
+  </si>
+  <si>
+    <t>Supervisor Perbaikan UPT Workshop Perbaikan</t>
+  </si>
+  <si>
+    <t>Supervisor Rekayasa Perawatan UPT Workshop Rekayasa Perawatan</t>
+  </si>
+  <si>
+    <t>Teknisi Subunit Perbaikan UPT Workshop Sintelis Medan</t>
+  </si>
+  <si>
+    <t>8 Okt 1993</t>
+  </si>
+  <si>
+    <t>12 Mei 1995</t>
+  </si>
+  <si>
+    <t>Kepala UPT Resor Kelas C I.1 Sbt</t>
+  </si>
+  <si>
+    <t>I.1 Sbt</t>
+  </si>
+  <si>
+    <t>15 Mei 1987</t>
+  </si>
+  <si>
+    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C I.1 Sbt</t>
+  </si>
+  <si>
+    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C I.1 Sbt</t>
+  </si>
+  <si>
+    <t>20 Okt 1989</t>
+  </si>
+  <si>
+    <t>PNC Preventif UPT Resor STL I.1 Sbt</t>
+  </si>
+  <si>
+    <t>19 Agu 1994</t>
+  </si>
+  <si>
+    <t>UPT Resor Sintelis Kelas C I.2 Blw</t>
+  </si>
+  <si>
+    <t>I.2 Blw</t>
+  </si>
+  <si>
+    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C I.2 Blw</t>
+  </si>
+  <si>
+    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C I.2 Blw</t>
+  </si>
+  <si>
+    <t>PNC Perbaikan UPT Resor STL I.2 Blw</t>
+  </si>
+  <si>
+    <t>21 Okt 1992</t>
+  </si>
+  <si>
+    <t>11 Mei 1993</t>
+  </si>
+  <si>
+    <t>PNC Preventif UPT Resor STL I.2 Blw</t>
+  </si>
+  <si>
+    <t>28 Agu 1997</t>
+  </si>
+  <si>
+    <t>PLT Kepala UPT Resor Sintelis Kelas B I.3 Mdn</t>
+  </si>
+  <si>
+    <t>I.3 Mdn</t>
+  </si>
+  <si>
+    <t>5 Okt 1989</t>
+  </si>
+  <si>
+    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas B I.3 Mdn</t>
+  </si>
+  <si>
+    <t>1 Agu 1982</t>
+  </si>
+  <si>
+    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas B I.3 Mdn</t>
+  </si>
+  <si>
+    <t>30 Agu 1994</t>
+  </si>
+  <si>
+    <t>PNC Perbaikan UPT Resor STL I.3 Mdn</t>
+  </si>
+  <si>
+    <t>24 Agu 1994</t>
+  </si>
+  <si>
+    <t>PNC Preventif UPT Resor STL I.3 Mdn</t>
+  </si>
+  <si>
+    <t>23 Okt 1993</t>
+  </si>
+  <si>
+    <t>16 Agu 2003</t>
+  </si>
+  <si>
+    <t>PLT Kepala UPT Resor Kelas B I.4 Lbp</t>
+  </si>
+  <si>
+    <t>I.5 Tbi</t>
+  </si>
+  <si>
+    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas B I.4 Lbp</t>
+  </si>
+  <si>
+    <t>I.4 Lbp</t>
+  </si>
+  <si>
+    <t>18 Okt 1990</t>
+  </si>
+  <si>
+    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas B I.4 Lbp</t>
+  </si>
+  <si>
+    <t>PNC Perbaikan UPT Resor STL I.4 Lbp</t>
+  </si>
+  <si>
+    <t>PNC Preventif UPT Resor STL I.4 Lbp</t>
+  </si>
+  <si>
+    <t>15 Mei 1994</t>
+  </si>
+  <si>
+    <t>Kepala UPT Resor Kelas C I.5 Tbi</t>
+  </si>
+  <si>
+    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C I.5 Tbi</t>
+  </si>
+  <si>
+    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C I.5 Tbi</t>
+  </si>
+  <si>
+    <t>PNC Perbaikan UPT Resor STL I.5 Tbi</t>
+  </si>
+  <si>
+    <t>12 Des 1990</t>
+  </si>
+  <si>
+    <t>4 Okt 1993</t>
+  </si>
+  <si>
+    <t>PNC Preventif UPT Resor STL I.5 Tbi</t>
+  </si>
+  <si>
+    <t>5 Okt 1996</t>
+  </si>
+  <si>
+    <t>14 Des 1994</t>
+  </si>
+  <si>
+    <t>Kepala UPT Resor Kelas C I.6 Bdt</t>
+  </si>
+  <si>
+    <t>I.6 Bdt</t>
+  </si>
+  <si>
+    <t>19 Des 1985</t>
+  </si>
+  <si>
+    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C I.6 Bdt</t>
+  </si>
+  <si>
+    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C I.6 Bdt</t>
+  </si>
+  <si>
+    <t>PNC Perbaikan UPT Resor STL I.6 Bdt</t>
+  </si>
+  <si>
+    <t>PNC Preventif UPT Resor STL I.6 Bdt</t>
+  </si>
+  <si>
+    <t>6 Agu 1994</t>
+  </si>
+  <si>
+    <t>16 Mei 1995</t>
+  </si>
+  <si>
+    <t>Kepala UPT Resor I.7 Kelas C Pra</t>
+  </si>
+  <si>
+    <t>I.7 Pra</t>
+  </si>
+  <si>
+    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C I.7 Pra</t>
+  </si>
+  <si>
+    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C I.7 Pra</t>
+  </si>
+  <si>
+    <t>PNC Perbaikan UPT Resor STL I.7 Pra</t>
+  </si>
+  <si>
+    <t>PNC Preventif UPT Resor STL I.7 Pra</t>
+  </si>
+  <si>
+    <t>1 Agu 1995</t>
+  </si>
+  <si>
+    <t>3 Okt 1996</t>
+  </si>
+  <si>
+    <t>Kepala UPT Resor Kelas C I.8 Kis</t>
+  </si>
+  <si>
+    <t>I.8 Kis</t>
+  </si>
+  <si>
+    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C I.8 Kis</t>
+  </si>
+  <si>
+    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C I.8 Kis</t>
+  </si>
+  <si>
+    <t>PNC Perbaikan UPT Resor STL I.8 Kis</t>
+  </si>
+  <si>
+    <t>8 Des 1992</t>
+  </si>
+  <si>
+    <t>PNC Preventif UPT Resor STL I.8 Kis</t>
+  </si>
+  <si>
+    <t>Kepala UPT Resor Kelas C I.9 Pur</t>
+  </si>
+  <si>
+    <t>I.9 Pur</t>
+  </si>
+  <si>
+    <t>4 Des 1988</t>
+  </si>
+  <si>
+    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C I.9 Pur</t>
+  </si>
+  <si>
+    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C I.9 Pur</t>
+  </si>
+  <si>
+    <t>2 Okt 1988</t>
+  </si>
+  <si>
+    <t>PNC Perbaikan UPT Resor STL I.9 Pur</t>
+  </si>
+  <si>
+    <t>PNC Preventif UPT Resor STL I.9 Pur</t>
+  </si>
+  <si>
+    <t>4 Okt 1996</t>
+  </si>
+  <si>
+    <t>Kepala UPT Resor Kelas C I.10 Rap</t>
+  </si>
+  <si>
+    <t>I.10 Rap</t>
+  </si>
+  <si>
+    <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C I.10 Rap</t>
+  </si>
+  <si>
+    <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C I.10 Rap</t>
+  </si>
+  <si>
+    <t>PNC Perbaikan UPT Resor I.10 Rap</t>
+  </si>
+  <si>
+    <t>PNC Preventif UPT Resor STL I.10 Rap</t>
+  </si>
+  <si>
+    <t>16 Mei 1994</t>
+  </si>
+  <si>
+    <t>PMP.161176.01041</t>
+  </si>
+  <si>
+    <t>PMP. 140874. 00988</t>
+  </si>
+  <si>
+    <t>PMP. 291273. 00981</t>
+  </si>
+  <si>
+    <t>PMP.260477.60525</t>
+  </si>
+  <si>
+    <t>PRP.060586.126623</t>
+  </si>
+  <si>
+    <t>PRP.200993.44142</t>
+  </si>
+  <si>
+    <t>PRP. 020470. 126722</t>
+  </si>
+  <si>
+    <t>PRP.040391.126898</t>
+  </si>
+  <si>
+    <t>PRP.130295.41157</t>
+  </si>
+  <si>
+    <t>PRP.081093.44137</t>
+  </si>
+  <si>
+    <t>PRP.120595.50421</t>
+  </si>
+  <si>
+    <t>PRP.150587.126430</t>
+  </si>
+  <si>
+    <t>PRP.160291.126897</t>
+  </si>
+  <si>
+    <t>PRP.201089.02184</t>
+  </si>
+  <si>
+    <t>PRP.190894.117644</t>
+  </si>
+  <si>
+    <t>PRP.111289.126641</t>
+  </si>
+  <si>
+    <t>PRP.240787.00334</t>
+  </si>
+  <si>
+    <t>PRP.140292.126628</t>
+  </si>
+  <si>
+    <t>PRP.290694.44139</t>
+  </si>
+  <si>
+    <t>PRP.211092.42698</t>
+  </si>
+  <si>
+    <t>PRP.051193.122827</t>
+  </si>
+  <si>
+    <t>PRP.280897.122824</t>
+  </si>
+  <si>
+    <t>PRP.080182.126721</t>
+  </si>
+  <si>
+    <t>PRP.200894.02219</t>
+  </si>
+  <si>
+    <t>PRP.020393.02199</t>
+  </si>
+  <si>
+    <t>PRP.230793.02180</t>
+  </si>
+  <si>
+    <t>PRP.240894.122836</t>
+  </si>
+  <si>
+    <t>PRP.240192.02181</t>
+  </si>
+  <si>
+    <t>PRP.231093.42697</t>
+  </si>
+  <si>
+    <t>PRP.030397.127309</t>
+  </si>
+  <si>
+    <t>PRP.160802.73666</t>
+  </si>
+  <si>
+    <t>PRP.150386.126701</t>
+  </si>
+  <si>
+    <t>PRP.181090.02221</t>
+  </si>
+  <si>
+    <t>PRP.011188.126429</t>
+  </si>
+  <si>
+    <t>PRP.041296.45689</t>
+  </si>
+  <si>
+    <t>PRP.230293.44141</t>
+  </si>
+  <si>
+    <t>PRP.090697.42695</t>
+  </si>
+  <si>
+    <t>PRP.110896.123025</t>
+  </si>
+  <si>
+    <t>PRP.070589.02178</t>
+  </si>
+  <si>
+    <t>PRP.150594.122894</t>
+  </si>
+  <si>
+    <t>PRP.240385.126639</t>
+  </si>
+  <si>
+    <t>PRP.180992.44138</t>
+  </si>
+  <si>
+    <t>PRP.121290.02220</t>
+  </si>
+  <si>
+    <t>PRP.021193.02203</t>
+  </si>
+  <si>
+    <t>PRP.070893.44144</t>
+  </si>
+  <si>
+    <t>PRP.100596.45002</t>
+  </si>
+  <si>
+    <t>PRP.141294.40747</t>
+  </si>
+  <si>
+    <t>PRP.250396.127310</t>
+  </si>
+  <si>
+    <t>PRP.191285.126643</t>
+  </si>
+  <si>
+    <t>PRP.140689.127124</t>
+  </si>
+  <si>
+    <t>PRP.300391.02200</t>
+  </si>
+  <si>
+    <t>PRP.280795.117647</t>
+  </si>
+  <si>
+    <t>PRP.080694.43435</t>
+  </si>
+  <si>
+    <t>PRP.160595.122990</t>
+  </si>
+  <si>
+    <t>PRP.280689.02206</t>
+  </si>
+  <si>
+    <t>PRP.200188.127308</t>
+  </si>
+  <si>
+    <t>PRP.160397.117650</t>
+  </si>
+  <si>
+    <t>PRP.111093.122829</t>
+  </si>
+  <si>
+    <t>PRP.290296.122834</t>
+  </si>
+  <si>
+    <t>PRP.280394.122837</t>
+  </si>
+  <si>
+    <t>PRP.080195.42696</t>
+  </si>
+  <si>
+    <t>PRP.100396.02207</t>
+  </si>
+  <si>
+    <t>PRP.041089.126702</t>
+  </si>
+  <si>
+    <t>PRP.140487.126703</t>
+  </si>
+  <si>
+    <t>PRP.230385.126642</t>
+  </si>
+  <si>
+    <t>PRP.180992.44143</t>
+  </si>
+  <si>
+    <t>PRP.120892.02179</t>
+  </si>
+  <si>
+    <t>PRP.091094.123094</t>
+  </si>
+  <si>
+    <t>PRP.260197.45988</t>
+  </si>
+  <si>
+    <t>PRP.230297.122830</t>
+  </si>
+  <si>
+    <t>PRP.041288.126720</t>
+  </si>
+  <si>
+    <t>PRP.100288.126431</t>
+  </si>
+  <si>
+    <t>PRP.020397.117649</t>
+  </si>
+  <si>
+    <t>PRP.010997.46710</t>
+  </si>
+  <si>
+    <t>PRP.041096.41158</t>
+  </si>
+  <si>
+    <t>PRP.170396.117643</t>
+  </si>
+  <si>
+    <t>PRP.060499.122832</t>
+  </si>
+  <si>
+    <t>PRP.031286.126704</t>
+  </si>
+  <si>
+    <t>PRP.090494.44140</t>
+  </si>
+  <si>
+    <t>PRP.040989.02208</t>
+  </si>
+  <si>
+    <t>PRP.070994.02204</t>
+  </si>
+  <si>
+    <t>PRP.260998.127125</t>
+  </si>
+  <si>
+    <t>PRP.160696.122833</t>
+  </si>
+  <si>
+    <t>PRP.190292.02183</t>
+  </si>
+  <si>
+    <t>PRP.160594.122823</t>
+  </si>
+  <si>
+    <t>PMP.140874.00988</t>
+  </si>
+  <si>
+    <t>PMP.291273.00981</t>
+  </si>
+  <si>
+    <t>PMP.060586.712.19</t>
+  </si>
+  <si>
+    <t>PMP.020470.71217</t>
+  </si>
+  <si>
+    <t>PMP.150587.67258</t>
+  </si>
+  <si>
+    <t>PMP.111289.68999</t>
+  </si>
+  <si>
+    <t>PMP.150386.71215</t>
+  </si>
+  <si>
+    <t>PMP.041089.67594</t>
+  </si>
+  <si>
+    <t>PMP.041288.67256</t>
   </si>
 </sst>
 </file>
@@ -327,7 +1104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -351,6 +1128,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -655,7 +1435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T73"/>
+  <dimension ref="A1:T96"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.86328125" style="2" customWidth="1"/>
@@ -665,7 +1445,7 @@
     <col min="5" max="5" width="20.59765625" style="2" customWidth="1"/>
     <col min="6" max="6" width="32" style="4" customWidth="1"/>
     <col min="7" max="7" width="8.46484375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.1328125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13.1328125" style="6" customWidth="1"/>
     <col min="9" max="9" width="7.06640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="10.73046875" style="2" customWidth="1"/>
     <col min="11" max="13" width="13.1328125" style="6" customWidth="1"/>
@@ -700,7 +1480,7 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="7" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -742,31 +1522,31 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C2" s="2">
-        <v>43550</v>
+        <v>43432</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>57</v>
+        <v>141</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H2" s="6">
-        <v>45550</v>
+        <v>46054</v>
       </c>
       <c r="I2" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>26</v>
@@ -775,524 +1555,536 @@
         <v>35217</v>
       </c>
       <c r="L2" s="6">
-        <v>26893</v>
+        <v>28080</v>
       </c>
       <c r="M2" s="6">
-        <v>47362</v>
+        <v>48549</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="O2" s="6">
+        <v>46246</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>65</v>
+        <v>245</v>
       </c>
       <c r="R2" s="6">
-        <v>46851</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
+        <v>46246</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="2">
+        <v>42640</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="2">
-        <v>64523</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="F3" s="4" t="s">
-        <v>58</v>
+        <v>142</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H3" s="6">
-        <v>45992</v>
+        <v>45945</v>
       </c>
       <c r="I3" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K3" s="6">
-        <v>41791</v>
+        <v>34669</v>
       </c>
       <c r="L3" s="6">
-        <v>32690</v>
+        <v>27347</v>
       </c>
       <c r="M3" s="6">
-        <v>53175</v>
+        <v>47818</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>66</v>
+        <v>246</v>
       </c>
       <c r="O3" s="6">
-        <v>46574</v>
+        <v>45696</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>79</v>
+        <v>330</v>
       </c>
       <c r="R3" s="6">
-        <v>47008</v>
+        <v>47370</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="2">
+        <v>42633</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="2">
-        <v>70533</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="F4" s="4" t="s">
-        <v>59</v>
+        <v>143</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="H4" s="6">
-        <v>45371</v>
+        <v>45792</v>
       </c>
       <c r="I4" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K4" s="6">
-        <v>42646</v>
-      </c>
-      <c r="L4" s="6">
-        <v>34457</v>
+        <v>34669</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>144</v>
       </c>
       <c r="M4" s="6">
-        <v>54940</v>
+        <v>47362</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>67</v>
+        <v>247</v>
       </c>
       <c r="O4" s="6">
-        <v>46011</v>
+        <v>45696</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>80</v>
+        <v>331</v>
       </c>
       <c r="R4" s="6">
-        <v>47370</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
+        <v>47265</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="2">
+        <v>46483</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="2">
-        <v>68959</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="F5" s="4" t="s">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="H5" s="6">
-        <v>44927</v>
+        <v>45945</v>
       </c>
       <c r="I5" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K5" s="6">
-        <v>42681</v>
+        <v>35433</v>
       </c>
       <c r="L5" s="6">
-        <v>33054</v>
+        <v>28241</v>
       </c>
       <c r="M5" s="6">
-        <v>53509</v>
+        <v>48700</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>68</v>
+        <v>248</v>
       </c>
       <c r="O5" s="6">
-        <v>46433</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
+        <v>46950</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="R5" s="6">
+        <v>46950</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C6" s="2">
-        <v>57107</v>
+        <v>51093</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>61</v>
+        <v>146</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="H6" s="6">
-        <v>44927</v>
+        <v>45627</v>
       </c>
       <c r="I6" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K6" s="6">
-        <v>40190</v>
+        <v>39093</v>
       </c>
       <c r="L6" s="6">
-        <v>32027</v>
+        <v>31568</v>
       </c>
       <c r="M6" s="6">
-        <v>52505</v>
+        <v>52048</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>69</v>
+        <v>249</v>
       </c>
       <c r="O6" s="6">
-        <v>46433</v>
+        <v>47407</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="R6" s="6">
+        <v>47265</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C7" s="2">
-        <v>68965</v>
+        <v>64499</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>62</v>
+        <v>147</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="H7" s="6">
-        <v>44927</v>
+        <v>45809</v>
       </c>
       <c r="I7" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K7" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L7" s="6">
-        <v>32828</v>
+        <v>41791</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>148</v>
       </c>
       <c r="M7" s="6">
-        <v>53297</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="O7" s="6">
-        <v>46448</v>
+        <v>53267</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C8" s="2">
-        <v>72289</v>
+        <v>56700</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>62</v>
+        <v>149</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="H8" s="6">
-        <v>44927</v>
+        <v>45915</v>
       </c>
       <c r="I8" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K8" s="6">
-        <v>43286</v>
+        <v>40163</v>
       </c>
       <c r="L8" s="6">
-        <v>35263</v>
+        <v>31831</v>
       </c>
       <c r="M8" s="6">
-        <v>55732</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="O8" s="6">
-        <v>46851</v>
+        <v>52291</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C9" s="2">
-        <v>72279</v>
+        <v>70434</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>62</v>
+        <v>150</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="H9" s="6">
-        <v>44927</v>
+        <v>45231</v>
       </c>
       <c r="I9" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K9" s="6">
-        <v>43286</v>
+        <v>42675</v>
       </c>
       <c r="L9" s="6">
-        <v>35597</v>
+        <v>34232</v>
       </c>
       <c r="M9" s="6">
-        <v>56066</v>
+        <v>54697</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>72</v>
+        <v>250</v>
       </c>
       <c r="O9" s="6">
-        <v>46861</v>
+        <v>46494</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C10" s="2">
-        <v>68962</v>
+        <v>42616</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>63</v>
+        <v>151</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>64</v>
+        <v>152</v>
       </c>
       <c r="H10" s="6">
-        <v>44927</v>
+        <v>45809</v>
       </c>
       <c r="I10" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K10" s="6">
-        <v>42681</v>
+        <v>34346</v>
       </c>
       <c r="L10" s="6">
-        <v>34043</v>
+        <v>25660</v>
       </c>
       <c r="M10" s="6">
-        <v>54514</v>
+        <v>46143</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>73</v>
+        <v>251</v>
       </c>
       <c r="O10" s="6">
-        <v>46433</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.45">
+        <v>47285</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="R10" s="6">
+        <v>47265</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C11" s="2">
-        <v>68970</v>
+        <v>59951</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>56</v>
+        <v>139</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>63</v>
+        <v>153</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>64</v>
+        <v>152</v>
       </c>
       <c r="H11" s="6">
-        <v>44927</v>
+        <v>45823</v>
       </c>
       <c r="I11" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K11" s="6">
-        <v>42681</v>
+        <v>40545</v>
       </c>
       <c r="L11" s="6">
-        <v>35383</v>
+        <v>33331</v>
       </c>
       <c r="M11" s="6">
-        <v>55854</v>
+        <v>53813</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>74</v>
+        <v>252</v>
       </c>
       <c r="O11" s="6">
-        <v>46448</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.45">
+        <v>47261</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C12" s="2">
-        <v>68966</v>
+        <v>71547</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>56</v>
+        <v>139</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>63</v>
+        <v>154</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>64</v>
+        <v>152</v>
       </c>
       <c r="H12" s="6">
-        <v>44927</v>
+        <v>45672</v>
       </c>
       <c r="I12" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>26</v>
       </c>
       <c r="K12" s="6">
-        <v>42681</v>
+        <v>42898</v>
       </c>
       <c r="L12" s="6">
-        <v>34538</v>
+        <v>34743</v>
       </c>
       <c r="M12" s="6">
-        <v>55001</v>
+        <v>55213</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>75</v>
+        <v>253</v>
       </c>
       <c r="O12" s="6">
-        <v>46433</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.45">
+        <v>47370</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C13" s="2">
-        <v>72284</v>
+        <v>70930</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>56</v>
+        <v>140</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>63</v>
+        <v>155</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>64</v>
+        <v>152</v>
       </c>
       <c r="H13" s="6">
-        <v>44927</v>
+        <v>45823</v>
       </c>
       <c r="I13" s="2">
         <v>5</v>
@@ -1301,45 +2093,45 @@
         <v>26</v>
       </c>
       <c r="K13" s="6">
-        <v>43286</v>
-      </c>
-      <c r="L13" s="6">
-        <v>34968</v>
+        <v>42725</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>156</v>
       </c>
       <c r="M13" s="6">
-        <v>55427</v>
+        <v>54728</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>76</v>
+        <v>254</v>
       </c>
       <c r="O13" s="6">
-        <v>46851</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.45">
+        <v>46494</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C14" s="2">
-        <v>68963</v>
+        <v>73948</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>56</v>
+        <v>140</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>63</v>
+        <v>155</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>64</v>
+        <v>152</v>
       </c>
       <c r="H14" s="6">
-        <v>44927</v>
+        <v>45611</v>
       </c>
       <c r="I14" s="2">
         <v>5</v>
@@ -1348,302 +2140,3860 @@
         <v>26</v>
       </c>
       <c r="K14" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L14" s="6">
-        <v>33449</v>
+        <v>44197</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>157</v>
       </c>
       <c r="M14" s="6">
-        <v>53905</v>
+        <v>55305</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>77</v>
+        <v>255</v>
       </c>
       <c r="O14" s="6">
-        <v>46433</v>
+        <v>46727</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C15" s="2">
-        <v>72282</v>
+        <v>54027</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H15" s="6">
+        <v>45672</v>
+      </c>
+      <c r="I15" s="2">
+        <v>8</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15" s="6">
+        <v>39814</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="M15" s="6">
+        <v>52383</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="O15" s="6">
+        <v>46951</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="R15" s="6">
+        <v>47097</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="2">
+        <v>59950</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H16" s="6">
+        <v>45823</v>
+      </c>
+      <c r="I16" s="2">
+        <v>7</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K16" s="6">
+        <v>40545</v>
+      </c>
+      <c r="L16" s="6">
+        <v>33285</v>
+      </c>
+      <c r="M16" s="6">
+        <v>53752</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="O16" s="6">
+        <v>47265</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="2">
+        <v>69524</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H17" s="6">
+        <v>45823</v>
+      </c>
+      <c r="I17" s="2">
+        <v>7</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K17" s="6">
+        <v>42681</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="M17" s="6">
+        <v>53267</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="O17" s="6">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="2">
+        <v>71581</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F15" s="4" t="s">
+      <c r="E18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H18" s="6">
+        <v>44927</v>
+      </c>
+      <c r="I18" s="2">
+        <v>5</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" s="6">
+        <v>43075</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="M18" s="6">
+        <v>55032</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="O18" s="6">
+        <v>46663</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="2">
+        <v>56762</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="H19" s="6">
+        <v>45992</v>
+      </c>
+      <c r="I19" s="2">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19" s="6">
+        <v>40163</v>
+      </c>
+      <c r="L19" s="6">
+        <v>32824</v>
+      </c>
+      <c r="M19" s="6">
+        <v>53297</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="O19" s="6">
+        <v>47285</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="R19" s="6">
+        <v>47175</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="2">
+        <v>59962</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="H20" s="6">
+        <v>45823</v>
+      </c>
+      <c r="I20" s="2">
+        <v>7</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K20" s="6">
+        <v>40545</v>
+      </c>
+      <c r="L20" s="6">
+        <v>31982</v>
+      </c>
+      <c r="M20" s="6">
+        <v>52444</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="O20" s="6">
+        <v>46973</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="2">
+        <v>59963</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="H21" s="6">
+        <v>45672</v>
+      </c>
+      <c r="I21" s="2">
+        <v>7</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K21" s="6">
+        <v>40545</v>
+      </c>
+      <c r="L21" s="6">
+        <v>33648</v>
+      </c>
+      <c r="M21" s="6">
+        <v>54118</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="O21" s="6">
+        <v>47203</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="C22" s="2">
+        <v>71594</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="H22" s="6">
+        <v>45323</v>
+      </c>
+      <c r="I22" s="2">
+        <v>5</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K22" s="6">
+        <v>42898</v>
+      </c>
+      <c r="L22" s="6">
+        <v>34514</v>
+      </c>
+      <c r="M22" s="6">
+        <v>54970</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="O22" s="6">
+        <v>46494</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H15" s="6">
+      <c r="C23" s="2">
+        <v>70928</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="H23" s="6">
+        <v>45323</v>
+      </c>
+      <c r="I23" s="2">
+        <v>5</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K23" s="6">
+        <v>42725</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="M23" s="6">
+        <v>54363</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="O23" s="6">
+        <v>46494</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A24" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="2">
+        <v>73289</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="H24" s="6">
+        <v>45323</v>
+      </c>
+      <c r="I24" s="2">
+        <v>5</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K24" s="6">
+        <v>43419</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="M24" s="6">
+        <v>54575</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="O24" s="6">
+        <v>46937</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="2">
+        <v>73217</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="H25" s="6">
+        <v>45058</v>
+      </c>
+      <c r="I25" s="2">
+        <v>5</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K25" s="6">
+        <v>43419</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="M25" s="6">
+        <v>56128</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="O25" s="6">
+        <v>46851</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="2">
+        <v>51142</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H26" s="6">
+        <v>45962</v>
+      </c>
+      <c r="I26" s="2">
+        <v>9</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K26" s="6">
+        <v>39093</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="M26" s="6">
+        <v>53267</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="2">
+        <v>59952</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H27" s="6">
+        <v>45823</v>
+      </c>
+      <c r="I27" s="2">
+        <v>8</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K27" s="6">
+        <v>40545</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="M27" s="6">
+        <v>50649</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="O27" s="6">
+        <v>47203</v>
+      </c>
+      <c r="P27" s="8"/>
+    </row>
+    <row r="28" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="2">
+        <v>68900</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H28" s="6">
+        <v>45672</v>
+      </c>
+      <c r="I28" s="2">
+        <v>8</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K28" s="6">
+        <v>42681</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="M28" s="6">
+        <v>55032</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="O28" s="6">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="2">
+        <v>70013</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H29" s="6">
         <v>44927</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I29" s="2">
         <v>5</v>
       </c>
-      <c r="J15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K15" s="6">
-        <v>43286</v>
-      </c>
-      <c r="L15" s="6">
-        <v>36374</v>
-      </c>
-      <c r="M15" s="6">
-        <v>56858</v>
-      </c>
-      <c r="N15" s="2" t="s">
+      <c r="J29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K29" s="6">
+        <v>42597</v>
+      </c>
+      <c r="L29" s="6">
+        <v>34003</v>
+      </c>
+      <c r="M29" s="6">
+        <v>54483</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="O29" s="6">
+        <v>46208</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="2">
+        <v>68896</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H30" s="6">
+        <v>45058</v>
+      </c>
+      <c r="I30" s="2">
+        <v>5</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K30" s="6">
+        <v>43046</v>
+      </c>
+      <c r="L30" s="6">
+        <v>34173</v>
+      </c>
+      <c r="M30" s="6">
+        <v>54758</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="O30" s="6">
+        <v>46208</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="2">
+        <v>73566</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H31" s="6">
+        <v>45323</v>
+      </c>
+      <c r="I31" s="2">
+        <v>5</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K31" s="6">
+        <v>43419</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="M31" s="6">
+        <v>55032</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="O31" s="6">
+        <v>46916</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A32" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="2">
+        <v>70012</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H32" s="6">
+        <v>45323</v>
+      </c>
+      <c r="I32" s="2">
+        <v>5</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K32" s="6">
+        <v>42597</v>
+      </c>
+      <c r="L32" s="6">
+        <v>33627</v>
+      </c>
+      <c r="M32" s="6">
+        <v>54089</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="O32" s="6">
+        <v>46208</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A33" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" s="2">
+        <v>70934</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H33" s="6">
+        <v>45058</v>
+      </c>
+      <c r="I33" s="2">
+        <v>5</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K33" s="6">
+        <v>42725</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="M33" s="6">
+        <v>54728</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="O33" s="6">
+        <v>46494</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A34" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="2">
+        <v>73516</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H34" s="6">
+        <v>45058</v>
+      </c>
+      <c r="I34" s="2">
+        <v>5</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K34" s="6">
+        <v>43419</v>
+      </c>
+      <c r="L34" s="6">
+        <v>35492</v>
+      </c>
+      <c r="M34" s="6">
+        <v>55975</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="O34" s="6">
+        <v>47370</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A35" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" s="2">
+        <v>76925</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H35" s="6">
+        <v>45689</v>
+      </c>
+      <c r="I35" s="2">
+        <v>5</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K35" s="6">
+        <v>45289</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="M35" s="6">
+        <v>58319</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="O35" s="6">
+        <v>47324</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A36" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" s="2">
+        <v>54022</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H36" s="6">
+        <v>45809</v>
+      </c>
+      <c r="I36" s="2">
+        <v>9</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K36" s="6">
+        <v>39814</v>
+      </c>
+      <c r="L36" s="6">
+        <v>31486</v>
+      </c>
+      <c r="M36" s="6">
+        <v>51957</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="O36" s="6">
+        <v>47261</v>
+      </c>
+      <c r="Q36" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="R36" s="6">
+        <v>47265</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A37" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="O15" s="6">
-        <v>46861</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="D16" s="2"/>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D17" s="2"/>
-      <c r="H17" s="6"/>
-    </row>
-    <row r="18" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D18" s="2"/>
-      <c r="H18" s="6"/>
-    </row>
-    <row r="19" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D19" s="2"/>
-      <c r="H19" s="6"/>
-    </row>
-    <row r="20" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D20" s="2"/>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D21" s="2"/>
-      <c r="H21" s="6"/>
-    </row>
-    <row r="22" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D22" s="2"/>
-      <c r="H22" s="6"/>
-    </row>
-    <row r="23" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D23" s="2"/>
-      <c r="H23" s="6"/>
-    </row>
-    <row r="24" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D24" s="2"/>
-      <c r="H24" s="6"/>
-    </row>
-    <row r="25" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D25" s="2"/>
-      <c r="H25" s="6"/>
-    </row>
-    <row r="26" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D26" s="2"/>
-      <c r="H26" s="6"/>
-    </row>
-    <row r="27" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D27" s="2"/>
-      <c r="H27" s="6"/>
-    </row>
-    <row r="28" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D28" s="2"/>
-      <c r="H28" s="6"/>
-      <c r="P28" s="8"/>
-    </row>
-    <row r="29" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D29" s="2"/>
-      <c r="H29" s="6"/>
-    </row>
-    <row r="30" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D30" s="2"/>
-      <c r="H30" s="6"/>
-    </row>
-    <row r="31" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D31" s="2"/>
-      <c r="H31" s="6"/>
-    </row>
-    <row r="32" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D32" s="2"/>
-      <c r="H32" s="6"/>
-    </row>
-    <row r="33" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D33" s="2"/>
-      <c r="H33" s="6"/>
-    </row>
-    <row r="34" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D34" s="2"/>
-      <c r="H34" s="6"/>
-    </row>
-    <row r="35" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D35" s="2"/>
-      <c r="H35" s="6"/>
-    </row>
-    <row r="36" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D36" s="2"/>
-      <c r="H36" s="6"/>
-    </row>
-    <row r="37" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D37" s="2"/>
-      <c r="H37" s="6"/>
-    </row>
-    <row r="38" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D38" s="2"/>
-      <c r="H38" s="6"/>
-    </row>
-    <row r="39" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D39" s="2"/>
-      <c r="H39" s="6"/>
-    </row>
-    <row r="40" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D40" s="2"/>
-      <c r="H40" s="6"/>
-    </row>
-    <row r="41" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D41" s="2"/>
-      <c r="H41" s="6"/>
-    </row>
-    <row r="42" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D42" s="2"/>
-      <c r="H42" s="6"/>
-    </row>
-    <row r="43" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D43" s="2"/>
-      <c r="H43" s="6"/>
-    </row>
-    <row r="44" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D44" s="2"/>
-      <c r="H44" s="6"/>
-    </row>
-    <row r="45" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D45" s="2"/>
-      <c r="H45" s="6"/>
-    </row>
-    <row r="46" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D46" s="2"/>
-      <c r="H46" s="6"/>
-    </row>
-    <row r="47" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D47" s="2"/>
-      <c r="H47" s="6"/>
-    </row>
-    <row r="48" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D48" s="2"/>
-      <c r="H48" s="6"/>
-    </row>
-    <row r="49" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D49" s="2"/>
-      <c r="H49" s="6"/>
-    </row>
-    <row r="50" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D50" s="2"/>
-      <c r="H50" s="6"/>
-    </row>
-    <row r="51" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D51" s="2"/>
-      <c r="H51" s="6"/>
-    </row>
-    <row r="52" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D52" s="2"/>
-      <c r="H52" s="6"/>
-    </row>
-    <row r="53" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D53" s="2"/>
-      <c r="H53" s="6"/>
-    </row>
-    <row r="54" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D54" s="2"/>
-      <c r="H54" s="6"/>
-    </row>
-    <row r="55" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D55" s="2"/>
-      <c r="H55" s="6"/>
-    </row>
-    <row r="56" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D56" s="2"/>
-      <c r="H56" s="6"/>
-    </row>
-    <row r="57" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D57" s="2"/>
-      <c r="H57" s="6"/>
-    </row>
-    <row r="58" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D58" s="2"/>
-      <c r="H58" s="6"/>
-    </row>
-    <row r="59" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D59" s="2"/>
-      <c r="H59" s="6"/>
-    </row>
-    <row r="60" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D60" s="2"/>
-      <c r="H60" s="6"/>
-    </row>
-    <row r="61" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D61" s="2"/>
-      <c r="H61" s="6"/>
-    </row>
-    <row r="62" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D62" s="2"/>
-      <c r="H62" s="6"/>
-    </row>
-    <row r="63" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D63" s="2"/>
-      <c r="H63" s="6"/>
-    </row>
-    <row r="64" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D64" s="2"/>
-      <c r="H64" s="6"/>
-    </row>
-    <row r="65" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D65" s="2"/>
-      <c r="H65" s="6"/>
-    </row>
-    <row r="66" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D66" s="2"/>
-      <c r="H66" s="6"/>
-    </row>
-    <row r="67" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D67" s="2"/>
-      <c r="H67" s="6"/>
-    </row>
-    <row r="68" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D68" s="2"/>
-      <c r="H68" s="6"/>
-    </row>
-    <row r="69" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D69" s="2"/>
-      <c r="H69" s="6"/>
-    </row>
-    <row r="70" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D70" s="2"/>
-      <c r="H70" s="6"/>
-    </row>
-    <row r="71" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D71" s="2"/>
-      <c r="H71" s="6"/>
-    </row>
-    <row r="72" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D72" s="2"/>
-      <c r="H72" s="6"/>
-    </row>
-    <row r="73" spans="4:8" x14ac:dyDescent="0.45">
-      <c r="D73" s="2"/>
-      <c r="H73" s="6"/>
+      <c r="C37" s="2">
+        <v>67508</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H37" s="6">
+        <v>45823</v>
+      </c>
+      <c r="I37" s="2">
+        <v>8</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K37" s="6">
+        <v>42372</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="M37" s="6">
+        <v>53632</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="O37" s="6">
+        <v>46744</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A38" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" s="2">
+        <v>59965</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H38" s="6">
+        <v>45992</v>
+      </c>
+      <c r="I38" s="2">
+        <v>8</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K38" s="6">
+        <v>40545</v>
+      </c>
+      <c r="L38" s="6">
+        <v>32153</v>
+      </c>
+      <c r="M38" s="6">
+        <v>52628</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="O38" s="6">
+        <v>46937</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A39" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C39" s="2">
+        <v>71586</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H39" s="6">
+        <v>45323</v>
+      </c>
+      <c r="I39" s="2">
+        <v>5</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K39" s="6">
+        <v>42898</v>
+      </c>
+      <c r="L39" s="6">
+        <v>34336</v>
+      </c>
+      <c r="M39" s="6">
+        <v>54820</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A40" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" s="2">
+        <v>71574</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H40" s="6">
+        <v>44927</v>
+      </c>
+      <c r="I40" s="2">
+        <v>5</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K40" s="6">
+        <v>42898</v>
+      </c>
+      <c r="L40" s="6">
+        <v>35167</v>
+      </c>
+      <c r="M40" s="6">
+        <v>55640</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="O40" s="6">
+        <v>46574</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A41" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C41" s="2">
+        <v>70929</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H41" s="6">
+        <v>45323</v>
+      </c>
+      <c r="I41" s="2">
+        <v>5</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K41" s="6">
+        <v>42725</v>
+      </c>
+      <c r="L41" s="6">
+        <v>34023</v>
+      </c>
+      <c r="M41" s="6">
+        <v>54483</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="O41" s="6">
+        <v>46494</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A42" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" s="2">
+        <v>70432</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H42" s="6">
+        <v>44927</v>
+      </c>
+      <c r="I42" s="2">
+        <v>5</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K42" s="6">
+        <v>42380</v>
+      </c>
+      <c r="L42" s="6">
+        <v>35590</v>
+      </c>
+      <c r="M42" s="6">
+        <v>56066</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="O42" s="6">
+        <v>46494</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A43" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" s="2">
+        <v>73390</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H43" s="6">
+        <v>44927</v>
+      </c>
+      <c r="I43" s="2">
+        <v>5</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K43" s="6">
+        <v>43419</v>
+      </c>
+      <c r="L43" s="6">
+        <v>35377</v>
+      </c>
+      <c r="M43" s="6">
+        <v>55854</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="O43" s="6">
+        <v>46937</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A44" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C44" s="2">
+        <v>70014</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H44" s="6">
+        <v>45823</v>
+      </c>
+      <c r="I44" s="2">
+        <v>5</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K44" s="6">
+        <v>42597</v>
+      </c>
+      <c r="L44" s="6">
+        <v>32694</v>
+      </c>
+      <c r="M44" s="6">
+        <v>53175</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="O44" s="6">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A45" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" s="2">
+        <v>73586</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H45" s="6">
+        <v>45058</v>
+      </c>
+      <c r="I45" s="2">
+        <v>5</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K45" s="6">
+        <v>43419</v>
+      </c>
+      <c r="L45" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="M45" s="6">
+        <v>54940</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="O45" s="6">
+        <v>46973</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A46" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C46" s="2">
+        <v>57108</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H46" s="6">
+        <v>45823</v>
+      </c>
+      <c r="I46" s="2">
+        <v>8</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K46" s="6">
+        <v>40190</v>
+      </c>
+      <c r="L46" s="6">
+        <v>32173</v>
+      </c>
+      <c r="M46" s="6">
+        <v>52628</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A47" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" s="2">
+        <v>59949</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H47" s="6">
+        <v>45058</v>
+      </c>
+      <c r="I47" s="2">
+        <v>7</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K47" s="6">
+        <v>40545</v>
+      </c>
+      <c r="L47" s="6">
+        <v>31130</v>
+      </c>
+      <c r="M47" s="6">
+        <v>51592</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="O47" s="6">
+        <v>47285</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A48" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C48" s="2">
+        <v>62095</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H48" s="6">
+        <v>45992</v>
+      </c>
+      <c r="I48" s="2">
+        <v>7</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K48" s="6">
+        <v>40917</v>
+      </c>
+      <c r="L48" s="6">
+        <v>31877</v>
+      </c>
+      <c r="M48" s="6">
+        <v>52352</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A49" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C49" s="2">
+        <v>70427</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H49" s="6">
+        <v>45323</v>
+      </c>
+      <c r="I49" s="2">
+        <v>5</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K49" s="6">
+        <v>42380</v>
+      </c>
+      <c r="L49" s="6">
+        <v>33865</v>
+      </c>
+      <c r="M49" s="6">
+        <v>54332</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="O49" s="6">
+        <v>46494</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A50" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C50" s="2">
+        <v>70016</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H50" s="6">
+        <v>45323</v>
+      </c>
+      <c r="I50" s="2">
+        <v>5</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K50" s="6">
+        <v>42597</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="M50" s="6">
+        <v>53693</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="O50" s="6">
+        <v>46433</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A51" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C51" s="2">
+        <v>71592</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H51" s="6">
+        <v>45323</v>
+      </c>
+      <c r="I51" s="2">
+        <v>5</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K51" s="6">
+        <v>42898</v>
+      </c>
+      <c r="L51" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="M51" s="6">
+        <v>54728</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A52" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C52" s="2">
+        <v>70436</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H52" s="6">
+        <v>44927</v>
+      </c>
+      <c r="I52" s="2">
+        <v>5</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K52" s="6">
+        <v>42380</v>
+      </c>
+      <c r="L52" s="6">
+        <v>34011</v>
+      </c>
+      <c r="M52" s="6">
+        <v>54483</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="O52" s="6">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A53" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C53" s="2">
+        <v>71558</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H53" s="6">
+        <v>45323</v>
+      </c>
+      <c r="I53" s="2">
+        <v>5</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K53" s="6">
+        <v>42898</v>
+      </c>
+      <c r="L53" s="6">
+        <v>34158</v>
+      </c>
+      <c r="M53" s="6">
+        <v>54758</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="O53" s="6">
+        <v>46494</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A54" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C54" s="2">
+        <v>70933</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H54" s="6">
+        <v>44927</v>
+      </c>
+      <c r="I54" s="2">
+        <v>5</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K54" s="6">
+        <v>42725</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="M54" s="6">
+        <v>55824</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="O54" s="6">
+        <v>46550</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A55" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C55" s="2">
+        <v>70429</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H55" s="6">
+        <v>45058</v>
+      </c>
+      <c r="I55" s="2">
+        <v>5</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K55" s="6">
+        <v>42380</v>
+      </c>
+      <c r="L55" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="M55" s="6">
+        <v>55154</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="O55" s="6">
+        <v>46433</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A56" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C56" s="2">
+        <v>73537</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H56" s="6">
+        <v>45058</v>
+      </c>
+      <c r="I56" s="2">
+        <v>5</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K56" s="6">
+        <v>43419</v>
+      </c>
+      <c r="L56" s="6">
+        <v>35149</v>
+      </c>
+      <c r="M56" s="6">
+        <v>55610</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="O56" s="6">
+        <v>47203</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A57" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C57" s="2">
+        <v>62045</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H57" s="6">
+        <v>45823</v>
+      </c>
+      <c r="I57" s="2">
+        <v>8</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K57" s="6">
+        <v>40917</v>
+      </c>
+      <c r="L57" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="M57" s="6">
+        <v>51867</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="O57" s="6">
+        <v>47203</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A58" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C58" s="2">
+        <v>59958</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H58" s="6">
+        <v>45992</v>
+      </c>
+      <c r="I58" s="2">
+        <v>7</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K58" s="6">
+        <v>40545</v>
+      </c>
+      <c r="L58" s="6">
+        <v>31488</v>
+      </c>
+      <c r="M58" s="6">
+        <v>51957</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A59" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C59" s="2">
+        <v>59961</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H59" s="6">
+        <v>45992</v>
+      </c>
+      <c r="I59" s="2">
+        <v>7</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K59" s="6">
+        <v>40545</v>
+      </c>
+      <c r="L59" s="6">
+        <v>32673</v>
+      </c>
+      <c r="M59" s="6">
+        <v>53144</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="O59" s="6">
+        <v>47370</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A60" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C60" s="2">
+        <v>70015</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H60" s="6">
+        <v>44927</v>
+      </c>
+      <c r="I60" s="2">
+        <v>5</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K60" s="6">
+        <v>42597</v>
+      </c>
+      <c r="L60" s="6">
+        <v>33327</v>
+      </c>
+      <c r="M60" s="6">
+        <v>53783</v>
+      </c>
+      <c r="N60" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="O60" s="6">
+        <v>46208</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A61" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C61" s="2">
+        <v>73249</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H61" s="6">
+        <v>45323</v>
+      </c>
+      <c r="I61" s="2">
+        <v>5</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K61" s="6">
+        <v>43419</v>
+      </c>
+      <c r="L61" s="6">
+        <v>34908</v>
+      </c>
+      <c r="M61" s="6">
+        <v>55366</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="O61" s="6">
+        <v>46663</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A62" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C62" s="2">
+        <v>70935</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H62" s="6">
+        <v>45323</v>
+      </c>
+      <c r="I62" s="2">
+        <v>5</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K62" s="6">
+        <v>42725</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="M62" s="6">
+        <v>55032</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="O62" s="6">
+        <v>46494</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A63" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C63" s="2">
+        <v>73523</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H63" s="6">
+        <v>45058</v>
+      </c>
+      <c r="I63" s="2">
+        <v>5</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K63" s="6">
+        <v>43419</v>
+      </c>
+      <c r="L63" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="M63" s="6">
+        <v>55305</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="O63" s="6">
+        <v>46851</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A64" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C64" s="2">
+        <v>59964</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H64" s="6">
+        <v>45992</v>
+      </c>
+      <c r="I64" s="2">
+        <v>8</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K64" s="6">
+        <v>40545</v>
+      </c>
+      <c r="L64" s="6">
+        <v>32599</v>
+      </c>
+      <c r="M64" s="6">
+        <v>53083</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A65" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C65" s="2">
+        <v>59960</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H65" s="6">
+        <v>45992</v>
+      </c>
+      <c r="I65" s="2">
+        <v>7</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K65" s="6">
+        <v>40545</v>
+      </c>
+      <c r="L65" s="6">
+        <v>32687</v>
+      </c>
+      <c r="M65" s="6">
+        <v>53144</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="O65" s="6">
+        <v>46744</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A66" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C66" s="2">
+        <v>59956</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H66" s="6">
+        <v>45823</v>
+      </c>
+      <c r="I66" s="2">
+        <v>7</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K66" s="6">
+        <v>40545</v>
+      </c>
+      <c r="L66" s="6">
+        <v>32162</v>
+      </c>
+      <c r="M66" s="6">
+        <v>52628</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="O66" s="6">
+        <v>47261</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A67" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C67" s="2">
+        <v>73468</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H67" s="6">
+        <v>45323</v>
+      </c>
+      <c r="I67" s="2">
+        <v>5</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K67" s="6">
+        <v>43419</v>
+      </c>
+      <c r="L67" s="6">
+        <v>35505</v>
+      </c>
+      <c r="M67" s="6">
+        <v>55975</v>
+      </c>
+      <c r="N67" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="O67" s="6">
+        <v>46663</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A68" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C68" s="2">
+        <v>73302</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H68" s="6">
+        <v>45058</v>
+      </c>
+      <c r="I68" s="2">
+        <v>5</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K68" s="6">
+        <v>43419</v>
+      </c>
+      <c r="L68" s="6">
+        <v>34283</v>
+      </c>
+      <c r="M68" s="6">
+        <v>54758</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="O68" s="6">
+        <v>46916</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A69" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C69" s="2">
+        <v>73507</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H69" s="6">
+        <v>45058</v>
+      </c>
+      <c r="I69" s="2">
+        <v>5</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K69" s="6">
+        <v>43419</v>
+      </c>
+      <c r="L69" s="6">
+        <v>35124</v>
+      </c>
+      <c r="M69" s="6">
+        <v>55579</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="O69" s="6">
+        <v>46916</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A70" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C70" s="2">
+        <v>73583</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H70" s="6">
+        <v>45323</v>
+      </c>
+      <c r="I70" s="2">
+        <v>5</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K70" s="6">
+        <v>43419</v>
+      </c>
+      <c r="L70" s="6">
+        <v>34421</v>
+      </c>
+      <c r="M70" s="6">
+        <v>54879</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="O70" s="6">
+        <v>46916</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A71" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C71" s="2">
+        <v>70433</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H71" s="6">
+        <v>45323</v>
+      </c>
+      <c r="I71" s="2">
+        <v>5</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K71" s="6">
+        <v>42380</v>
+      </c>
+      <c r="L71" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="M71" s="6">
+        <v>55397</v>
+      </c>
+      <c r="N71" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="O71" s="6">
+        <v>46494</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A72" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C72" s="2">
+        <v>69527</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H72" s="6">
+        <v>44927</v>
+      </c>
+      <c r="I72" s="2">
+        <v>5</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K72" s="6">
+        <v>42681</v>
+      </c>
+      <c r="L72" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="M72" s="6">
+        <v>55824</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="O72" s="6">
+        <v>46433</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A73" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C73" s="2">
+        <v>56712</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H73" s="9">
+        <v>45823</v>
+      </c>
+      <c r="I73" s="2">
+        <v>8</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K73" s="6">
+        <v>40163</v>
+      </c>
+      <c r="L73" s="6">
+        <v>32608</v>
+      </c>
+      <c r="M73" s="6">
+        <v>53083</v>
+      </c>
+      <c r="N73" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="O73" s="6">
+        <v>47261</v>
+      </c>
+      <c r="Q73" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="R73" s="6">
+        <v>47114</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A74" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C74" s="2">
+        <v>59953</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H74" s="9">
+        <v>44927</v>
+      </c>
+      <c r="I74" s="2">
+        <v>7</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K74" s="6">
+        <v>40545</v>
+      </c>
+      <c r="L74" s="6">
+        <v>31881</v>
+      </c>
+      <c r="M74" s="6">
+        <v>52352</v>
+      </c>
+      <c r="N74" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="O74" s="6">
+        <v>47232</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A75" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C75" s="2">
+        <v>59948</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H75" s="6">
+        <v>45058</v>
+      </c>
+      <c r="I75" s="2">
+        <v>7</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K75" s="6">
+        <v>40545</v>
+      </c>
+      <c r="L75" s="6">
+        <v>31129</v>
+      </c>
+      <c r="M75" s="6">
+        <v>51592</v>
+      </c>
+      <c r="N75" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="O75" s="6">
+        <v>47203</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A76" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C76" s="2">
+        <v>70926</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H76" s="9">
+        <v>44927</v>
+      </c>
+      <c r="I76" s="2">
+        <v>5</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K76" s="6">
+        <v>42725</v>
+      </c>
+      <c r="L76" s="6">
+        <v>33865</v>
+      </c>
+      <c r="M76" s="6">
+        <v>54332</v>
+      </c>
+      <c r="N76" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="O76" s="6">
+        <v>46494</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A77" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C77" s="2">
+        <v>69529</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H77" s="9">
+        <v>45323</v>
+      </c>
+      <c r="I77" s="2">
+        <v>5</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K77" s="6">
+        <v>42681</v>
+      </c>
+      <c r="L77" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="M77" s="6">
+        <v>54424</v>
+      </c>
+      <c r="N77" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="O77" s="6">
+        <v>46208</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A78" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C78" s="2">
+        <v>73490</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H78" s="6">
+        <v>45058</v>
+      </c>
+      <c r="I78" s="2">
+        <v>5</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K78" s="6">
+        <v>43419</v>
+      </c>
+      <c r="L78" s="6">
+        <v>34587</v>
+      </c>
+      <c r="M78" s="6">
+        <v>55062</v>
+      </c>
+      <c r="N78" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="O78" s="6">
+        <v>46916</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A79" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C79" s="2">
+        <v>71535</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H79" s="6">
+        <v>45058</v>
+      </c>
+      <c r="I79" s="2">
+        <v>5</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K79" s="6">
+        <v>42898</v>
+      </c>
+      <c r="L79" s="6">
+        <v>35456</v>
+      </c>
+      <c r="M79" s="6">
+        <v>55916</v>
+      </c>
+      <c r="N79" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="O79" s="6">
+        <v>46595</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A80" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C80" s="2">
+        <v>73314</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H80" s="9">
+        <v>44927</v>
+      </c>
+      <c r="I80" s="2">
+        <v>5</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K80" s="6">
+        <v>43419</v>
+      </c>
+      <c r="L80" s="6">
+        <v>35484</v>
+      </c>
+      <c r="M80" s="6">
+        <v>55944</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="O80" s="6">
+        <v>46953</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A81" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C81" s="2">
+        <v>54038</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="H81" s="9">
+        <v>45672</v>
+      </c>
+      <c r="I81" s="2">
+        <v>8</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K81" s="6">
+        <v>39814</v>
+      </c>
+      <c r="L81" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="M81" s="6">
+        <v>52963</v>
+      </c>
+      <c r="N81" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="O81" s="6">
+        <v>47261</v>
+      </c>
+      <c r="Q81" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="R81" s="6">
+        <v>47097</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A82" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C82" s="2">
+        <v>70435</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="H82" s="9">
+        <v>45672</v>
+      </c>
+      <c r="I82" s="2">
+        <v>7</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K82" s="6">
+        <v>42380</v>
+      </c>
+      <c r="L82" s="6">
+        <v>34009</v>
+      </c>
+      <c r="M82" s="6">
+        <v>54483</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A83" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C83" s="2">
+        <v>59955</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="H83" s="9">
+        <v>45823</v>
+      </c>
+      <c r="I83" s="2">
+        <v>7</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K83" s="6">
+        <v>40545</v>
+      </c>
+      <c r="L83" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="M83" s="6">
+        <v>52902</v>
+      </c>
+      <c r="N83" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="O83" s="6">
+        <v>46937</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A84" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C84" s="2">
+        <v>73389</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="H84" s="9">
+        <v>44927</v>
+      </c>
+      <c r="I84" s="2">
+        <v>5</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K84" s="6">
+        <v>43419</v>
+      </c>
+      <c r="L84" s="6">
+        <v>35491</v>
+      </c>
+      <c r="M84" s="6">
+        <v>55975</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="O84" s="6">
+        <v>46663</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A85" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C85" s="2">
+        <v>70428</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="H85" s="9">
+        <v>45323</v>
+      </c>
+      <c r="I85" s="2">
+        <v>5</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K85" s="6">
+        <v>42380</v>
+      </c>
+      <c r="L85" s="6">
+        <v>35439</v>
+      </c>
+      <c r="M85" s="6">
+        <v>55916</v>
+      </c>
+      <c r="N85" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="O85" s="6">
+        <v>46595</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A86" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C86" s="2">
+        <v>70927</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="H86" s="9">
+        <v>44927</v>
+      </c>
+      <c r="I86" s="2">
+        <v>5</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K86" s="6">
+        <v>42725</v>
+      </c>
+      <c r="L86" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="M86" s="6">
+        <v>55824</v>
+      </c>
+      <c r="N86" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="O86" s="6">
+        <v>46448</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A87" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C87" s="2">
+        <v>71566</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="H87" s="9">
+        <v>45323</v>
+      </c>
+      <c r="I87" s="2">
+        <v>5</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K87" s="6">
+        <v>42898</v>
+      </c>
+      <c r="L87" s="6">
+        <v>35141</v>
+      </c>
+      <c r="M87" s="6">
+        <v>55610</v>
+      </c>
+      <c r="N87" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="O87" s="6">
+        <v>46727</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A88" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C88" s="2">
+        <v>73415</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="H88" s="6">
+        <v>45058</v>
+      </c>
+      <c r="I88" s="2">
+        <v>5</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K88" s="6">
+        <v>43419</v>
+      </c>
+      <c r="L88" s="6">
+        <v>36256</v>
+      </c>
+      <c r="M88" s="6">
+        <v>56735</v>
+      </c>
+      <c r="N88" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="O88" s="6">
+        <v>46951</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A89" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C89" s="2">
+        <v>56806</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H89" s="6">
+        <v>45992</v>
+      </c>
+      <c r="I89" s="2">
+        <v>8</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K89" s="6">
+        <v>40163</v>
+      </c>
+      <c r="L89" s="6">
+        <v>31483</v>
+      </c>
+      <c r="M89" s="6">
+        <v>51957</v>
+      </c>
+      <c r="N89" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="O89" s="6">
+        <v>47203</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A90" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C90" s="2">
+        <v>70931</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H90" s="6">
+        <v>45992</v>
+      </c>
+      <c r="I90" s="2">
+        <v>7</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K90" s="6">
+        <v>42725</v>
+      </c>
+      <c r="L90" s="6">
+        <v>34581</v>
+      </c>
+      <c r="M90" s="6">
+        <v>55062</v>
+      </c>
+      <c r="N90" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="O90" s="6">
+        <v>46494</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="A91" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C91" s="2">
+        <v>67506</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H91" s="9">
+        <v>45823</v>
+      </c>
+      <c r="I91" s="2">
+        <v>7</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K91" s="6">
+        <v>42372</v>
+      </c>
+      <c r="L91" s="6">
+        <v>32607</v>
+      </c>
+      <c r="M91" s="6">
+        <v>53083</v>
+      </c>
+      <c r="N91" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="O91" s="6">
+        <v>46574</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A92" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C92" s="2">
+        <v>70437</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H92" s="9">
+        <v>44927</v>
+      </c>
+      <c r="I92" s="2">
+        <v>5</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K92" s="6">
+        <v>42380</v>
+      </c>
+      <c r="L92" s="6">
+        <v>34584</v>
+      </c>
+      <c r="M92" s="6">
+        <v>55062</v>
+      </c>
+      <c r="N92" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="O92" s="6">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A93" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C93" s="2">
+        <v>73392</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H93" s="9">
+        <v>44927</v>
+      </c>
+      <c r="I93" s="2">
+        <v>5</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K93" s="6">
+        <v>43419</v>
+      </c>
+      <c r="L93" s="6">
+        <v>36064</v>
+      </c>
+      <c r="M93" s="6">
+        <v>56523</v>
+      </c>
+      <c r="N93" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="O93" s="6">
+        <v>47232</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A94" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C94" s="2">
+        <v>73441</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H94" s="6">
+        <v>45058</v>
+      </c>
+      <c r="I94" s="2">
+        <v>5</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K94" s="6">
+        <v>43419</v>
+      </c>
+      <c r="L94" s="6">
+        <v>35232</v>
+      </c>
+      <c r="M94" s="6">
+        <v>55701</v>
+      </c>
+      <c r="N94" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="O94" s="6">
+        <v>46937</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A95" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C95" s="2">
+        <v>69522</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H95" s="9">
+        <v>45323</v>
+      </c>
+      <c r="I95" s="2">
+        <v>5</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K95" s="6">
+        <v>42737</v>
+      </c>
+      <c r="L95" s="6">
+        <v>33653</v>
+      </c>
+      <c r="M95" s="6">
+        <v>54118</v>
+      </c>
+      <c r="N95" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="O95" s="6">
+        <v>46208</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A96" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C96" s="2">
+        <v>73212</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H96" s="6">
+        <v>45058</v>
+      </c>
+      <c r="I96" s="2">
+        <v>5</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K96" s="6">
+        <v>43419</v>
+      </c>
+      <c r="L96" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="M96" s="6">
+        <v>54940</v>
+      </c>
+      <c r="N96" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="O96" s="6">
+        <v>46916</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:T96" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <extLst>
@@ -1653,19 +6003,19 @@
           <x14:formula1>
             <xm:f>LIST_DATA!$A$1:$A$9</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D999</xm:sqref>
+          <xm:sqref>D2:D998</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$B$1:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J999</xm:sqref>
+          <xm:sqref>J2:J998</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$C$1:$C$15</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I999</xm:sqref>
+          <xm:sqref>I2:I998</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/personalia/I SU.xlsx
+++ b/data/personalia/I SU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="191" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4283878A-FAB5-40ED-9A4D-E8E126EEDD46}"/>
+  <xr:revisionPtr revIDLastSave="227" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E27E5DA-1FD0-47D9-999A-6480C6103329}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="307">
   <si>
     <t>Wilayah</t>
   </si>
@@ -463,9 +463,6 @@
     <t>QC STL IB Tbi</t>
   </si>
   <si>
-    <t>29 Agu 1973</t>
-  </si>
-  <si>
     <t>QC STL IC Kis</t>
   </si>
   <si>
@@ -475,9 +472,6 @@
     <t>AM Kegiatan dan Pembiyaan Divre I SU</t>
   </si>
   <si>
-    <t>6 Okt 1989</t>
-  </si>
-  <si>
     <t>AM Perencanaan Teknis Divre I SU</t>
   </si>
   <si>
@@ -499,36 +493,21 @@
     <t>Teknisi Subunit Perbaikan UPT Workshop Sintelis Medan</t>
   </si>
   <si>
-    <t>8 Okt 1993</t>
-  </si>
-  <si>
-    <t>12 Mei 1995</t>
-  </si>
-  <si>
     <t>Kepala UPT Resor Kelas C I.1 Sbt</t>
   </si>
   <si>
     <t>I.1 Sbt</t>
   </si>
   <si>
-    <t>15 Mei 1987</t>
-  </si>
-  <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C I.1 Sbt</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C I.1 Sbt</t>
   </si>
   <si>
-    <t>20 Okt 1989</t>
-  </si>
-  <si>
     <t>PNC Preventif UPT Resor STL I.1 Sbt</t>
   </si>
   <si>
-    <t>19 Agu 1994</t>
-  </si>
-  <si>
     <t>UPT Resor Sintelis Kelas C I.2 Blw</t>
   </si>
   <si>
@@ -544,54 +523,27 @@
     <t>PNC Perbaikan UPT Resor STL I.2 Blw</t>
   </si>
   <si>
-    <t>21 Okt 1992</t>
-  </si>
-  <si>
-    <t>11 Mei 1993</t>
-  </si>
-  <si>
     <t>PNC Preventif UPT Resor STL I.2 Blw</t>
   </si>
   <si>
-    <t>28 Agu 1997</t>
-  </si>
-  <si>
     <t>PLT Kepala UPT Resor Sintelis Kelas B I.3 Mdn</t>
   </si>
   <si>
     <t>I.3 Mdn</t>
   </si>
   <si>
-    <t>5 Okt 1989</t>
-  </si>
-  <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas B I.3 Mdn</t>
   </si>
   <si>
-    <t>1 Agu 1982</t>
-  </si>
-  <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas B I.3 Mdn</t>
   </si>
   <si>
-    <t>30 Agu 1994</t>
-  </si>
-  <si>
     <t>PNC Perbaikan UPT Resor STL I.3 Mdn</t>
   </si>
   <si>
-    <t>24 Agu 1994</t>
-  </si>
-  <si>
     <t>PNC Preventif UPT Resor STL I.3 Mdn</t>
   </si>
   <si>
-    <t>23 Okt 1993</t>
-  </si>
-  <si>
-    <t>16 Agu 2003</t>
-  </si>
-  <si>
     <t>PLT Kepala UPT Resor Kelas B I.4 Lbp</t>
   </si>
   <si>
@@ -604,9 +556,6 @@
     <t>I.4 Lbp</t>
   </si>
   <si>
-    <t>18 Okt 1990</t>
-  </si>
-  <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas B I.4 Lbp</t>
   </si>
   <si>
@@ -616,9 +565,6 @@
     <t>PNC Preventif UPT Resor STL I.4 Lbp</t>
   </si>
   <si>
-    <t>15 Mei 1994</t>
-  </si>
-  <si>
     <t>Kepala UPT Resor Kelas C I.5 Tbi</t>
   </si>
   <si>
@@ -631,30 +577,15 @@
     <t>PNC Perbaikan UPT Resor STL I.5 Tbi</t>
   </si>
   <si>
-    <t>12 Des 1990</t>
-  </si>
-  <si>
-    <t>4 Okt 1993</t>
-  </si>
-  <si>
     <t>PNC Preventif UPT Resor STL I.5 Tbi</t>
   </si>
   <si>
-    <t>5 Okt 1996</t>
-  </si>
-  <si>
-    <t>14 Des 1994</t>
-  </si>
-  <si>
     <t>Kepala UPT Resor Kelas C I.6 Bdt</t>
   </si>
   <si>
     <t>I.6 Bdt</t>
   </si>
   <si>
-    <t>19 Des 1985</t>
-  </si>
-  <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C I.6 Bdt</t>
   </si>
   <si>
@@ -667,12 +598,6 @@
     <t>PNC Preventif UPT Resor STL I.6 Bdt</t>
   </si>
   <si>
-    <t>6 Agu 1994</t>
-  </si>
-  <si>
-    <t>16 Mei 1995</t>
-  </si>
-  <si>
     <t>Kepala UPT Resor I.7 Kelas C Pra</t>
   </si>
   <si>
@@ -691,12 +616,6 @@
     <t>PNC Preventif UPT Resor STL I.7 Pra</t>
   </si>
   <si>
-    <t>1 Agu 1995</t>
-  </si>
-  <si>
-    <t>3 Okt 1996</t>
-  </si>
-  <si>
     <t>Kepala UPT Resor Kelas C I.8 Kis</t>
   </si>
   <si>
@@ -712,9 +631,6 @@
     <t>PNC Perbaikan UPT Resor STL I.8 Kis</t>
   </si>
   <si>
-    <t>8 Des 1992</t>
-  </si>
-  <si>
     <t>PNC Preventif UPT Resor STL I.8 Kis</t>
   </si>
   <si>
@@ -724,27 +640,18 @@
     <t>I.9 Pur</t>
   </si>
   <si>
-    <t>4 Des 1988</t>
-  </si>
-  <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C I.9 Pur</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C I.9 Pur</t>
   </si>
   <si>
-    <t>2 Okt 1988</t>
-  </si>
-  <si>
     <t>PNC Perbaikan UPT Resor STL I.9 Pur</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL I.9 Pur</t>
   </si>
   <si>
-    <t>4 Okt 1996</t>
-  </si>
-  <si>
     <t>Kepala UPT Resor Kelas C I.10 Rap</t>
   </si>
   <si>
@@ -761,9 +668,6 @@
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL I.10 Rap</t>
-  </si>
-  <si>
-    <t>16 Mei 1994</t>
   </si>
   <si>
     <t>PMP.161176.01041</t>
@@ -1561,13 +1465,13 @@
         <v>48549</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="O2" s="6">
         <v>46246</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="R2" s="6">
         <v>46246</v>
@@ -1614,13 +1518,13 @@
         <v>47818</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="O3" s="6">
         <v>45696</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="R3" s="6">
         <v>47370</v>
@@ -1660,20 +1564,20 @@
       <c r="K4" s="6">
         <v>34669</v>
       </c>
-      <c r="L4" s="6" t="s">
-        <v>144</v>
+      <c r="L4" s="6">
+        <v>26903</v>
       </c>
       <c r="M4" s="6">
         <v>47362</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="O4" s="6">
         <v>45696</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>331</v>
+        <v>299</v>
       </c>
       <c r="R4" s="6">
         <v>47265</v>
@@ -1696,7 +1600,7 @@
         <v>38</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>36</v>
@@ -1720,13 +1624,13 @@
         <v>48700</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="O5" s="6">
         <v>46950</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="R5" s="6">
         <v>46950</v>
@@ -1749,7 +1653,7 @@
         <v>35</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>36</v>
@@ -1773,13 +1677,13 @@
         <v>52048</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>249</v>
+        <v>217</v>
       </c>
       <c r="O6" s="6">
         <v>47407</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>332</v>
+        <v>300</v>
       </c>
       <c r="R6" s="6">
         <v>47265</v>
@@ -1802,7 +1706,7 @@
         <v>35</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>36</v>
@@ -1819,8 +1723,8 @@
       <c r="K7" s="6">
         <v>41791</v>
       </c>
-      <c r="L7" s="6" t="s">
-        <v>148</v>
+      <c r="L7" s="6">
+        <v>32787</v>
       </c>
       <c r="M7" s="6">
         <v>53267</v>
@@ -1843,7 +1747,7 @@
         <v>35</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>36</v>
@@ -1884,7 +1788,7 @@
         <v>33</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>36</v>
@@ -1908,7 +1812,7 @@
         <v>54697</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="O9" s="6">
         <v>46494</v>
@@ -1931,10 +1835,10 @@
         <v>138</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H10" s="6">
         <v>45809</v>
@@ -1955,13 +1859,13 @@
         <v>46143</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>251</v>
+        <v>219</v>
       </c>
       <c r="O10" s="6">
         <v>47285</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>333</v>
+        <v>301</v>
       </c>
       <c r="R10" s="6">
         <v>47265</v>
@@ -1984,10 +1888,10 @@
         <v>139</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H11" s="6">
         <v>45823</v>
@@ -2008,7 +1912,7 @@
         <v>53813</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="O11" s="6">
         <v>47261</v>
@@ -2031,10 +1935,10 @@
         <v>139</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H12" s="6">
         <v>45672</v>
@@ -2055,7 +1959,7 @@
         <v>55213</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>253</v>
+        <v>221</v>
       </c>
       <c r="O12" s="6">
         <v>47370</v>
@@ -2078,10 +1982,10 @@
         <v>140</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H13" s="6">
         <v>45823</v>
@@ -2095,14 +1999,14 @@
       <c r="K13" s="6">
         <v>42725</v>
       </c>
-      <c r="L13" s="6" t="s">
-        <v>156</v>
+      <c r="L13" s="6">
+        <v>34250</v>
       </c>
       <c r="M13" s="6">
         <v>54728</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>254</v>
+        <v>222</v>
       </c>
       <c r="O13" s="6">
         <v>46494</v>
@@ -2125,10 +2029,10 @@
         <v>140</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H14" s="6">
         <v>45611</v>
@@ -2142,14 +2046,14 @@
       <c r="K14" s="6">
         <v>44197</v>
       </c>
-      <c r="L14" s="6" t="s">
-        <v>157</v>
+      <c r="L14" s="6">
+        <v>34831</v>
       </c>
       <c r="M14" s="6">
         <v>55305</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>255</v>
+        <v>223</v>
       </c>
       <c r="O14" s="6">
         <v>46727</v>
@@ -2172,10 +2076,10 @@
         <v>39</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H15" s="6">
         <v>45672</v>
@@ -2189,20 +2093,20 @@
       <c r="K15" s="6">
         <v>39814</v>
       </c>
-      <c r="L15" s="6" t="s">
-        <v>160</v>
+      <c r="L15" s="6">
+        <v>31912</v>
       </c>
       <c r="M15" s="6">
         <v>52383</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="O15" s="6">
         <v>46951</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>334</v>
+        <v>302</v>
       </c>
       <c r="R15" s="6">
         <v>47097</v>
@@ -2225,10 +2129,10 @@
         <v>40</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H16" s="6">
         <v>45823</v>
@@ -2249,7 +2153,7 @@
         <v>53752</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="O16" s="6">
         <v>47265</v>
@@ -2272,10 +2176,10 @@
         <v>40</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H17" s="6">
         <v>45823</v>
@@ -2289,14 +2193,14 @@
       <c r="K17" s="6">
         <v>42681</v>
       </c>
-      <c r="L17" s="6" t="s">
-        <v>163</v>
+      <c r="L17" s="6">
+        <v>32801</v>
       </c>
       <c r="M17" s="6">
         <v>53267</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>258</v>
+        <v>226</v>
       </c>
       <c r="O17" s="6">
         <v>46211</v>
@@ -2319,10 +2223,10 @@
         <v>41</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H18" s="6">
         <v>44927</v>
@@ -2336,14 +2240,14 @@
       <c r="K18" s="6">
         <v>43075</v>
       </c>
-      <c r="L18" s="6" t="s">
-        <v>165</v>
+      <c r="L18" s="6">
+        <v>34565</v>
       </c>
       <c r="M18" s="6">
         <v>55032</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>259</v>
+        <v>227</v>
       </c>
       <c r="O18" s="6">
         <v>46663</v>
@@ -2366,10 +2270,10 @@
         <v>39</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="H19" s="6">
         <v>45992</v>
@@ -2390,13 +2294,13 @@
         <v>53297</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>260</v>
+        <v>228</v>
       </c>
       <c r="O19" s="6">
         <v>47285</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>335</v>
+        <v>303</v>
       </c>
       <c r="R19" s="6">
         <v>47175</v>
@@ -2419,10 +2323,10 @@
         <v>40</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="H20" s="6">
         <v>45823</v>
@@ -2443,7 +2347,7 @@
         <v>52444</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>261</v>
+        <v>229</v>
       </c>
       <c r="O20" s="6">
         <v>46973</v>
@@ -2466,10 +2370,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="H21" s="6">
         <v>45672</v>
@@ -2490,7 +2394,7 @@
         <v>54118</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>262</v>
+        <v>230</v>
       </c>
       <c r="O21" s="6">
         <v>47203</v>
@@ -2513,10 +2417,10 @@
         <v>41</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="H22" s="6">
         <v>45323</v>
@@ -2537,7 +2441,7 @@
         <v>54970</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>263</v>
+        <v>231</v>
       </c>
       <c r="O22" s="6">
         <v>46494</v>
@@ -2560,10 +2464,10 @@
         <v>41</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="H23" s="6">
         <v>45323</v>
@@ -2577,14 +2481,14 @@
       <c r="K23" s="6">
         <v>42725</v>
       </c>
-      <c r="L23" s="6" t="s">
-        <v>171</v>
+      <c r="L23" s="6">
+        <v>33898</v>
       </c>
       <c r="M23" s="6">
         <v>54363</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>264</v>
+        <v>232</v>
       </c>
       <c r="O23" s="6">
         <v>46494</v>
@@ -2607,10 +2511,10 @@
         <v>41</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="H24" s="6">
         <v>45323</v>
@@ -2624,14 +2528,14 @@
       <c r="K24" s="6">
         <v>43419</v>
       </c>
-      <c r="L24" s="6" t="s">
-        <v>172</v>
+      <c r="L24" s="6">
+        <v>34100</v>
       </c>
       <c r="M24" s="6">
         <v>54575</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>265</v>
+        <v>233</v>
       </c>
       <c r="O24" s="6">
         <v>46937</v>
@@ -2654,10 +2558,10 @@
         <v>41</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="H25" s="6">
         <v>45058</v>
@@ -2671,14 +2575,14 @@
       <c r="K25" s="6">
         <v>43419</v>
       </c>
-      <c r="L25" s="6" t="s">
-        <v>174</v>
+      <c r="L25" s="6">
+        <v>35670</v>
       </c>
       <c r="M25" s="6">
         <v>56128</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="O25" s="6">
         <v>46851</v>
@@ -2701,10 +2605,10 @@
         <v>39</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="H26" s="6">
         <v>45962</v>
@@ -2718,8 +2622,8 @@
       <c r="K26" s="6">
         <v>39093</v>
       </c>
-      <c r="L26" s="6" t="s">
-        <v>177</v>
+      <c r="L26" s="6">
+        <v>32786</v>
       </c>
       <c r="M26" s="6">
         <v>53267</v>
@@ -2742,10 +2646,10 @@
         <v>40</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="H27" s="6">
         <v>45823</v>
@@ -2759,14 +2663,14 @@
       <c r="K27" s="6">
         <v>40545</v>
       </c>
-      <c r="L27" s="6" t="s">
-        <v>179</v>
+      <c r="L27" s="6">
+        <v>30164</v>
       </c>
       <c r="M27" s="6">
         <v>50649</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="O27" s="6">
         <v>47203</v>
@@ -2790,10 +2694,10 @@
         <v>40</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="H28" s="6">
         <v>45672</v>
@@ -2807,14 +2711,14 @@
       <c r="K28" s="6">
         <v>42681</v>
       </c>
-      <c r="L28" s="6" t="s">
-        <v>181</v>
+      <c r="L28" s="6">
+        <v>34576</v>
       </c>
       <c r="M28" s="6">
         <v>55032</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>268</v>
+        <v>236</v>
       </c>
       <c r="O28" s="6">
         <v>46446</v>
@@ -2837,10 +2741,10 @@
         <v>41</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="H29" s="6">
         <v>44927</v>
@@ -2861,7 +2765,7 @@
         <v>54483</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>269</v>
+        <v>237</v>
       </c>
       <c r="O29" s="6">
         <v>46208</v>
@@ -2884,10 +2788,10 @@
         <v>41</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="H30" s="6">
         <v>45058</v>
@@ -2908,7 +2812,7 @@
         <v>54758</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>270</v>
+        <v>238</v>
       </c>
       <c r="O30" s="6">
         <v>46208</v>
@@ -2931,10 +2835,10 @@
         <v>41</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="H31" s="6">
         <v>45323</v>
@@ -2948,14 +2852,14 @@
       <c r="K31" s="6">
         <v>43419</v>
       </c>
-      <c r="L31" s="6" t="s">
-        <v>183</v>
+      <c r="L31" s="6">
+        <v>34570</v>
       </c>
       <c r="M31" s="6">
         <v>55032</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>271</v>
+        <v>239</v>
       </c>
       <c r="O31" s="6">
         <v>46916</v>
@@ -2978,10 +2882,10 @@
         <v>41</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="H32" s="6">
         <v>45323</v>
@@ -3002,7 +2906,7 @@
         <v>54089</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>272</v>
+        <v>240</v>
       </c>
       <c r="O32" s="6">
         <v>46208</v>
@@ -3025,10 +2929,10 @@
         <v>41</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="H33" s="6">
         <v>45058</v>
@@ -3042,14 +2946,14 @@
       <c r="K33" s="6">
         <v>42725</v>
       </c>
-      <c r="L33" s="6" t="s">
-        <v>185</v>
+      <c r="L33" s="6">
+        <v>34265</v>
       </c>
       <c r="M33" s="6">
         <v>54728</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>273</v>
+        <v>241</v>
       </c>
       <c r="O33" s="6">
         <v>46494</v>
@@ -3072,10 +2976,10 @@
         <v>41</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="H34" s="6">
         <v>45058</v>
@@ -3096,7 +3000,7 @@
         <v>55975</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
       <c r="O34" s="6">
         <v>47370</v>
@@ -3119,10 +3023,10 @@
         <v>41</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="H35" s="6">
         <v>45689</v>
@@ -3136,14 +3040,14 @@
       <c r="K35" s="6">
         <v>45289</v>
       </c>
-      <c r="L35" s="6" t="s">
-        <v>186</v>
+      <c r="L35" s="6">
+        <v>37849</v>
       </c>
       <c r="M35" s="6">
         <v>58319</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>275</v>
+        <v>243</v>
       </c>
       <c r="O35" s="6">
         <v>47324</v>
@@ -3166,10 +3070,10 @@
         <v>39</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="H36" s="6">
         <v>45809</v>
@@ -3190,13 +3094,13 @@
         <v>51957</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>276</v>
+        <v>244</v>
       </c>
       <c r="O36" s="6">
         <v>47261</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>336</v>
+        <v>304</v>
       </c>
       <c r="R36" s="6">
         <v>47265</v>
@@ -3219,10 +3123,10 @@
         <v>40</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="H37" s="6">
         <v>45823</v>
@@ -3236,14 +3140,14 @@
       <c r="K37" s="6">
         <v>42372</v>
       </c>
-      <c r="L37" s="6" t="s">
-        <v>191</v>
+      <c r="L37" s="6">
+        <v>33164</v>
       </c>
       <c r="M37" s="6">
         <v>53632</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>277</v>
+        <v>245</v>
       </c>
       <c r="O37" s="6">
         <v>46744</v>
@@ -3266,10 +3170,10 @@
         <v>40</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="H38" s="6">
         <v>45992</v>
@@ -3290,7 +3194,7 @@
         <v>52628</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>278</v>
+        <v>246</v>
       </c>
       <c r="O38" s="6">
         <v>46937</v>
@@ -3313,10 +3217,10 @@
         <v>41</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="H39" s="6">
         <v>45323</v>
@@ -3354,10 +3258,10 @@
         <v>41</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="H40" s="6">
         <v>44927</v>
@@ -3378,7 +3282,7 @@
         <v>55640</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>279</v>
+        <v>247</v>
       </c>
       <c r="O40" s="6">
         <v>46574</v>
@@ -3401,10 +3305,10 @@
         <v>41</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="H41" s="6">
         <v>45323</v>
@@ -3425,7 +3329,7 @@
         <v>54483</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>280</v>
+        <v>248</v>
       </c>
       <c r="O41" s="6">
         <v>46494</v>
@@ -3448,10 +3352,10 @@
         <v>41</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="H42" s="6">
         <v>44927</v>
@@ -3472,7 +3376,7 @@
         <v>56066</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="O42" s="6">
         <v>46494</v>
@@ -3495,10 +3399,10 @@
         <v>41</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="H43" s="6">
         <v>44927</v>
@@ -3519,7 +3423,7 @@
         <v>55854</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>282</v>
+        <v>250</v>
       </c>
       <c r="O43" s="6">
         <v>46937</v>
@@ -3542,10 +3446,10 @@
         <v>41</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="H44" s="6">
         <v>45823</v>
@@ -3566,7 +3470,7 @@
         <v>53175</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>283</v>
+        <v>251</v>
       </c>
       <c r="O44" s="6">
         <v>46446</v>
@@ -3589,10 +3493,10 @@
         <v>41</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="H45" s="6">
         <v>45058</v>
@@ -3606,14 +3510,14 @@
       <c r="K45" s="6">
         <v>43419</v>
       </c>
-      <c r="L45" s="6" t="s">
-        <v>195</v>
+      <c r="L45" s="6">
+        <v>34469</v>
       </c>
       <c r="M45" s="6">
         <v>54940</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>284</v>
+        <v>252</v>
       </c>
       <c r="O45" s="6">
         <v>46973</v>
@@ -3636,10 +3540,10 @@
         <v>39</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="H46" s="6">
         <v>45823</v>
@@ -3677,10 +3581,10 @@
         <v>40</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="H47" s="6">
         <v>45058</v>
@@ -3701,7 +3605,7 @@
         <v>51592</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>285</v>
+        <v>253</v>
       </c>
       <c r="O47" s="6">
         <v>47285</v>
@@ -3724,10 +3628,10 @@
         <v>40</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="H48" s="6">
         <v>45992</v>
@@ -3765,10 +3669,10 @@
         <v>41</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="H49" s="6">
         <v>45323</v>
@@ -3789,7 +3693,7 @@
         <v>54332</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>286</v>
+        <v>254</v>
       </c>
       <c r="O49" s="6">
         <v>46494</v>
@@ -3812,10 +3716,10 @@
         <v>41</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="H50" s="6">
         <v>45323</v>
@@ -3829,14 +3733,14 @@
       <c r="K50" s="6">
         <v>42597</v>
       </c>
-      <c r="L50" s="6" t="s">
-        <v>200</v>
+      <c r="L50" s="6">
+        <v>33219</v>
       </c>
       <c r="M50" s="6">
         <v>53693</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="O50" s="6">
         <v>46433</v>
@@ -3859,10 +3763,10 @@
         <v>41</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="H51" s="6">
         <v>45323</v>
@@ -3876,8 +3780,8 @@
       <c r="K51" s="6">
         <v>42898</v>
       </c>
-      <c r="L51" s="6" t="s">
-        <v>201</v>
+      <c r="L51" s="6">
+        <v>34246</v>
       </c>
       <c r="M51" s="6">
         <v>54728</v>
@@ -3900,10 +3804,10 @@
         <v>41</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="H52" s="6">
         <v>44927</v>
@@ -3924,7 +3828,7 @@
         <v>54483</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>288</v>
+        <v>256</v>
       </c>
       <c r="O52" s="6">
         <v>46446</v>
@@ -3947,10 +3851,10 @@
         <v>41</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="H53" s="6">
         <v>45323</v>
@@ -3971,7 +3875,7 @@
         <v>54758</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>289</v>
+        <v>257</v>
       </c>
       <c r="O53" s="6">
         <v>46494</v>
@@ -3994,10 +3898,10 @@
         <v>41</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="H54" s="6">
         <v>44927</v>
@@ -4011,14 +3915,14 @@
       <c r="K54" s="6">
         <v>42725</v>
       </c>
-      <c r="L54" s="6" t="s">
-        <v>203</v>
+      <c r="L54" s="6">
+        <v>35343</v>
       </c>
       <c r="M54" s="6">
         <v>55824</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>290</v>
+        <v>258</v>
       </c>
       <c r="O54" s="6">
         <v>46550</v>
@@ -4041,10 +3945,10 @@
         <v>41</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="H55" s="6">
         <v>45058</v>
@@ -4058,14 +3962,14 @@
       <c r="K55" s="6">
         <v>42380</v>
       </c>
-      <c r="L55" s="6" t="s">
-        <v>204</v>
+      <c r="L55" s="6">
+        <v>34682</v>
       </c>
       <c r="M55" s="6">
         <v>55154</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>291</v>
+        <v>259</v>
       </c>
       <c r="O55" s="6">
         <v>46433</v>
@@ -4088,10 +3992,10 @@
         <v>41</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="H56" s="6">
         <v>45058</v>
@@ -4112,7 +4016,7 @@
         <v>55610</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>292</v>
+        <v>260</v>
       </c>
       <c r="O56" s="6">
         <v>47203</v>
@@ -4135,10 +4039,10 @@
         <v>39</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="H57" s="6">
         <v>45823</v>
@@ -4152,14 +4056,14 @@
       <c r="K57" s="6">
         <v>40917</v>
       </c>
-      <c r="L57" s="6" t="s">
-        <v>207</v>
+      <c r="L57" s="6">
+        <v>31400</v>
       </c>
       <c r="M57" s="6">
         <v>51867</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>293</v>
+        <v>261</v>
       </c>
       <c r="O57" s="6">
         <v>47203</v>
@@ -4182,10 +4086,10 @@
         <v>40</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="H58" s="6">
         <v>45992</v>
@@ -4223,10 +4127,10 @@
         <v>40</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="H59" s="6">
         <v>45992</v>
@@ -4247,7 +4151,7 @@
         <v>53144</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>294</v>
+        <v>262</v>
       </c>
       <c r="O59" s="6">
         <v>47370</v>
@@ -4270,10 +4174,10 @@
         <v>41</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="H60" s="6">
         <v>44927</v>
@@ -4294,7 +4198,7 @@
         <v>53783</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>295</v>
+        <v>263</v>
       </c>
       <c r="O60" s="6">
         <v>46208</v>
@@ -4317,10 +4221,10 @@
         <v>41</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="H61" s="6">
         <v>45323</v>
@@ -4341,7 +4245,7 @@
         <v>55366</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>296</v>
+        <v>264</v>
       </c>
       <c r="O61" s="6">
         <v>46663</v>
@@ -4364,10 +4268,10 @@
         <v>41</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="H62" s="6">
         <v>45323</v>
@@ -4381,14 +4285,14 @@
       <c r="K62" s="6">
         <v>42725</v>
       </c>
-      <c r="L62" s="6" t="s">
-        <v>212</v>
+      <c r="L62" s="6">
+        <v>34552</v>
       </c>
       <c r="M62" s="6">
         <v>55032</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>297</v>
+        <v>265</v>
       </c>
       <c r="O62" s="6">
         <v>46494</v>
@@ -4411,10 +4315,10 @@
         <v>41</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="H63" s="6">
         <v>45058</v>
@@ -4428,14 +4332,14 @@
       <c r="K63" s="6">
         <v>43419</v>
       </c>
-      <c r="L63" s="6" t="s">
-        <v>213</v>
+      <c r="L63" s="6">
+        <v>34835</v>
       </c>
       <c r="M63" s="6">
         <v>55305</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>298</v>
+        <v>266</v>
       </c>
       <c r="O63" s="6">
         <v>46851</v>
@@ -4458,10 +4362,10 @@
         <v>39</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="H64" s="6">
         <v>45992</v>
@@ -4499,10 +4403,10 @@
         <v>40</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="H65" s="6">
         <v>45992</v>
@@ -4523,7 +4427,7 @@
         <v>53144</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>299</v>
+        <v>267</v>
       </c>
       <c r="O65" s="6">
         <v>46744</v>
@@ -4546,10 +4450,10 @@
         <v>40</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="H66" s="6">
         <v>45823</v>
@@ -4570,7 +4474,7 @@
         <v>52628</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>300</v>
+        <v>268</v>
       </c>
       <c r="O66" s="6">
         <v>47261</v>
@@ -4593,10 +4497,10 @@
         <v>41</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="H67" s="6">
         <v>45323</v>
@@ -4617,7 +4521,7 @@
         <v>55975</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c r="O67" s="6">
         <v>46663</v>
@@ -4640,10 +4544,10 @@
         <v>41</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="H68" s="6">
         <v>45058</v>
@@ -4664,7 +4568,7 @@
         <v>54758</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>302</v>
+        <v>270</v>
       </c>
       <c r="O68" s="6">
         <v>46916</v>
@@ -4687,10 +4591,10 @@
         <v>41</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="H69" s="6">
         <v>45058</v>
@@ -4711,7 +4615,7 @@
         <v>55579</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>303</v>
+        <v>271</v>
       </c>
       <c r="O69" s="6">
         <v>46916</v>
@@ -4734,10 +4638,10 @@
         <v>41</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="H70" s="6">
         <v>45323</v>
@@ -4758,7 +4662,7 @@
         <v>54879</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="O70" s="6">
         <v>46916</v>
@@ -4781,10 +4685,10 @@
         <v>41</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="H71" s="6">
         <v>45323</v>
@@ -4798,14 +4702,14 @@
       <c r="K71" s="6">
         <v>42380</v>
       </c>
-      <c r="L71" s="6" t="s">
-        <v>220</v>
+      <c r="L71" s="6">
+        <v>34912</v>
       </c>
       <c r="M71" s="6">
         <v>55397</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>305</v>
+        <v>273</v>
       </c>
       <c r="O71" s="6">
         <v>46494</v>
@@ -4828,10 +4732,10 @@
         <v>41</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="H72" s="6">
         <v>44927</v>
@@ -4845,14 +4749,14 @@
       <c r="K72" s="6">
         <v>42681</v>
       </c>
-      <c r="L72" s="6" t="s">
-        <v>221</v>
+      <c r="L72" s="6">
+        <v>35341</v>
       </c>
       <c r="M72" s="6">
         <v>55824</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>306</v>
+        <v>274</v>
       </c>
       <c r="O72" s="6">
         <v>46433</v>
@@ -4875,10 +4779,10 @@
         <v>39</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="H73" s="9">
         <v>45823</v>
@@ -4899,13 +4803,13 @@
         <v>53083</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>307</v>
+        <v>275</v>
       </c>
       <c r="O73" s="6">
         <v>47261</v>
       </c>
       <c r="Q73" s="2" t="s">
-        <v>337</v>
+        <v>305</v>
       </c>
       <c r="R73" s="6">
         <v>47114</v>
@@ -4928,10 +4832,10 @@
         <v>40</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="H74" s="9">
         <v>44927</v>
@@ -4952,7 +4856,7 @@
         <v>52352</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>308</v>
+        <v>276</v>
       </c>
       <c r="O74" s="6">
         <v>47232</v>
@@ -4975,10 +4879,10 @@
         <v>40</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="H75" s="6">
         <v>45058</v>
@@ -4999,7 +4903,7 @@
         <v>51592</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>309</v>
+        <v>277</v>
       </c>
       <c r="O75" s="6">
         <v>47203</v>
@@ -5022,10 +4926,10 @@
         <v>41</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="H76" s="9">
         <v>44927</v>
@@ -5046,7 +4950,7 @@
         <v>54332</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>310</v>
+        <v>278</v>
       </c>
       <c r="O76" s="6">
         <v>46494</v>
@@ -5069,10 +4973,10 @@
         <v>41</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="H77" s="9">
         <v>45323</v>
@@ -5086,14 +4990,14 @@
       <c r="K77" s="6">
         <v>42681</v>
       </c>
-      <c r="L77" s="6" t="s">
-        <v>227</v>
+      <c r="L77" s="6">
+        <v>33946</v>
       </c>
       <c r="M77" s="6">
         <v>54424</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>311</v>
+        <v>279</v>
       </c>
       <c r="O77" s="6">
         <v>46208</v>
@@ -5116,10 +5020,10 @@
         <v>41</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="H78" s="6">
         <v>45058</v>
@@ -5140,7 +5044,7 @@
         <v>55062</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>312</v>
+        <v>280</v>
       </c>
       <c r="O78" s="6">
         <v>46916</v>
@@ -5163,10 +5067,10 @@
         <v>41</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>228</v>
+        <v>200</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="H79" s="6">
         <v>45058</v>
@@ -5187,7 +5091,7 @@
         <v>55916</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="O79" s="6">
         <v>46595</v>
@@ -5210,10 +5114,10 @@
         <v>41</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>228</v>
+        <v>200</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="H80" s="9">
         <v>44927</v>
@@ -5234,7 +5138,7 @@
         <v>55944</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>314</v>
+        <v>282</v>
       </c>
       <c r="O80" s="6">
         <v>46953</v>
@@ -5257,10 +5161,10 @@
         <v>39</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>229</v>
+        <v>201</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="H81" s="9">
         <v>45672</v>
@@ -5274,20 +5178,20 @@
       <c r="K81" s="6">
         <v>39814</v>
       </c>
-      <c r="L81" s="6" t="s">
-        <v>231</v>
+      <c r="L81" s="6">
+        <v>32481</v>
       </c>
       <c r="M81" s="6">
         <v>52963</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>315</v>
+        <v>283</v>
       </c>
       <c r="O81" s="6">
         <v>47261</v>
       </c>
       <c r="Q81" s="2" t="s">
-        <v>338</v>
+        <v>306</v>
       </c>
       <c r="R81" s="6">
         <v>47097</v>
@@ -5310,10 +5214,10 @@
         <v>40</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>232</v>
+        <v>203</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="H82" s="9">
         <v>45672</v>
@@ -5351,10 +5255,10 @@
         <v>40</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>233</v>
+        <v>204</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="H83" s="9">
         <v>45823</v>
@@ -5368,14 +5272,14 @@
       <c r="K83" s="6">
         <v>40545</v>
       </c>
-      <c r="L83" s="6" t="s">
-        <v>234</v>
+      <c r="L83" s="6">
+        <v>32418</v>
       </c>
       <c r="M83" s="6">
         <v>52902</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>316</v>
+        <v>284</v>
       </c>
       <c r="O83" s="6">
         <v>46937</v>
@@ -5398,10 +5302,10 @@
         <v>41</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="H84" s="9">
         <v>44927</v>
@@ -5422,7 +5326,7 @@
         <v>55975</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>317</v>
+        <v>285</v>
       </c>
       <c r="O84" s="6">
         <v>46663</v>
@@ -5445,10 +5349,10 @@
         <v>41</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="H85" s="9">
         <v>45323</v>
@@ -5469,7 +5373,7 @@
         <v>55916</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>318</v>
+        <v>286</v>
       </c>
       <c r="O85" s="6">
         <v>46595</v>
@@ -5492,10 +5396,10 @@
         <v>41</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="H86" s="9">
         <v>44927</v>
@@ -5509,14 +5413,14 @@
       <c r="K86" s="6">
         <v>42725</v>
       </c>
-      <c r="L86" s="6" t="s">
-        <v>237</v>
+      <c r="L86" s="6">
+        <v>35342</v>
       </c>
       <c r="M86" s="6">
         <v>55824</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>319</v>
+        <v>287</v>
       </c>
       <c r="O86" s="6">
         <v>46448</v>
@@ -5539,10 +5443,10 @@
         <v>41</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="H87" s="9">
         <v>45323</v>
@@ -5563,7 +5467,7 @@
         <v>55610</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>320</v>
+        <v>288</v>
       </c>
       <c r="O87" s="6">
         <v>46727</v>
@@ -5586,10 +5490,10 @@
         <v>41</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="H88" s="6">
         <v>45058</v>
@@ -5610,7 +5514,7 @@
         <v>56735</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>321</v>
+        <v>289</v>
       </c>
       <c r="O88" s="6">
         <v>46951</v>
@@ -5633,10 +5537,10 @@
         <v>39</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>238</v>
+        <v>207</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="H89" s="6">
         <v>45992</v>
@@ -5657,7 +5561,7 @@
         <v>51957</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>322</v>
+        <v>290</v>
       </c>
       <c r="O89" s="6">
         <v>47203</v>
@@ -5680,10 +5584,10 @@
         <v>40</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>240</v>
+        <v>209</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="H90" s="6">
         <v>45992</v>
@@ -5704,7 +5608,7 @@
         <v>55062</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>323</v>
+        <v>291</v>
       </c>
       <c r="O90" s="6">
         <v>46494</v>
@@ -5727,10 +5631,10 @@
         <v>40</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>241</v>
+        <v>210</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="H91" s="9">
         <v>45823</v>
@@ -5751,7 +5655,7 @@
         <v>53083</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>324</v>
+        <v>292</v>
       </c>
       <c r="O91" s="6">
         <v>46574</v>
@@ -5774,10 +5678,10 @@
         <v>41</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="H92" s="9">
         <v>44927</v>
@@ -5798,7 +5702,7 @@
         <v>55062</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>325</v>
+        <v>293</v>
       </c>
       <c r="O92" s="6">
         <v>46446</v>
@@ -5821,10 +5725,10 @@
         <v>41</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="H93" s="9">
         <v>44927</v>
@@ -5845,7 +5749,7 @@
         <v>56523</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>326</v>
+        <v>294</v>
       </c>
       <c r="O93" s="6">
         <v>47232</v>
@@ -5868,10 +5772,10 @@
         <v>41</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="H94" s="6">
         <v>45058</v>
@@ -5892,7 +5796,7 @@
         <v>55701</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>327</v>
+        <v>295</v>
       </c>
       <c r="O94" s="6">
         <v>46937</v>
@@ -5915,10 +5819,10 @@
         <v>41</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>243</v>
+        <v>212</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="H95" s="9">
         <v>45323</v>
@@ -5939,7 +5843,7 @@
         <v>54118</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>328</v>
+        <v>296</v>
       </c>
       <c r="O95" s="6">
         <v>46208</v>
@@ -5962,10 +5866,10 @@
         <v>41</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>243</v>
+        <v>212</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="H96" s="6">
         <v>45058</v>
@@ -5979,14 +5883,14 @@
       <c r="K96" s="6">
         <v>43419</v>
       </c>
-      <c r="L96" s="6" t="s">
-        <v>244</v>
+      <c r="L96" s="6">
+        <v>34470</v>
       </c>
       <c r="M96" s="6">
         <v>54940</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>329</v>
+        <v>297</v>
       </c>
       <c r="O96" s="6">
         <v>46916</v>

--- a/data/personalia/I SU.xlsx
+++ b/data/personalia/I SU.xlsx
@@ -5,22 +5,33 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\18. STE APP\Personalia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="227" documentId="8_{2EC12D97-7331-4D7E-89F2-494686D0BEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E27E5DA-1FD0-47D9-999A-6480C6103329}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02957EB-3CA9-43AE-AB14-F3DDA38D6CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template Personalia" sheetId="1" r:id="rId1"/>
-    <sheet name="LIST_DATA" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="LIST_DATA" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$B$1:$L$97</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Template Personalia'!$A$1:$T$96</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -29,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="321">
   <si>
     <t>Wilayah</t>
   </si>
@@ -82,9 +93,6 @@
     <t>Berlaku PMP (YYYY-MM-DD)</t>
   </si>
   <si>
-    <t>Tingkat PMP</t>
-  </si>
-  <si>
     <t>No WA</t>
   </si>
   <si>
@@ -673,12 +681,6 @@
     <t>PMP.161176.01041</t>
   </si>
   <si>
-    <t>PMP. 140874. 00988</t>
-  </si>
-  <si>
-    <t>PMP. 291273. 00981</t>
-  </si>
-  <si>
     <t>PMP.260477.60525</t>
   </si>
   <si>
@@ -950,6 +952,60 @@
   </si>
   <si>
     <t>PMP.041288.67256</t>
+  </si>
+  <si>
+    <t>MULAI
+DINAS</t>
+  </si>
+  <si>
+    <t>TANGGAL
+LAHIR</t>
+  </si>
+  <si>
+    <t>TANGGAL
+BEBAS TUGAS</t>
+  </si>
+  <si>
+    <t>DODI CHAERUL HARDY</t>
+  </si>
+  <si>
+    <t>DAVID PEBRIANTO TAMPUBOLON</t>
+  </si>
+  <si>
+    <t>Klasifikasi PRP</t>
+  </si>
+  <si>
+    <t>Berlaku s/d PRP</t>
+  </si>
+  <si>
+    <t>Klasifikasi PMP</t>
+  </si>
+  <si>
+    <t>Berlaku s/d PMP</t>
+  </si>
+  <si>
+    <t>PENDIDIKAN</t>
+  </si>
+  <si>
+    <t>PMP Lanjutan</t>
+  </si>
+  <si>
+    <t>PMP Pelaksana</t>
+  </si>
+  <si>
+    <t>PRP Lanjutan</t>
+  </si>
+  <si>
+    <t>PRP Pelaksana</t>
+  </si>
+  <si>
+    <t>TMT POSISI</t>
+  </si>
+  <si>
+    <t>PRP.</t>
+  </si>
+  <si>
+    <t>PMP.</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1064,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1031,11 +1087,23 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1339,7 +1407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T96"/>
+  <dimension ref="A1:AB96"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.86328125" style="2" customWidth="1"/>
@@ -1355,11 +1423,13 @@
     <col min="11" max="13" width="13.1328125" style="6" customWidth="1"/>
     <col min="14" max="14" width="22" style="2" customWidth="1"/>
     <col min="15" max="15" width="13.1328125" style="6" customWidth="1"/>
-    <col min="16" max="16" width="22" style="3" customWidth="1"/>
+    <col min="16" max="16" width="15.59765625" style="6" customWidth="1"/>
     <col min="17" max="17" width="22" style="2" customWidth="1"/>
-    <col min="18" max="18" width="13.1328125" style="6" customWidth="1"/>
-    <col min="19" max="20" width="22" style="3" customWidth="1"/>
-    <col min="21" max="16384" width="9.06640625" style="3" hidden="1"/>
+    <col min="18" max="19" width="13.1328125" style="6" customWidth="1"/>
+    <col min="20" max="20" width="22" style="3" customWidth="1"/>
+    <col min="21" max="26" width="0" style="3" hidden="1" customWidth="1"/>
+    <col min="27" max="28" width="0" style="3" hidden="1"/>
+    <col min="29" max="16384" width="9.06640625" style="3" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="5" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
@@ -1370,7 +1440,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1408,7 +1478,7 @@
       <c r="O1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="7" t="s">
         <v>14</v>
       </c>
       <c r="Q1" s="1" t="s">
@@ -1417,34 +1487,34 @@
       <c r="R1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="C2" s="2">
         <v>43432</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H2" s="6">
         <v>46054</v>
@@ -1453,7 +1523,7 @@
         <v>12</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K2" s="6">
         <v>35217</v>
@@ -1464,49 +1534,46 @@
       <c r="M2" s="6">
         <v>48549</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="O2" s="6">
-        <v>46246</v>
-      </c>
       <c r="Q2" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="R2" s="6">
         <v>46246</v>
       </c>
+      <c r="S2" s="6" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C3" s="2">
         <v>42640</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H3" s="6">
-        <v>45945</v>
+        <v>45550</v>
       </c>
       <c r="I3" s="2">
         <v>11</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K3" s="6">
         <v>34669</v>
@@ -1517,40 +1584,37 @@
       <c r="M3" s="6">
         <v>47818</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="O3" s="6">
-        <v>45696</v>
-      </c>
       <c r="Q3" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="R3" s="6">
         <v>47370</v>
       </c>
+      <c r="S3" s="6" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" s="2">
         <v>42633</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H4" s="6">
         <v>45792</v>
@@ -1559,51 +1623,48 @@
         <v>11</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K4" s="6">
         <v>34669</v>
       </c>
       <c r="L4" s="6">
-        <v>26903</v>
+        <v>26905</v>
       </c>
       <c r="M4" s="6">
         <v>47362</v>
       </c>
-      <c r="N4" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="O4" s="6">
-        <v>45696</v>
-      </c>
       <c r="Q4" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="R4" s="6">
         <v>47265</v>
       </c>
+      <c r="S4" s="6" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" s="2">
         <v>46483</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="6">
         <v>45945</v>
@@ -1612,10 +1673,10 @@
         <v>11</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K5" s="6">
-        <v>35433</v>
+        <v>35490</v>
       </c>
       <c r="L5" s="6">
         <v>28241</v>
@@ -1623,40 +1684,37 @@
       <c r="M5" s="6">
         <v>48700</v>
       </c>
-      <c r="N5" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="O5" s="6">
-        <v>46950</v>
-      </c>
       <c r="Q5" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="R5" s="6">
         <v>46950</v>
       </c>
+      <c r="S5" s="6" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C6" s="2">
         <v>51093</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="H6" s="6">
         <v>45627</v>
@@ -1665,51 +1723,57 @@
         <v>9</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K6" s="6">
-        <v>39093</v>
+        <v>39387</v>
       </c>
       <c r="L6" s="6">
-        <v>31568</v>
+        <v>31538</v>
       </c>
       <c r="M6" s="6">
-        <v>52048</v>
+        <v>52018</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="O6" s="6">
-        <v>47407</v>
+        <v>47377</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>316</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="R6" s="6">
         <v>47265</v>
       </c>
+      <c r="S6" s="6" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" s="2">
         <v>64499</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="H7" s="6">
         <v>45809</v>
@@ -1718,39 +1782,48 @@
         <v>9</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K7" s="6">
         <v>41791</v>
       </c>
       <c r="L7" s="6">
-        <v>32787</v>
+        <v>32788</v>
       </c>
       <c r="M7" s="6">
         <v>53267</v>
       </c>
+      <c r="N7" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="O7" s="6">
+        <v>45696</v>
+      </c>
+      <c r="P7" s="6" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C8" s="2">
         <v>56700</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="H8" s="6">
         <v>45915</v>
@@ -1759,7 +1832,7 @@
         <v>9</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K8" s="6">
         <v>40163</v>
@@ -1770,37 +1843,55 @@
       <c r="M8" s="6">
         <v>52291</v>
       </c>
+      <c r="N8" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="O8" s="6">
+        <v>47261</v>
+      </c>
+      <c r="P8" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="R8" s="6">
+        <v>47097</v>
+      </c>
+      <c r="S8" s="6" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C9" s="2">
         <v>70434</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H9" s="6">
-        <v>45231</v>
+        <v>44468</v>
       </c>
       <c r="I9" s="2">
         <v>4</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K9" s="6">
         <v>42675</v>
@@ -1812,45 +1903,48 @@
         <v>54697</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="O9" s="6">
-        <v>46494</v>
+        <v>46446</v>
+      </c>
+      <c r="P9" s="6" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C10" s="2">
         <v>42616</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F10" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>150</v>
-      </c>
       <c r="H10" s="6">
-        <v>45809</v>
+        <v>45597</v>
       </c>
       <c r="I10" s="2">
         <v>9</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K10" s="6">
-        <v>34346</v>
+        <v>34669</v>
       </c>
       <c r="L10" s="6">
         <v>25660</v>
@@ -1859,39 +1953,45 @@
         <v>46143</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="O10" s="6">
-        <v>47285</v>
+        <v>47295</v>
+      </c>
+      <c r="P10" s="6" t="s">
+        <v>316</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="R10" s="6">
         <v>47265</v>
       </c>
+      <c r="S10" s="6" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="11" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" s="2">
         <v>59951</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H11" s="6">
         <v>45823</v>
@@ -1900,45 +2000,48 @@
         <v>8</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K11" s="6">
-        <v>40545</v>
+        <v>40575</v>
       </c>
       <c r="L11" s="6">
-        <v>33331</v>
+        <v>33301</v>
       </c>
       <c r="M11" s="6">
-        <v>53813</v>
+        <v>53783</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O11" s="6">
         <v>47261</v>
       </c>
+      <c r="P11" s="6" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="12" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C12" s="2">
         <v>71547</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H12" s="6">
         <v>45672</v>
@@ -1947,10 +2050,10 @@
         <v>8</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K12" s="6">
-        <v>42898</v>
+        <v>43075</v>
       </c>
       <c r="L12" s="6">
         <v>34743</v>
@@ -1959,33 +2062,36 @@
         <v>55213</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="O12" s="6">
-        <v>47370</v>
+        <v>46446</v>
+      </c>
+      <c r="P12" s="6" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13" s="2">
         <v>70930</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H13" s="6">
         <v>45823</v>
@@ -1994,7 +2100,7 @@
         <v>5</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K13" s="6">
         <v>42725</v>
@@ -2006,33 +2112,36 @@
         <v>54728</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O13" s="6">
-        <v>46494</v>
+        <v>46446</v>
+      </c>
+      <c r="P13" s="6" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C14" s="2">
         <v>73948</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H14" s="6">
         <v>45611</v>
@@ -2041,45 +2150,48 @@
         <v>5</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K14" s="6">
-        <v>44197</v>
+        <v>44198</v>
       </c>
       <c r="L14" s="6">
         <v>34831</v>
       </c>
       <c r="M14" s="6">
-        <v>55305</v>
+        <v>55274</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="O14" s="6">
         <v>46727</v>
       </c>
+      <c r="P14" s="6" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C15" s="2">
         <v>54027</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F15" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="H15" s="6">
         <v>45672</v>
@@ -2088,7 +2200,7 @@
         <v>8</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="K15" s="6">
         <v>39814</v>
@@ -2100,39 +2212,45 @@
         <v>52383</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="O15" s="6">
-        <v>46951</v>
+        <v>46950</v>
+      </c>
+      <c r="P15" s="6" t="s">
+        <v>316</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="R15" s="6">
         <v>47097</v>
       </c>
+      <c r="S15" s="6" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="16" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C16" s="2">
         <v>59950</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H16" s="6">
         <v>45823</v>
@@ -2141,10 +2259,10 @@
         <v>7</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K16" s="6">
-        <v>40545</v>
+        <v>40575</v>
       </c>
       <c r="L16" s="6">
         <v>33285</v>
@@ -2153,33 +2271,36 @@
         <v>53752</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O16" s="6">
         <v>47265</v>
       </c>
-    </row>
-    <row r="17" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P16" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C17" s="2">
         <v>69524</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H17" s="6">
         <v>45823</v>
@@ -2188,10 +2309,10 @@
         <v>7</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K17" s="6">
-        <v>42681</v>
+        <v>42562</v>
       </c>
       <c r="L17" s="6">
         <v>32801</v>
@@ -2200,33 +2321,36 @@
         <v>53267</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O17" s="6">
-        <v>46211</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.45">
+        <v>46209</v>
+      </c>
+      <c r="P17" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C18" s="2">
         <v>71581</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H18" s="6">
         <v>44927</v>
@@ -2235,7 +2359,7 @@
         <v>5</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K18" s="6">
         <v>43075</v>
@@ -2247,86 +2371,95 @@
         <v>55032</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O18" s="6">
         <v>46663</v>
       </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P18" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C19" s="2">
         <v>56762</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F19" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>160</v>
-      </c>
       <c r="H19" s="6">
-        <v>45992</v>
+        <v>45672</v>
       </c>
       <c r="I19" s="2">
         <v>8</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K19" s="6">
         <v>40163</v>
       </c>
       <c r="L19" s="6">
-        <v>32824</v>
+        <v>32853</v>
       </c>
       <c r="M19" s="6">
-        <v>53297</v>
+        <v>53328</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="O19" s="6">
-        <v>47285</v>
+        <v>47295</v>
+      </c>
+      <c r="P19" s="6" t="s">
+        <v>316</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="R19" s="6">
         <v>47175</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S19" s="6" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C20" s="2">
         <v>59962</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H20" s="6">
         <v>45823</v>
@@ -2335,45 +2468,48 @@
         <v>7</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K20" s="6">
-        <v>40545</v>
+        <v>40575</v>
       </c>
       <c r="L20" s="6">
         <v>31982</v>
       </c>
       <c r="M20" s="6">
-        <v>52444</v>
+        <v>15919</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="O20" s="6">
-        <v>46973</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+        <v>46915</v>
+      </c>
+      <c r="P20" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C21" s="2">
         <v>59963</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H21" s="6">
         <v>45672</v>
@@ -2382,10 +2518,10 @@
         <v>7</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K21" s="6">
-        <v>40545</v>
+        <v>40575</v>
       </c>
       <c r="L21" s="6">
         <v>33648</v>
@@ -2394,33 +2530,36 @@
         <v>54118</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O21" s="6">
         <v>47203</v>
       </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P21" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C22" s="2">
         <v>71594</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H22" s="6">
         <v>45323</v>
@@ -2429,45 +2568,48 @@
         <v>5</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K22" s="6">
-        <v>42898</v>
+        <v>43075</v>
       </c>
       <c r="L22" s="6">
-        <v>34514</v>
+        <v>34606</v>
       </c>
       <c r="M22" s="6">
         <v>54970</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="O22" s="6">
-        <v>46494</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.45">
+        <v>46446</v>
+      </c>
+      <c r="P22" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C23" s="2">
         <v>70928</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H23" s="6">
         <v>45323</v>
@@ -2476,7 +2618,7 @@
         <v>5</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K23" s="6">
         <v>42725</v>
@@ -2488,33 +2630,36 @@
         <v>54363</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="O23" s="6">
-        <v>46494</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.45">
+        <v>46446</v>
+      </c>
+      <c r="P23" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C24" s="2">
         <v>73289</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H24" s="6">
         <v>45323</v>
@@ -2523,45 +2668,48 @@
         <v>5</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K24" s="6">
         <v>43419</v>
       </c>
       <c r="L24" s="6">
-        <v>34100</v>
+        <v>34278</v>
       </c>
       <c r="M24" s="6">
-        <v>54575</v>
+        <v>54758</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="O24" s="6">
         <v>46937</v>
       </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P24" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C25" s="2">
         <v>73217</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H25" s="6">
         <v>45058</v>
@@ -2570,7 +2718,7 @@
         <v>5</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K25" s="6">
         <v>43419</v>
@@ -2582,74 +2730,95 @@
         <v>56128</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O25" s="6">
-        <v>46851</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+        <v>46881</v>
+      </c>
+      <c r="P25" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C26" s="2">
         <v>51142</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F26" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>166</v>
-      </c>
       <c r="H26" s="6">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="I26" s="2">
         <v>9</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K26" s="6">
-        <v>39093</v>
+        <v>39387</v>
       </c>
       <c r="L26" s="6">
-        <v>32786</v>
+        <v>32638</v>
       </c>
       <c r="M26" s="6">
-        <v>53267</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+        <v>53114</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="O26" s="6">
+        <v>46916</v>
+      </c>
+      <c r="P26" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="R26" s="6">
+        <v>47265</v>
+      </c>
+      <c r="S26" s="6" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C27" s="2">
         <v>59952</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H27" s="6">
         <v>45823</v>
@@ -2658,46 +2827,48 @@
         <v>8</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K27" s="6">
-        <v>40545</v>
+        <v>40575</v>
       </c>
       <c r="L27" s="6">
-        <v>30164</v>
+        <v>29959</v>
       </c>
       <c r="M27" s="6">
-        <v>50649</v>
+        <v>50437</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="O27" s="6">
         <v>47203</v>
       </c>
-      <c r="P27" s="8"/>
-    </row>
-    <row r="28" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P27" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C28" s="2">
         <v>68900</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H28" s="6">
         <v>45672</v>
@@ -2706,10 +2877,10 @@
         <v>8</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K28" s="6">
-        <v>42681</v>
+        <v>42562</v>
       </c>
       <c r="L28" s="6">
         <v>34576</v>
@@ -2718,33 +2889,36 @@
         <v>55032</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="O28" s="6">
         <v>46446</v>
       </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P28" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C29" s="2">
         <v>70013</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H29" s="6">
         <v>44927</v>
@@ -2753,45 +2927,48 @@
         <v>5</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K29" s="6">
         <v>42597</v>
       </c>
       <c r="L29" s="6">
-        <v>34003</v>
+        <v>34030</v>
       </c>
       <c r="M29" s="6">
-        <v>54483</v>
+        <v>54514</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="O29" s="6">
         <v>46208</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P29" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C30" s="2">
         <v>68896</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H30" s="6">
         <v>45058</v>
@@ -2800,45 +2977,48 @@
         <v>5</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K30" s="6">
-        <v>43046</v>
+        <v>42562</v>
       </c>
       <c r="L30" s="6">
         <v>34173</v>
       </c>
       <c r="M30" s="6">
-        <v>54758</v>
+        <v>54636</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="O30" s="6">
         <v>46208</v>
       </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P30" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C31" s="2">
         <v>73566</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H31" s="6">
         <v>45323</v>
@@ -2847,7 +3027,7 @@
         <v>5</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K31" s="6">
         <v>43419</v>
@@ -2859,33 +3039,36 @@
         <v>55032</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="O31" s="6">
         <v>46916</v>
       </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P31" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C32" s="2">
         <v>70012</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H32" s="6">
         <v>45323</v>
@@ -2894,7 +3077,7 @@
         <v>5</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K32" s="6">
         <v>42597</v>
@@ -2906,33 +3089,36 @@
         <v>54089</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O32" s="6">
         <v>46208</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P32" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C33" s="2">
         <v>70934</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H33" s="6">
         <v>45058</v>
@@ -2941,7 +3127,7 @@
         <v>5</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K33" s="6">
         <v>42725</v>
@@ -2953,33 +3139,36 @@
         <v>54728</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="O33" s="6">
-        <v>46494</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.45">
+        <v>46446</v>
+      </c>
+      <c r="P33" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C34" s="2">
         <v>73516</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H34" s="6">
         <v>45058</v>
@@ -2988,7 +3177,7 @@
         <v>5</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K34" s="6">
         <v>43419</v>
@@ -3000,89 +3189,95 @@
         <v>55975</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="O34" s="6">
-        <v>47370</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.45">
+        <v>45692</v>
+      </c>
+      <c r="P34" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C35" s="2">
         <v>76925</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H35" s="6">
-        <v>45689</v>
+        <v>45444</v>
       </c>
       <c r="I35" s="2">
         <v>5</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K35" s="6">
         <v>45289</v>
       </c>
       <c r="L35" s="6">
-        <v>37849</v>
+        <v>37484</v>
       </c>
       <c r="M35" s="6">
-        <v>58319</v>
+        <v>57954</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="O35" s="6">
         <v>47324</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P35" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C36" s="2">
         <v>54022</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F36" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="G36" s="2" t="s">
-        <v>172</v>
-      </c>
       <c r="H36" s="6">
-        <v>45809</v>
+        <v>45058</v>
       </c>
       <c r="I36" s="2">
         <v>9</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K36" s="6">
         <v>39814</v>
@@ -3094,39 +3289,45 @@
         <v>51957</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="O36" s="6">
         <v>47261</v>
       </c>
+      <c r="P36" s="6" t="s">
+        <v>316</v>
+      </c>
       <c r="Q36" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="R36" s="6">
         <v>47265</v>
       </c>
-    </row>
-    <row r="37" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S36" s="6" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C37" s="2">
         <v>67508</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F37" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="H37" s="6">
         <v>45823</v>
@@ -3135,10 +3336,10 @@
         <v>8</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K37" s="6">
-        <v>42372</v>
+        <v>42430</v>
       </c>
       <c r="L37" s="6">
         <v>33164</v>
@@ -3147,33 +3348,36 @@
         <v>53632</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="O37" s="6">
-        <v>46744</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+        <v>46742</v>
+      </c>
+      <c r="P37" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C38" s="2">
         <v>59965</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H38" s="6">
         <v>45992</v>
@@ -3182,45 +3386,48 @@
         <v>8</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K38" s="6">
-        <v>40545</v>
+        <v>40575</v>
       </c>
       <c r="L38" s="6">
-        <v>32153</v>
+        <v>32448</v>
       </c>
       <c r="M38" s="6">
-        <v>52628</v>
+        <v>52932</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="O38" s="6">
         <v>46937</v>
       </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P38" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C39" s="2">
         <v>71586</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H39" s="6">
         <v>45323</v>
@@ -3229,39 +3436,48 @@
         <v>5</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K39" s="6">
-        <v>42898</v>
+        <v>43075</v>
       </c>
       <c r="L39" s="6">
-        <v>34336</v>
+        <v>34366</v>
       </c>
       <c r="M39" s="6">
-        <v>54820</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.45">
+        <v>54848</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="O39" s="6">
+        <v>46446</v>
+      </c>
+      <c r="P39" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C40" s="2">
         <v>71574</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H40" s="6">
         <v>44927</v>
@@ -3270,45 +3486,48 @@
         <v>5</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K40" s="6">
-        <v>42898</v>
+        <v>43075</v>
       </c>
       <c r="L40" s="6">
-        <v>35167</v>
+        <v>35403</v>
       </c>
       <c r="M40" s="6">
-        <v>55640</v>
+        <v>55885</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="O40" s="6">
-        <v>46574</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.45">
+        <v>46446</v>
+      </c>
+      <c r="P40" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C41" s="2">
         <v>70929</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H41" s="6">
         <v>45323</v>
@@ -3317,7 +3536,7 @@
         <v>5</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K41" s="6">
         <v>42725</v>
@@ -3329,33 +3548,36 @@
         <v>54483</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="O41" s="6">
-        <v>46494</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.45">
+        <v>46446</v>
+      </c>
+      <c r="P41" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C42" s="2">
         <v>70432</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H42" s="6">
         <v>44927</v>
@@ -3364,10 +3586,10 @@
         <v>5</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K42" s="6">
-        <v>42380</v>
+        <v>42675</v>
       </c>
       <c r="L42" s="6">
         <v>35590</v>
@@ -3376,33 +3598,36 @@
         <v>56066</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O42" s="6">
-        <v>46494</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.45">
+        <v>46446</v>
+      </c>
+      <c r="P42" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C43" s="2">
         <v>73390</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H43" s="6">
         <v>44927</v>
@@ -3411,45 +3636,48 @@
         <v>5</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K43" s="6">
         <v>43419</v>
       </c>
       <c r="L43" s="6">
-        <v>35377</v>
+        <v>35288</v>
       </c>
       <c r="M43" s="6">
-        <v>55854</v>
+        <v>55763</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="O43" s="6">
         <v>46937</v>
       </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P43" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C44" s="2">
         <v>70014</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H44" s="6">
         <v>45823</v>
@@ -3458,45 +3686,48 @@
         <v>5</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K44" s="6">
         <v>42597</v>
       </c>
       <c r="L44" s="6">
-        <v>32694</v>
+        <v>32635</v>
       </c>
       <c r="M44" s="6">
-        <v>53175</v>
+        <v>53114</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="O44" s="6">
         <v>46446</v>
       </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P44" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C45" s="2">
         <v>73586</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H45" s="6">
         <v>45058</v>
@@ -3505,7 +3736,7 @@
         <v>5</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K45" s="6">
         <v>43419</v>
@@ -3517,33 +3748,36 @@
         <v>54940</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O45" s="6">
-        <v>46973</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.45">
+        <v>47041</v>
+      </c>
+      <c r="P45" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A46" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C46" s="2">
         <v>57108</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H46" s="6">
         <v>45823</v>
@@ -3552,10 +3786,10 @@
         <v>8</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K46" s="6">
-        <v>40190</v>
+        <v>40513</v>
       </c>
       <c r="L46" s="6">
         <v>32173</v>
@@ -3563,40 +3797,58 @@
       <c r="M46" s="6">
         <v>52628</v>
       </c>
-    </row>
-    <row r="47" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="N46" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="O46" s="6">
+        <v>46953</v>
+      </c>
+      <c r="P46" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q46" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="R46" s="6">
+        <v>47110</v>
+      </c>
+      <c r="S46" s="6" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A47" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C47" s="2">
         <v>59949</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H47" s="6">
-        <v>45058</v>
+        <v>45672</v>
       </c>
       <c r="I47" s="2">
         <v>7</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K47" s="6">
-        <v>40545</v>
+        <v>40575</v>
       </c>
       <c r="L47" s="6">
         <v>31130</v>
@@ -3605,33 +3857,36 @@
         <v>51592</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="O47" s="6">
-        <v>47285</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+        <v>47295</v>
+      </c>
+      <c r="P47" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C48" s="2">
         <v>62095</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H48" s="6">
         <v>45992</v>
@@ -3640,39 +3895,48 @@
         <v>7</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K48" s="6">
-        <v>40917</v>
+        <v>41153</v>
       </c>
       <c r="L48" s="6">
-        <v>31877</v>
+        <v>32054</v>
       </c>
       <c r="M48" s="6">
-        <v>52352</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.45">
+        <v>52536</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="O48" s="6">
+        <v>46117</v>
+      </c>
+      <c r="P48" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A49" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C49" s="2">
         <v>70427</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H49" s="6">
         <v>45323</v>
@@ -3681,10 +3945,10 @@
         <v>5</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K49" s="6">
-        <v>42380</v>
+        <v>42675</v>
       </c>
       <c r="L49" s="6">
         <v>33865</v>
@@ -3693,33 +3957,36 @@
         <v>54332</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="O49" s="6">
-        <v>46494</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.45">
+        <v>46446</v>
+      </c>
+      <c r="P49" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C50" s="2">
         <v>70016</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H50" s="6">
         <v>45323</v>
@@ -3728,7 +3995,7 @@
         <v>5</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K50" s="6">
         <v>42597</v>
@@ -3740,33 +4007,36 @@
         <v>53693</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="O50" s="6">
-        <v>46433</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.45">
+        <v>46446</v>
+      </c>
+      <c r="P50" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A51" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C51" s="2">
         <v>71592</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H51" s="6">
         <v>45323</v>
@@ -3775,39 +4045,48 @@
         <v>5</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K51" s="6">
-        <v>42898</v>
+        <v>43075</v>
       </c>
       <c r="L51" s="6">
-        <v>34246</v>
+        <v>34069</v>
       </c>
       <c r="M51" s="6">
-        <v>54728</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.45">
+        <v>54544</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="O51" s="6">
+        <v>46446</v>
+      </c>
+      <c r="P51" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A52" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C52" s="2">
         <v>70436</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H52" s="6">
         <v>44927</v>
@@ -3816,45 +4095,48 @@
         <v>5</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K52" s="6">
-        <v>42380</v>
+        <v>42675</v>
       </c>
       <c r="L52" s="6">
-        <v>34011</v>
+        <v>34275</v>
       </c>
       <c r="M52" s="6">
-        <v>54483</v>
+        <v>54758</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="O52" s="6">
         <v>46446</v>
       </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P52" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C53" s="2">
         <v>71558</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H53" s="6">
         <v>45323</v>
@@ -3863,45 +4145,48 @@
         <v>5</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K53" s="6">
-        <v>42898</v>
+        <v>43075</v>
       </c>
       <c r="L53" s="6">
-        <v>34158</v>
+        <v>34188</v>
       </c>
       <c r="M53" s="6">
-        <v>54758</v>
+        <v>54667</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="O53" s="6">
-        <v>46494</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.45">
+        <v>46446</v>
+      </c>
+      <c r="P53" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A54" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C54" s="2">
         <v>70933</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H54" s="6">
         <v>44927</v>
@@ -3910,45 +4195,48 @@
         <v>5</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K54" s="6">
         <v>42725</v>
       </c>
       <c r="L54" s="6">
-        <v>35343</v>
+        <v>35195</v>
       </c>
       <c r="M54" s="6">
-        <v>55824</v>
+        <v>55671</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="O54" s="6">
-        <v>46550</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.45">
+        <v>46446</v>
+      </c>
+      <c r="P54" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A55" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C55" s="2">
         <v>70429</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H55" s="6">
         <v>45058</v>
@@ -3957,10 +4245,10 @@
         <v>5</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K55" s="6">
-        <v>42380</v>
+        <v>42675</v>
       </c>
       <c r="L55" s="6">
         <v>34682</v>
@@ -3969,33 +4257,36 @@
         <v>55154</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O55" s="6">
-        <v>46433</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.45">
+        <v>46446</v>
+      </c>
+      <c r="P55" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A56" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C56" s="2">
         <v>73537</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H56" s="6">
         <v>45058</v>
@@ -4004,7 +4295,7 @@
         <v>5</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K56" s="6">
         <v>43419</v>
@@ -4016,33 +4307,36 @@
         <v>55610</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="O56" s="6">
         <v>47203</v>
       </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P56" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A57" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C57" s="2">
         <v>62045</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F57" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="G57" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="H57" s="6">
         <v>45823</v>
@@ -4051,10 +4345,10 @@
         <v>8</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K57" s="6">
-        <v>40917</v>
+        <v>41153</v>
       </c>
       <c r="L57" s="6">
         <v>31400</v>
@@ -4063,33 +4357,36 @@
         <v>51867</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="O57" s="6">
         <v>47203</v>
       </c>
-    </row>
-    <row r="58" spans="1:15" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P57" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A58" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C58" s="2">
         <v>59958</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H58" s="6">
         <v>45992</v>
@@ -4098,10 +4395,10 @@
         <v>7</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K58" s="6">
-        <v>40545</v>
+        <v>40575</v>
       </c>
       <c r="L58" s="6">
         <v>31488</v>
@@ -4109,28 +4406,37 @@
       <c r="M58" s="6">
         <v>51957</v>
       </c>
-    </row>
-    <row r="59" spans="1:15" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="N58" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="O58" s="6">
+        <v>47203</v>
+      </c>
+      <c r="P58" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A59" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C59" s="2">
         <v>59961</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H59" s="6">
         <v>45992</v>
@@ -4139,10 +4445,10 @@
         <v>7</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K59" s="6">
-        <v>40545</v>
+        <v>40575</v>
       </c>
       <c r="L59" s="6">
         <v>32673</v>
@@ -4151,33 +4457,36 @@
         <v>53144</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="O59" s="6">
         <v>47370</v>
       </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P59" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A60" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C60" s="2">
         <v>70015</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H60" s="6">
         <v>44927</v>
@@ -4186,7 +4495,7 @@
         <v>5</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K60" s="6">
         <v>42597</v>
@@ -4198,33 +4507,36 @@
         <v>53783</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="O60" s="6">
         <v>46208</v>
       </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P60" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A61" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C61" s="2">
         <v>73249</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H61" s="6">
         <v>45323</v>
@@ -4233,7 +4545,7 @@
         <v>5</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K61" s="6">
         <v>43419</v>
@@ -4245,33 +4557,36 @@
         <v>55366</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="O61" s="6">
         <v>46663</v>
       </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P61" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A62" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C62" s="2">
         <v>70935</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H62" s="6">
         <v>45323</v>
@@ -4280,54 +4595,57 @@
         <v>5</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K62" s="6">
         <v>42725</v>
       </c>
       <c r="L62" s="6">
-        <v>34552</v>
+        <v>34493</v>
       </c>
       <c r="M62" s="6">
-        <v>55032</v>
+        <v>54970</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="O62" s="6">
-        <v>46494</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.45">
+        <v>46663</v>
+      </c>
+      <c r="P62" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A63" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C63" s="2">
         <v>73523</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H63" s="6">
-        <v>45058</v>
+        <v>43525</v>
       </c>
       <c r="I63" s="2">
         <v>5</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K63" s="6">
         <v>43419</v>
@@ -4339,33 +4657,36 @@
         <v>55305</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="O63" s="6">
-        <v>46851</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.45">
+        <v>46881</v>
+      </c>
+      <c r="P63" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C64" s="2">
         <v>59964</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F64" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="G64" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="H64" s="6">
         <v>45992</v>
@@ -4374,39 +4695,57 @@
         <v>8</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K64" s="6">
-        <v>40545</v>
+        <v>40575</v>
       </c>
       <c r="L64" s="6">
-        <v>32599</v>
+        <v>32522</v>
       </c>
       <c r="M64" s="6">
-        <v>53083</v>
-      </c>
-    </row>
-    <row r="65" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+        <v>52994</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="O64" s="6">
+        <v>47370</v>
+      </c>
+      <c r="P64" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q64" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="R64" s="6">
+        <v>47370</v>
+      </c>
+      <c r="S64" s="6" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A65" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C65" s="2">
         <v>59960</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H65" s="6">
         <v>45992</v>
@@ -4415,10 +4754,10 @@
         <v>7</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K65" s="6">
-        <v>40545</v>
+        <v>40575</v>
       </c>
       <c r="L65" s="6">
         <v>32687</v>
@@ -4427,33 +4766,36 @@
         <v>53144</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="O65" s="6">
-        <v>46744</v>
-      </c>
-    </row>
-    <row r="66" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+        <v>46722</v>
+      </c>
+      <c r="P65" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A66" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C66" s="2">
         <v>59956</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H66" s="6">
         <v>45823</v>
@@ -4462,10 +4804,10 @@
         <v>7</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K66" s="6">
-        <v>40545</v>
+        <v>40575</v>
       </c>
       <c r="L66" s="6">
         <v>32162</v>
@@ -4474,33 +4816,36 @@
         <v>52628</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="O66" s="6">
         <v>47261</v>
       </c>
-    </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P66" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A67" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C67" s="2">
         <v>73468</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H67" s="6">
         <v>45323</v>
@@ -4509,7 +4854,7 @@
         <v>5</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K67" s="6">
         <v>43419</v>
@@ -4521,33 +4866,36 @@
         <v>55975</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="O67" s="6">
         <v>46663</v>
       </c>
-    </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P67" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A68" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C68" s="2">
         <v>73302</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H68" s="6">
         <v>45058</v>
@@ -4556,45 +4904,48 @@
         <v>5</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K68" s="6">
         <v>43419</v>
       </c>
       <c r="L68" s="6">
-        <v>34283</v>
+        <v>34253</v>
       </c>
       <c r="M68" s="6">
-        <v>54758</v>
+        <v>54728</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="O68" s="6">
         <v>46916</v>
       </c>
-    </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P68" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A69" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C69" s="2">
         <v>73507</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H69" s="6">
         <v>45058</v>
@@ -4603,7 +4954,7 @@
         <v>5</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K69" s="6">
         <v>43419</v>
@@ -4615,33 +4966,36 @@
         <v>55579</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="O69" s="6">
         <v>46916</v>
       </c>
-    </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P69" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A70" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C70" s="2">
         <v>73583</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H70" s="6">
         <v>45323</v>
@@ -4650,7 +5004,7 @@
         <v>5</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K70" s="6">
         <v>43419</v>
@@ -4662,33 +5016,36 @@
         <v>54879</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="O70" s="6">
         <v>46916</v>
       </c>
-    </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P70" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A71" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C71" s="2">
         <v>70433</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H71" s="6">
         <v>45323</v>
@@ -4697,45 +5054,48 @@
         <v>5</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K71" s="6">
-        <v>42380</v>
+        <v>42675</v>
       </c>
       <c r="L71" s="6">
-        <v>34912</v>
+        <v>34707</v>
       </c>
       <c r="M71" s="6">
-        <v>55397</v>
+        <v>55185</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="O71" s="6">
-        <v>46494</v>
-      </c>
-    </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.45">
+        <v>46446</v>
+      </c>
+      <c r="P71" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A72" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C72" s="2">
         <v>69527</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H72" s="6">
         <v>44927</v>
@@ -4744,110 +5104,119 @@
         <v>5</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K72" s="6">
-        <v>42681</v>
+        <v>42562</v>
       </c>
       <c r="L72" s="6">
-        <v>35341</v>
+        <v>35134</v>
       </c>
       <c r="M72" s="6">
-        <v>55824</v>
+        <v>55610</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="O72" s="6">
-        <v>46433</v>
-      </c>
-    </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.45">
+        <v>46446</v>
+      </c>
+      <c r="P72" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A73" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C73" s="2">
         <v>56712</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F73" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="G73" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="G73" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="H73" s="9">
+      <c r="H73" s="6">
         <v>45823</v>
       </c>
       <c r="I73" s="2">
         <v>8</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K73" s="6">
         <v>40163</v>
       </c>
       <c r="L73" s="6">
-        <v>32608</v>
+        <v>32785</v>
       </c>
       <c r="M73" s="6">
-        <v>53083</v>
+        <v>53267</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="O73" s="6">
         <v>47261</v>
       </c>
+      <c r="P73" s="6" t="s">
+        <v>316</v>
+      </c>
       <c r="Q73" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="R73" s="6">
         <v>47114</v>
       </c>
-    </row>
-    <row r="74" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S73" s="6" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A74" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C74" s="2">
         <v>59953</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="H74" s="9">
+        <v>195</v>
+      </c>
+      <c r="H74" s="6">
         <v>44927</v>
       </c>
       <c r="I74" s="2">
         <v>7</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K74" s="6">
-        <v>40545</v>
+        <v>40575</v>
       </c>
       <c r="L74" s="6">
         <v>31881</v>
@@ -4856,33 +5225,36 @@
         <v>52352</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="O74" s="6">
         <v>47232</v>
       </c>
-    </row>
-    <row r="75" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P74" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A75" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C75" s="2">
         <v>59948</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H75" s="6">
         <v>45058</v>
@@ -4891,54 +5263,57 @@
         <v>7</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K75" s="6">
-        <v>40545</v>
+        <v>40575</v>
       </c>
       <c r="L75" s="6">
         <v>31129</v>
       </c>
       <c r="M75" s="6">
-        <v>51592</v>
+        <v>51533</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="O75" s="6">
-        <v>47203</v>
-      </c>
-    </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.45">
+        <v>47292</v>
+      </c>
+      <c r="P75" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A76" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C76" s="2">
         <v>70926</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="H76" s="9">
+        <v>195</v>
+      </c>
+      <c r="H76" s="6">
         <v>44927</v>
       </c>
       <c r="I76" s="2">
         <v>5</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K76" s="6">
         <v>42725</v>
@@ -4950,80 +5325,86 @@
         <v>54332</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="O76" s="6">
-        <v>46494</v>
-      </c>
-    </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.45">
+        <v>46446</v>
+      </c>
+      <c r="P76" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A77" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C77" s="2">
         <v>69529</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="H77" s="9">
+        <v>195</v>
+      </c>
+      <c r="H77" s="6">
         <v>45323</v>
       </c>
       <c r="I77" s="2">
         <v>5</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K77" s="6">
-        <v>42681</v>
+        <v>42562</v>
       </c>
       <c r="L77" s="6">
-        <v>33946</v>
+        <v>33828</v>
       </c>
       <c r="M77" s="6">
-        <v>54424</v>
+        <v>54302</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="O77" s="6">
         <v>46208</v>
       </c>
-    </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P77" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A78" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C78" s="2">
         <v>73490</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H78" s="6">
         <v>45058</v>
@@ -5032,45 +5413,48 @@
         <v>5</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K78" s="6">
         <v>43419</v>
       </c>
       <c r="L78" s="6">
-        <v>34587</v>
+        <v>34616</v>
       </c>
       <c r="M78" s="6">
-        <v>55062</v>
+        <v>55093</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="O78" s="6">
         <v>46916</v>
       </c>
-    </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P78" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A79" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C79" s="2">
         <v>71535</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H79" s="6">
         <v>45058</v>
@@ -5079,10 +5463,10 @@
         <v>5</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K79" s="6">
-        <v>42898</v>
+        <v>43075</v>
       </c>
       <c r="L79" s="6">
         <v>35456</v>
@@ -5091,42 +5475,45 @@
         <v>55916</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="O79" s="6">
-        <v>46595</v>
-      </c>
-    </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.45">
+        <v>46446</v>
+      </c>
+      <c r="P79" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A80" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C80" s="2">
         <v>73314</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="H80" s="9">
+        <v>195</v>
+      </c>
+      <c r="H80" s="6">
         <v>44927</v>
       </c>
       <c r="I80" s="2">
         <v>5</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K80" s="6">
         <v>43419</v>
@@ -5138,42 +5525,45 @@
         <v>55944</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="O80" s="6">
         <v>46953</v>
       </c>
-    </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P80" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A81" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C81" s="2">
         <v>54038</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F81" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="G81" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="G81" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H81" s="9">
+      <c r="H81" s="6">
         <v>45672</v>
       </c>
       <c r="I81" s="2">
         <v>8</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K81" s="6">
         <v>39814</v>
@@ -5185,136 +5575,154 @@
         <v>52963</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="O81" s="6">
         <v>47261</v>
       </c>
+      <c r="P81" s="6" t="s">
+        <v>316</v>
+      </c>
       <c r="Q81" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="R81" s="6">
         <v>47097</v>
       </c>
-    </row>
-    <row r="82" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S81" s="6" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A82" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C82" s="2">
         <v>70435</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H82" s="9">
+        <v>201</v>
+      </c>
+      <c r="H82" s="6">
         <v>45672</v>
       </c>
       <c r="I82" s="2">
         <v>7</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K82" s="6">
-        <v>42380</v>
+        <v>42675</v>
       </c>
       <c r="L82" s="6">
-        <v>34009</v>
+        <v>34214</v>
       </c>
       <c r="M82" s="6">
-        <v>54483</v>
-      </c>
-    </row>
-    <row r="83" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+        <v>54697</v>
+      </c>
+      <c r="N82" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="O82" s="6">
+        <v>46446</v>
+      </c>
+      <c r="P82" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A83" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C83" s="2">
         <v>59955</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H83" s="9">
+        <v>201</v>
+      </c>
+      <c r="H83" s="6">
         <v>45823</v>
       </c>
       <c r="I83" s="2">
         <v>7</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K83" s="6">
-        <v>40545</v>
+        <v>40575</v>
       </c>
       <c r="L83" s="6">
-        <v>32418</v>
+        <v>32183</v>
       </c>
       <c r="M83" s="6">
-        <v>52902</v>
+        <v>52657</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="O83" s="6">
         <v>46937</v>
       </c>
-    </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P83" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A84" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C84" s="2">
         <v>73389</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H84" s="9">
+        <v>201</v>
+      </c>
+      <c r="H84" s="6">
         <v>44927</v>
       </c>
       <c r="I84" s="2">
         <v>5</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K84" s="6">
         <v>43419</v>
@@ -5326,89 +5734,95 @@
         <v>55975</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="O84" s="6">
         <v>46663</v>
       </c>
-    </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P84" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A85" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C85" s="2">
         <v>70428</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H85" s="9">
+        <v>201</v>
+      </c>
+      <c r="H85" s="6">
         <v>45323</v>
       </c>
       <c r="I85" s="2">
         <v>5</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K85" s="6">
-        <v>42380</v>
+        <v>42675</v>
       </c>
       <c r="L85" s="6">
-        <v>35439</v>
+        <v>35674</v>
       </c>
       <c r="M85" s="6">
-        <v>55916</v>
+        <v>56158</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="O85" s="6">
-        <v>46595</v>
-      </c>
-    </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.45">
+        <v>46446</v>
+      </c>
+      <c r="P85" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A86" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C86" s="2">
         <v>70927</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H86" s="9">
+        <v>201</v>
+      </c>
+      <c r="H86" s="6">
         <v>44927</v>
       </c>
       <c r="I86" s="2">
         <v>5</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K86" s="6">
         <v>42725</v>
@@ -5420,45 +5834,48 @@
         <v>55824</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="O86" s="6">
-        <v>46448</v>
-      </c>
-    </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.45">
+        <v>46446</v>
+      </c>
+      <c r="P86" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A87" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C87" s="2">
         <v>71566</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H87" s="9">
+        <v>201</v>
+      </c>
+      <c r="H87" s="6">
         <v>45323</v>
       </c>
       <c r="I87" s="2">
         <v>5</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K87" s="6">
-        <v>42898</v>
+        <v>43075</v>
       </c>
       <c r="L87" s="6">
         <v>35141</v>
@@ -5467,33 +5884,36 @@
         <v>55610</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="O87" s="6">
         <v>46727</v>
       </c>
-    </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P87" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A88" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C88" s="2">
         <v>73415</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H88" s="6">
         <v>45058</v>
@@ -5502,7 +5922,7 @@
         <v>5</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K88" s="6">
         <v>43419</v>
@@ -5514,33 +5934,36 @@
         <v>56735</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="O88" s="6">
-        <v>46951</v>
-      </c>
-    </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.45">
+        <v>46950</v>
+      </c>
+      <c r="P88" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A89" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C89" s="2">
         <v>56806</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F89" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="G89" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="H89" s="6">
         <v>45992</v>
@@ -5549,151 +5972,160 @@
         <v>8</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K89" s="6">
         <v>40163</v>
       </c>
       <c r="L89" s="6">
-        <v>31483</v>
+        <v>31749</v>
       </c>
       <c r="M89" s="6">
-        <v>51957</v>
+        <v>52232</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="O89" s="6">
         <v>47203</v>
       </c>
-    </row>
-    <row r="90" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P89" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A90" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C90" s="2">
         <v>70931</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H90" s="6">
-        <v>45992</v>
+        <v>45323</v>
       </c>
       <c r="I90" s="2">
         <v>7</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K90" s="6">
         <v>42725</v>
       </c>
       <c r="L90" s="6">
-        <v>34581</v>
+        <v>34433</v>
       </c>
       <c r="M90" s="6">
-        <v>55062</v>
+        <v>54909</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="O90" s="6">
-        <v>46494</v>
-      </c>
-    </row>
-    <row r="91" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+        <v>46446</v>
+      </c>
+      <c r="P90" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A91" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C91" s="2">
         <v>67506</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="H91" s="9">
+        <v>207</v>
+      </c>
+      <c r="H91" s="6">
         <v>45823</v>
       </c>
       <c r="I91" s="2">
         <v>7</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K91" s="6">
-        <v>42372</v>
+        <v>42430</v>
       </c>
       <c r="L91" s="6">
-        <v>32607</v>
+        <v>32755</v>
       </c>
       <c r="M91" s="6">
-        <v>53083</v>
+        <v>53236</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="O91" s="6">
-        <v>46574</v>
-      </c>
-    </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.45">
+        <v>46446</v>
+      </c>
+      <c r="P91" s="6" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A92" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C92" s="2">
         <v>70437</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="H92" s="9">
+        <v>207</v>
+      </c>
+      <c r="H92" s="6">
         <v>44927</v>
       </c>
       <c r="I92" s="2">
         <v>5</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K92" s="6">
-        <v>42380</v>
+        <v>42675</v>
       </c>
       <c r="L92" s="6">
         <v>34584</v>
@@ -5702,42 +6134,45 @@
         <v>55062</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="O92" s="6">
         <v>46446</v>
       </c>
-    </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P92" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A93" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C93" s="2">
         <v>73392</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="H93" s="9">
+        <v>207</v>
+      </c>
+      <c r="H93" s="6">
         <v>44927</v>
       </c>
       <c r="I93" s="2">
         <v>5</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K93" s="6">
         <v>43419</v>
@@ -5749,33 +6184,36 @@
         <v>56523</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="O93" s="6">
         <v>47232</v>
       </c>
-    </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P93" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A94" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C94" s="2">
         <v>73441</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H94" s="6">
         <v>45058</v>
@@ -5784,7 +6222,7 @@
         <v>5</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K94" s="6">
         <v>43419</v>
@@ -5796,45 +6234,48 @@
         <v>55701</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="O94" s="6">
         <v>46937</v>
       </c>
-    </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P94" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A95" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C95" s="2">
         <v>69522</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="H95" s="9">
+        <v>207</v>
+      </c>
+      <c r="H95" s="6">
         <v>45323</v>
       </c>
       <c r="I95" s="2">
         <v>5</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K95" s="6">
-        <v>42737</v>
+        <v>42562</v>
       </c>
       <c r="L95" s="6">
         <v>33653</v>
@@ -5843,33 +6284,36 @@
         <v>54118</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="O95" s="6">
         <v>46208</v>
       </c>
-    </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P95" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A96" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C96" s="2">
         <v>73212</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H96" s="6">
         <v>45058</v>
@@ -5878,7 +6322,7 @@
         <v>5</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K96" s="6">
         <v>43419</v>
@@ -5890,10 +6334,13 @@
         <v>54940</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="O96" s="6">
         <v>46916</v>
+      </c>
+      <c r="P96" s="6" t="s">
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -5928,6 +6375,3006 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C80BD5E5-FF43-4A8F-8AE4-D8E60832200D}">
+  <dimension ref="B1:L97"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" customWidth="1"/>
+    <col min="2" max="2" width="31.19921875" customWidth="1"/>
+    <col min="3" max="3" width="9.06640625" style="8"/>
+    <col min="4" max="7" width="15.59765625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="12.73046875" style="8" customWidth="1"/>
+    <col min="9" max="9" width="29.796875" style="13" customWidth="1"/>
+    <col min="10" max="10" width="22.86328125" style="8" customWidth="1"/>
+    <col min="11" max="11" width="29.796875" style="13" customWidth="1"/>
+    <col min="12" max="12" width="22.86328125" style="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" s="10" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="B1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C2" s="8">
+        <v>50568</v>
+      </c>
+      <c r="D2" s="9">
+        <v>45792</v>
+      </c>
+      <c r="E2" s="9">
+        <v>39845</v>
+      </c>
+      <c r="F2" s="9">
+        <v>30251</v>
+      </c>
+      <c r="G2" s="9">
+        <v>50710</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="9">
+        <v>47203</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="L2" s="9">
+        <v>47203</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="8">
+        <v>42640</v>
+      </c>
+      <c r="D3" s="9">
+        <v>45550</v>
+      </c>
+      <c r="E3" s="9">
+        <v>34669</v>
+      </c>
+      <c r="F3" s="9">
+        <v>27347</v>
+      </c>
+      <c r="G3" s="9">
+        <v>47818</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="9">
+        <v>47370</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="L3" s="9">
+        <v>47370</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="8">
+        <v>42633</v>
+      </c>
+      <c r="D4" s="9">
+        <v>45792</v>
+      </c>
+      <c r="E4" s="9">
+        <v>34669</v>
+      </c>
+      <c r="F4" s="9">
+        <v>26905</v>
+      </c>
+      <c r="G4" s="9">
+        <v>47362</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" s="9">
+        <v>47265</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="L4" s="9">
+        <v>47265</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="8">
+        <v>46483</v>
+      </c>
+      <c r="D5" s="9">
+        <v>45945</v>
+      </c>
+      <c r="E5" s="9">
+        <v>35490</v>
+      </c>
+      <c r="F5" s="9">
+        <v>28241</v>
+      </c>
+      <c r="G5" s="9">
+        <v>48700</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="9">
+        <v>45580</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="L5" s="9">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="8">
+        <v>51093</v>
+      </c>
+      <c r="D6" s="9">
+        <v>45627</v>
+      </c>
+      <c r="E6" s="9">
+        <v>39387</v>
+      </c>
+      <c r="F6" s="9">
+        <v>31538</v>
+      </c>
+      <c r="G6" s="9">
+        <v>52018</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J6" s="9">
+        <v>47377</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="L6" s="9">
+        <v>47265</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="8">
+        <v>64499</v>
+      </c>
+      <c r="D7" s="9">
+        <v>45809</v>
+      </c>
+      <c r="E7" s="9">
+        <v>41791</v>
+      </c>
+      <c r="F7" s="9">
+        <v>32788</v>
+      </c>
+      <c r="G7" s="9">
+        <v>53267</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J7" s="9">
+        <v>45696</v>
+      </c>
+      <c r="L7" s="9"/>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="8">
+        <v>56700</v>
+      </c>
+      <c r="D8" s="9">
+        <v>45915</v>
+      </c>
+      <c r="E8" s="9">
+        <v>40163</v>
+      </c>
+      <c r="F8" s="9">
+        <v>31831</v>
+      </c>
+      <c r="G8" s="9">
+        <v>52291</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J8" s="11">
+        <v>47261</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="L8" s="9">
+        <v>47097</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="8">
+        <v>70434</v>
+      </c>
+      <c r="D9" s="9">
+        <v>44468</v>
+      </c>
+      <c r="E9" s="9">
+        <v>42675</v>
+      </c>
+      <c r="F9" s="9">
+        <v>34232</v>
+      </c>
+      <c r="G9" s="9">
+        <v>54697</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J9" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L9" s="9"/>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="8">
+        <v>42616</v>
+      </c>
+      <c r="D10" s="9">
+        <v>45597</v>
+      </c>
+      <c r="E10" s="9">
+        <v>34669</v>
+      </c>
+      <c r="F10" s="9">
+        <v>25660</v>
+      </c>
+      <c r="G10" s="9">
+        <v>46143</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J10" s="9">
+        <v>47295</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="L10" s="9">
+        <v>47265</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="8">
+        <v>59951</v>
+      </c>
+      <c r="D11" s="9">
+        <v>45823</v>
+      </c>
+      <c r="E11" s="9">
+        <v>40575</v>
+      </c>
+      <c r="F11" s="9">
+        <v>33301</v>
+      </c>
+      <c r="G11" s="9">
+        <v>53783</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J11" s="9">
+        <v>47261</v>
+      </c>
+      <c r="L11" s="9"/>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="8">
+        <v>71547</v>
+      </c>
+      <c r="D12" s="9">
+        <v>45672</v>
+      </c>
+      <c r="E12" s="9">
+        <v>43075</v>
+      </c>
+      <c r="F12" s="9">
+        <v>34743</v>
+      </c>
+      <c r="G12" s="9">
+        <v>55213</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J12" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L12" s="9"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="8">
+        <v>70930</v>
+      </c>
+      <c r="D13" s="9">
+        <v>45823</v>
+      </c>
+      <c r="E13" s="9">
+        <v>42725</v>
+      </c>
+      <c r="F13" s="9">
+        <v>34250</v>
+      </c>
+      <c r="G13" s="9">
+        <v>54728</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J13" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L13" s="9"/>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="8">
+        <v>73948</v>
+      </c>
+      <c r="D14" s="9">
+        <v>45611</v>
+      </c>
+      <c r="E14" s="9">
+        <v>44198</v>
+      </c>
+      <c r="F14" s="9">
+        <v>34831</v>
+      </c>
+      <c r="G14" s="9">
+        <v>55274</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J14" s="9">
+        <v>46727</v>
+      </c>
+      <c r="L14" s="9"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="8">
+        <v>54027</v>
+      </c>
+      <c r="D15" s="9">
+        <v>45672</v>
+      </c>
+      <c r="E15" s="9">
+        <v>39814</v>
+      </c>
+      <c r="F15" s="9">
+        <v>31912</v>
+      </c>
+      <c r="G15" s="9">
+        <v>52383</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J15" s="9">
+        <v>46950</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="L15" s="9">
+        <v>47097</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="8">
+        <v>69524</v>
+      </c>
+      <c r="D16" s="9">
+        <v>45823</v>
+      </c>
+      <c r="E16" s="9">
+        <v>42562</v>
+      </c>
+      <c r="F16" s="9">
+        <v>32801</v>
+      </c>
+      <c r="G16" s="9">
+        <v>53267</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J16" s="9">
+        <v>46209</v>
+      </c>
+      <c r="L16" s="9"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>308</v>
+      </c>
+      <c r="C17" s="8">
+        <v>59950</v>
+      </c>
+      <c r="D17" s="9">
+        <v>45823</v>
+      </c>
+      <c r="E17" s="9">
+        <v>40575</v>
+      </c>
+      <c r="F17" s="9">
+        <v>33285</v>
+      </c>
+      <c r="G17" s="9">
+        <v>53752</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J17" s="9">
+        <v>47265</v>
+      </c>
+      <c r="L17" s="9"/>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="8">
+        <v>71581</v>
+      </c>
+      <c r="D18" s="9">
+        <v>44927</v>
+      </c>
+      <c r="E18" s="9">
+        <v>43075</v>
+      </c>
+      <c r="F18" s="9">
+        <v>34565</v>
+      </c>
+      <c r="G18" s="9">
+        <v>55032</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J18" s="9">
+        <v>46663</v>
+      </c>
+      <c r="L18" s="9"/>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="8">
+        <v>56762</v>
+      </c>
+      <c r="D19" s="9">
+        <v>45672</v>
+      </c>
+      <c r="E19" s="9">
+        <v>40163</v>
+      </c>
+      <c r="F19" s="9">
+        <v>32853</v>
+      </c>
+      <c r="G19" s="9">
+        <v>53328</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J19" s="9">
+        <v>47295</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="L19" s="9">
+        <v>47175</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="8">
+        <v>59963</v>
+      </c>
+      <c r="D20" s="9">
+        <v>45672</v>
+      </c>
+      <c r="E20" s="9">
+        <v>40575</v>
+      </c>
+      <c r="F20" s="9">
+        <v>33648</v>
+      </c>
+      <c r="G20" s="9">
+        <v>54118</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J20" s="9">
+        <v>47203</v>
+      </c>
+      <c r="L20" s="9"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="8">
+        <v>59962</v>
+      </c>
+      <c r="D21" s="9">
+        <v>45823</v>
+      </c>
+      <c r="E21" s="9">
+        <v>40575</v>
+      </c>
+      <c r="F21" s="9">
+        <v>31982</v>
+      </c>
+      <c r="G21" s="9">
+        <v>15919</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J21" s="9">
+        <v>46915</v>
+      </c>
+      <c r="L21" s="9"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="8">
+        <v>71594</v>
+      </c>
+      <c r="D22" s="9">
+        <v>45323</v>
+      </c>
+      <c r="E22" s="9">
+        <v>43075</v>
+      </c>
+      <c r="F22" s="9">
+        <v>34606</v>
+      </c>
+      <c r="G22" s="9">
+        <v>54970</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J22" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L22" s="9"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="8">
+        <v>73289</v>
+      </c>
+      <c r="D23" s="9">
+        <v>45323</v>
+      </c>
+      <c r="E23" s="9">
+        <v>43419</v>
+      </c>
+      <c r="F23" s="9">
+        <v>34278</v>
+      </c>
+      <c r="G23" s="9">
+        <v>54758</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J23" s="9">
+        <v>46937</v>
+      </c>
+      <c r="L23" s="9"/>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B24" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="8">
+        <v>70928</v>
+      </c>
+      <c r="D24" s="9">
+        <v>45323</v>
+      </c>
+      <c r="E24" s="9">
+        <v>42725</v>
+      </c>
+      <c r="F24" s="9">
+        <v>33898</v>
+      </c>
+      <c r="G24" s="9">
+        <v>54363</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J24" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L24" s="9"/>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B25" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="8">
+        <v>73217</v>
+      </c>
+      <c r="D25" s="9">
+        <v>45058</v>
+      </c>
+      <c r="E25" s="9">
+        <v>43419</v>
+      </c>
+      <c r="F25" s="9">
+        <v>35670</v>
+      </c>
+      <c r="G25" s="9">
+        <v>56128</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J25" s="9">
+        <v>46881</v>
+      </c>
+      <c r="L25" s="9"/>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="8">
+        <v>51142</v>
+      </c>
+      <c r="D26" s="9">
+        <v>45992</v>
+      </c>
+      <c r="E26" s="9">
+        <v>39387</v>
+      </c>
+      <c r="F26" s="9">
+        <v>32638</v>
+      </c>
+      <c r="G26" s="9">
+        <v>53114</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J26" s="9">
+        <v>46916</v>
+      </c>
+      <c r="K26" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="L26" s="9">
+        <v>47265</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B27" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="8">
+        <v>68900</v>
+      </c>
+      <c r="D27" s="9">
+        <v>45672</v>
+      </c>
+      <c r="E27" s="9">
+        <v>42562</v>
+      </c>
+      <c r="F27" s="9">
+        <v>34576</v>
+      </c>
+      <c r="G27" s="9">
+        <v>55032</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J27" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L27" s="9"/>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B28" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="8">
+        <v>59952</v>
+      </c>
+      <c r="D28" s="9">
+        <v>45823</v>
+      </c>
+      <c r="E28" s="9">
+        <v>40575</v>
+      </c>
+      <c r="F28" s="9">
+        <v>29959</v>
+      </c>
+      <c r="G28" s="9">
+        <v>50437</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J28" s="9">
+        <v>47203</v>
+      </c>
+      <c r="L28" s="9"/>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B29" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="8">
+        <v>73566</v>
+      </c>
+      <c r="D29" s="9">
+        <v>45323</v>
+      </c>
+      <c r="E29" s="9">
+        <v>43419</v>
+      </c>
+      <c r="F29" s="9">
+        <v>34570</v>
+      </c>
+      <c r="G29" s="9">
+        <v>55032</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J29" s="9">
+        <v>46916</v>
+      </c>
+      <c r="L29" s="9"/>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B30" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="8">
+        <v>70013</v>
+      </c>
+      <c r="D30" s="9">
+        <v>44927</v>
+      </c>
+      <c r="E30" s="9">
+        <v>42597</v>
+      </c>
+      <c r="F30" s="9">
+        <v>34030</v>
+      </c>
+      <c r="G30" s="9">
+        <v>54514</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J30" s="9">
+        <v>46208</v>
+      </c>
+      <c r="L30" s="9"/>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B31" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="8">
+        <v>70012</v>
+      </c>
+      <c r="D31" s="9">
+        <v>45323</v>
+      </c>
+      <c r="E31" s="9">
+        <v>42597</v>
+      </c>
+      <c r="F31" s="9">
+        <v>33627</v>
+      </c>
+      <c r="G31" s="9">
+        <v>54089</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J31" s="9">
+        <v>46208</v>
+      </c>
+      <c r="L31" s="9"/>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B32" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="8">
+        <v>70934</v>
+      </c>
+      <c r="D32" s="9">
+        <v>45058</v>
+      </c>
+      <c r="E32" s="9">
+        <v>42725</v>
+      </c>
+      <c r="F32" s="9">
+        <v>34265</v>
+      </c>
+      <c r="G32" s="9">
+        <v>54728</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J32" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L32" s="9"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B33" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="8">
+        <v>68896</v>
+      </c>
+      <c r="D33" s="9">
+        <v>45058</v>
+      </c>
+      <c r="E33" s="9">
+        <v>42562</v>
+      </c>
+      <c r="F33" s="9">
+        <v>34173</v>
+      </c>
+      <c r="G33" s="9">
+        <v>54636</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J33" s="9">
+        <v>46208</v>
+      </c>
+      <c r="L33" s="9"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B34" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" s="8">
+        <v>73516</v>
+      </c>
+      <c r="D34" s="9">
+        <v>45058</v>
+      </c>
+      <c r="E34" s="9">
+        <v>43419</v>
+      </c>
+      <c r="F34" s="9">
+        <v>35492</v>
+      </c>
+      <c r="G34" s="9">
+        <v>55975</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J34" s="9">
+        <v>45692</v>
+      </c>
+      <c r="L34" s="9"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B35" t="s">
+        <v>75</v>
+      </c>
+      <c r="C35" s="8">
+        <v>76925</v>
+      </c>
+      <c r="D35" s="9">
+        <v>45444</v>
+      </c>
+      <c r="E35" s="9">
+        <v>45289</v>
+      </c>
+      <c r="F35" s="9">
+        <v>37484</v>
+      </c>
+      <c r="G35" s="9">
+        <v>57954</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I35" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J35" s="9">
+        <v>47324</v>
+      </c>
+      <c r="L35" s="9"/>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B36" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="8">
+        <v>54022</v>
+      </c>
+      <c r="D36" s="9">
+        <v>45058</v>
+      </c>
+      <c r="E36" s="9">
+        <v>39814</v>
+      </c>
+      <c r="F36" s="9">
+        <v>31486</v>
+      </c>
+      <c r="G36" s="9">
+        <v>51957</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I36" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J36" s="9">
+        <v>47261</v>
+      </c>
+      <c r="K36" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="L36" s="9">
+        <v>47265</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B37" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" s="8">
+        <v>67508</v>
+      </c>
+      <c r="D37" s="9">
+        <v>45823</v>
+      </c>
+      <c r="E37" s="9">
+        <v>42430</v>
+      </c>
+      <c r="F37" s="9">
+        <v>33164</v>
+      </c>
+      <c r="G37" s="9">
+        <v>53632</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I37" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J37" s="9">
+        <v>46742</v>
+      </c>
+      <c r="L37" s="9"/>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B38" t="s">
+        <v>78</v>
+      </c>
+      <c r="C38" s="8">
+        <v>59965</v>
+      </c>
+      <c r="D38" s="9">
+        <v>45992</v>
+      </c>
+      <c r="E38" s="9">
+        <v>40575</v>
+      </c>
+      <c r="F38" s="9">
+        <v>32448</v>
+      </c>
+      <c r="G38" s="9">
+        <v>52932</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I38" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J38" s="9">
+        <v>46937</v>
+      </c>
+      <c r="L38" s="9"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B39" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" s="8">
+        <v>70929</v>
+      </c>
+      <c r="D39" s="9">
+        <v>45323</v>
+      </c>
+      <c r="E39" s="9">
+        <v>42725</v>
+      </c>
+      <c r="F39" s="9">
+        <v>34023</v>
+      </c>
+      <c r="G39" s="9">
+        <v>54483</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I39" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J39" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L39" s="9"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B40" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="8">
+        <v>71586</v>
+      </c>
+      <c r="D40" s="9">
+        <v>45323</v>
+      </c>
+      <c r="E40" s="9">
+        <v>43075</v>
+      </c>
+      <c r="F40" s="9">
+        <v>34366</v>
+      </c>
+      <c r="G40" s="9">
+        <v>54848</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I40" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J40" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L40" s="9"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B41" t="s">
+        <v>82</v>
+      </c>
+      <c r="C41" s="8">
+        <v>70432</v>
+      </c>
+      <c r="D41" s="9">
+        <v>44927</v>
+      </c>
+      <c r="E41" s="9">
+        <v>42675</v>
+      </c>
+      <c r="F41" s="9">
+        <v>35590</v>
+      </c>
+      <c r="G41" s="9">
+        <v>56066</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I41" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J41" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L41" s="9"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B42" t="s">
+        <v>80</v>
+      </c>
+      <c r="C42" s="8">
+        <v>71574</v>
+      </c>
+      <c r="D42" s="9">
+        <v>44927</v>
+      </c>
+      <c r="E42" s="9">
+        <v>43075</v>
+      </c>
+      <c r="F42" s="9">
+        <v>35403</v>
+      </c>
+      <c r="G42" s="9">
+        <v>55885</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I42" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J42" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L42" s="9"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B43" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" s="8">
+        <v>70014</v>
+      </c>
+      <c r="D43" s="9">
+        <v>45823</v>
+      </c>
+      <c r="E43" s="9">
+        <v>42597</v>
+      </c>
+      <c r="F43" s="9">
+        <v>32635</v>
+      </c>
+      <c r="G43" s="9">
+        <v>53114</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I43" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J43" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L43" s="9"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B44" t="s">
+        <v>85</v>
+      </c>
+      <c r="C44" s="8">
+        <v>73586</v>
+      </c>
+      <c r="D44" s="9">
+        <v>45058</v>
+      </c>
+      <c r="E44" s="9">
+        <v>43419</v>
+      </c>
+      <c r="F44" s="9">
+        <v>34469</v>
+      </c>
+      <c r="G44" s="9">
+        <v>54940</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I44" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J44" s="9">
+        <v>47041</v>
+      </c>
+      <c r="L44" s="9"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B45" t="s">
+        <v>83</v>
+      </c>
+      <c r="C45" s="8">
+        <v>73390</v>
+      </c>
+      <c r="D45" s="9">
+        <v>44927</v>
+      </c>
+      <c r="E45" s="9">
+        <v>43419</v>
+      </c>
+      <c r="F45" s="9">
+        <v>35288</v>
+      </c>
+      <c r="G45" s="9">
+        <v>55763</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I45" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J45" s="9">
+        <v>46937</v>
+      </c>
+      <c r="L45" s="9"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B46" t="s">
+        <v>86</v>
+      </c>
+      <c r="C46" s="8">
+        <v>57108</v>
+      </c>
+      <c r="D46" s="9">
+        <v>45823</v>
+      </c>
+      <c r="E46" s="9">
+        <v>40513</v>
+      </c>
+      <c r="F46" s="9">
+        <v>32173</v>
+      </c>
+      <c r="G46" s="9">
+        <v>52628</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I46" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J46" s="9">
+        <v>46953</v>
+      </c>
+      <c r="K46" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="L46" s="9">
+        <v>47110</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B47" t="s">
+        <v>87</v>
+      </c>
+      <c r="C47" s="8">
+        <v>59949</v>
+      </c>
+      <c r="D47" s="9">
+        <v>45672</v>
+      </c>
+      <c r="E47" s="9">
+        <v>40575</v>
+      </c>
+      <c r="F47" s="9">
+        <v>31130</v>
+      </c>
+      <c r="G47" s="9">
+        <v>51592</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I47" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J47" s="9">
+        <v>47295</v>
+      </c>
+      <c r="L47" s="9"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B48" t="s">
+        <v>88</v>
+      </c>
+      <c r="C48" s="8">
+        <v>62095</v>
+      </c>
+      <c r="D48" s="9">
+        <v>45992</v>
+      </c>
+      <c r="E48" s="9">
+        <v>41153</v>
+      </c>
+      <c r="F48" s="9">
+        <v>32054</v>
+      </c>
+      <c r="G48" s="9">
+        <v>52536</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I48" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J48" s="9">
+        <v>46117</v>
+      </c>
+      <c r="L48" s="9"/>
+    </row>
+    <row r="49" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B49" t="s">
+        <v>89</v>
+      </c>
+      <c r="C49" s="8">
+        <v>70427</v>
+      </c>
+      <c r="D49" s="9">
+        <v>45323</v>
+      </c>
+      <c r="E49" s="9">
+        <v>42675</v>
+      </c>
+      <c r="F49" s="9">
+        <v>33865</v>
+      </c>
+      <c r="G49" s="9">
+        <v>54332</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I49" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J49" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L49" s="9"/>
+    </row>
+    <row r="50" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B50" t="s">
+        <v>93</v>
+      </c>
+      <c r="C50" s="8">
+        <v>71558</v>
+      </c>
+      <c r="D50" s="9">
+        <v>45323</v>
+      </c>
+      <c r="E50" s="9">
+        <v>43075</v>
+      </c>
+      <c r="F50" s="9">
+        <v>34188</v>
+      </c>
+      <c r="G50" s="9">
+        <v>54667</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I50" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J50" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L50" s="9"/>
+    </row>
+    <row r="51" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B51" t="s">
+        <v>90</v>
+      </c>
+      <c r="C51" s="8">
+        <v>70016</v>
+      </c>
+      <c r="D51" s="9">
+        <v>45323</v>
+      </c>
+      <c r="E51" s="9">
+        <v>42597</v>
+      </c>
+      <c r="F51" s="9">
+        <v>33219</v>
+      </c>
+      <c r="G51" s="9">
+        <v>53693</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I51" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J51" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L51" s="9"/>
+    </row>
+    <row r="52" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B52" t="s">
+        <v>94</v>
+      </c>
+      <c r="C52" s="8">
+        <v>70933</v>
+      </c>
+      <c r="D52" s="9">
+        <v>44927</v>
+      </c>
+      <c r="E52" s="9">
+        <v>42725</v>
+      </c>
+      <c r="F52" s="9">
+        <v>35195</v>
+      </c>
+      <c r="G52" s="9">
+        <v>55671</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I52" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J52" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L52" s="9"/>
+    </row>
+    <row r="53" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B53" t="s">
+        <v>95</v>
+      </c>
+      <c r="C53" s="8">
+        <v>70429</v>
+      </c>
+      <c r="D53" s="9">
+        <v>45058</v>
+      </c>
+      <c r="E53" s="9">
+        <v>42675</v>
+      </c>
+      <c r="F53" s="9">
+        <v>34682</v>
+      </c>
+      <c r="G53" s="9">
+        <v>55154</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I53" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J53" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L53" s="9"/>
+    </row>
+    <row r="54" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B54" t="s">
+        <v>92</v>
+      </c>
+      <c r="C54" s="8">
+        <v>70436</v>
+      </c>
+      <c r="D54" s="9">
+        <v>44927</v>
+      </c>
+      <c r="E54" s="9">
+        <v>42675</v>
+      </c>
+      <c r="F54" s="9">
+        <v>34275</v>
+      </c>
+      <c r="G54" s="9">
+        <v>54758</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I54" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J54" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L54" s="9"/>
+    </row>
+    <row r="55" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B55" t="s">
+        <v>96</v>
+      </c>
+      <c r="C55" s="8">
+        <v>73537</v>
+      </c>
+      <c r="D55" s="9">
+        <v>45058</v>
+      </c>
+      <c r="E55" s="9">
+        <v>43419</v>
+      </c>
+      <c r="F55" s="9">
+        <v>35149</v>
+      </c>
+      <c r="G55" s="9">
+        <v>55610</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I55" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J55" s="9">
+        <v>47203</v>
+      </c>
+      <c r="L55" s="9"/>
+    </row>
+    <row r="56" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B56" t="s">
+        <v>91</v>
+      </c>
+      <c r="C56" s="8">
+        <v>71592</v>
+      </c>
+      <c r="D56" s="9">
+        <v>45323</v>
+      </c>
+      <c r="E56" s="9">
+        <v>43075</v>
+      </c>
+      <c r="F56" s="9">
+        <v>34069</v>
+      </c>
+      <c r="G56" s="9">
+        <v>54544</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I56" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J56" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L56" s="9"/>
+    </row>
+    <row r="57" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B57" t="s">
+        <v>97</v>
+      </c>
+      <c r="C57" s="8">
+        <v>62045</v>
+      </c>
+      <c r="D57" s="9">
+        <v>45823</v>
+      </c>
+      <c r="E57" s="9">
+        <v>41153</v>
+      </c>
+      <c r="F57" s="9">
+        <v>31400</v>
+      </c>
+      <c r="G57" s="9">
+        <v>51867</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I57" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J57" s="9">
+        <v>47203</v>
+      </c>
+      <c r="L57" s="9"/>
+    </row>
+    <row r="58" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B58" t="s">
+        <v>99</v>
+      </c>
+      <c r="C58" s="8">
+        <v>59961</v>
+      </c>
+      <c r="D58" s="9">
+        <v>45992</v>
+      </c>
+      <c r="E58" s="9">
+        <v>40575</v>
+      </c>
+      <c r="F58" s="9">
+        <v>32673</v>
+      </c>
+      <c r="G58" s="9">
+        <v>53144</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I58" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J58" s="9">
+        <v>47370</v>
+      </c>
+      <c r="L58" s="9"/>
+    </row>
+    <row r="59" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B59" t="s">
+        <v>98</v>
+      </c>
+      <c r="C59" s="8">
+        <v>59958</v>
+      </c>
+      <c r="D59" s="9">
+        <v>45992</v>
+      </c>
+      <c r="E59" s="9">
+        <v>40575</v>
+      </c>
+      <c r="F59" s="9">
+        <v>31488</v>
+      </c>
+      <c r="G59" s="9">
+        <v>51957</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I59" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J59" s="9">
+        <v>47203</v>
+      </c>
+      <c r="L59" s="9"/>
+    </row>
+    <row r="60" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B60" t="s">
+        <v>102</v>
+      </c>
+      <c r="C60" s="8">
+        <v>70935</v>
+      </c>
+      <c r="D60" s="9">
+        <v>45323</v>
+      </c>
+      <c r="E60" s="9">
+        <v>42725</v>
+      </c>
+      <c r="F60" s="9">
+        <v>34493</v>
+      </c>
+      <c r="G60" s="9">
+        <v>54970</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I60" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J60" s="9">
+        <v>46663</v>
+      </c>
+      <c r="L60" s="9"/>
+    </row>
+    <row r="61" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B61" t="s">
+        <v>101</v>
+      </c>
+      <c r="C61" s="8">
+        <v>73249</v>
+      </c>
+      <c r="D61" s="9">
+        <v>45323</v>
+      </c>
+      <c r="E61" s="9">
+        <v>43419</v>
+      </c>
+      <c r="F61" s="9">
+        <v>34908</v>
+      </c>
+      <c r="G61" s="9">
+        <v>55366</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I61" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J61" s="9">
+        <v>46663</v>
+      </c>
+      <c r="L61" s="9"/>
+    </row>
+    <row r="62" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B62" t="s">
+        <v>100</v>
+      </c>
+      <c r="C62" s="8">
+        <v>70015</v>
+      </c>
+      <c r="D62" s="9">
+        <v>44927</v>
+      </c>
+      <c r="E62" s="9">
+        <v>42597</v>
+      </c>
+      <c r="F62" s="9">
+        <v>33327</v>
+      </c>
+      <c r="G62" s="9">
+        <v>53783</v>
+      </c>
+      <c r="H62" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I62" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J62" s="9">
+        <v>46208</v>
+      </c>
+      <c r="L62" s="9"/>
+    </row>
+    <row r="63" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B63" t="s">
+        <v>103</v>
+      </c>
+      <c r="C63" s="8">
+        <v>73523</v>
+      </c>
+      <c r="D63" s="9">
+        <v>43525</v>
+      </c>
+      <c r="E63" s="9">
+        <v>43419</v>
+      </c>
+      <c r="F63" s="9">
+        <v>34835</v>
+      </c>
+      <c r="G63" s="9">
+        <v>55305</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I63" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J63" s="9">
+        <v>46881</v>
+      </c>
+      <c r="L63" s="9"/>
+    </row>
+    <row r="64" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B64" t="s">
+        <v>104</v>
+      </c>
+      <c r="C64" s="8">
+        <v>59964</v>
+      </c>
+      <c r="D64" s="9">
+        <v>45992</v>
+      </c>
+      <c r="E64" s="9">
+        <v>40575</v>
+      </c>
+      <c r="F64" s="9">
+        <v>32522</v>
+      </c>
+      <c r="G64" s="9">
+        <v>52994</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I64" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J64" s="9">
+        <v>47370</v>
+      </c>
+      <c r="K64" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="L64" s="9">
+        <v>47370</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B65" t="s">
+        <v>106</v>
+      </c>
+      <c r="C65" s="8">
+        <v>59956</v>
+      </c>
+      <c r="D65" s="9">
+        <v>45823</v>
+      </c>
+      <c r="E65" s="9">
+        <v>40575</v>
+      </c>
+      <c r="F65" s="9">
+        <v>32162</v>
+      </c>
+      <c r="G65" s="9">
+        <v>52628</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I65" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J65" s="9">
+        <v>47261</v>
+      </c>
+      <c r="L65" s="9"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B66" t="s">
+        <v>105</v>
+      </c>
+      <c r="C66" s="8">
+        <v>59960</v>
+      </c>
+      <c r="D66" s="9">
+        <v>45992</v>
+      </c>
+      <c r="E66" s="9">
+        <v>40575</v>
+      </c>
+      <c r="F66" s="9">
+        <v>32687</v>
+      </c>
+      <c r="G66" s="9">
+        <v>53144</v>
+      </c>
+      <c r="H66" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I66" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J66" s="9">
+        <v>46722</v>
+      </c>
+      <c r="L66" s="9"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B67" t="s">
+        <v>110</v>
+      </c>
+      <c r="C67" s="8">
+        <v>73583</v>
+      </c>
+      <c r="D67" s="9">
+        <v>45323</v>
+      </c>
+      <c r="E67" s="9">
+        <v>43419</v>
+      </c>
+      <c r="F67" s="9">
+        <v>34421</v>
+      </c>
+      <c r="G67" s="9">
+        <v>54879</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I67" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J67" s="9">
+        <v>46916</v>
+      </c>
+      <c r="L67" s="9"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B68" t="s">
+        <v>111</v>
+      </c>
+      <c r="C68" s="8">
+        <v>70433</v>
+      </c>
+      <c r="D68" s="9">
+        <v>45323</v>
+      </c>
+      <c r="E68" s="9">
+        <v>42675</v>
+      </c>
+      <c r="F68" s="9">
+        <v>34707</v>
+      </c>
+      <c r="G68" s="9">
+        <v>55185</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I68" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J68" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L68" s="9"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B69" t="s">
+        <v>107</v>
+      </c>
+      <c r="C69" s="8">
+        <v>73468</v>
+      </c>
+      <c r="D69" s="9">
+        <v>45323</v>
+      </c>
+      <c r="E69" s="9">
+        <v>43419</v>
+      </c>
+      <c r="F69" s="9">
+        <v>35505</v>
+      </c>
+      <c r="G69" s="9">
+        <v>55975</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I69" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J69" s="9">
+        <v>46663</v>
+      </c>
+      <c r="L69" s="9"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B70" t="s">
+        <v>112</v>
+      </c>
+      <c r="C70" s="8">
+        <v>69527</v>
+      </c>
+      <c r="D70" s="9">
+        <v>44927</v>
+      </c>
+      <c r="E70" s="9">
+        <v>42562</v>
+      </c>
+      <c r="F70" s="9">
+        <v>35134</v>
+      </c>
+      <c r="G70" s="9">
+        <v>55610</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I70" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J70" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L70" s="9"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B71" t="s">
+        <v>108</v>
+      </c>
+      <c r="C71" s="8">
+        <v>73302</v>
+      </c>
+      <c r="D71" s="9">
+        <v>45058</v>
+      </c>
+      <c r="E71" s="9">
+        <v>43419</v>
+      </c>
+      <c r="F71" s="9">
+        <v>34253</v>
+      </c>
+      <c r="G71" s="9">
+        <v>54728</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I71" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J71" s="9">
+        <v>46916</v>
+      </c>
+      <c r="L71" s="9"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B72" t="s">
+        <v>109</v>
+      </c>
+      <c r="C72" s="8">
+        <v>73507</v>
+      </c>
+      <c r="D72" s="9">
+        <v>45058</v>
+      </c>
+      <c r="E72" s="9">
+        <v>43419</v>
+      </c>
+      <c r="F72" s="9">
+        <v>35124</v>
+      </c>
+      <c r="G72" s="9">
+        <v>55579</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I72" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J72" s="9">
+        <v>46916</v>
+      </c>
+      <c r="L72" s="9"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B73" t="s">
+        <v>113</v>
+      </c>
+      <c r="C73" s="8">
+        <v>56712</v>
+      </c>
+      <c r="D73" s="9">
+        <v>45823</v>
+      </c>
+      <c r="E73" s="9">
+        <v>40163</v>
+      </c>
+      <c r="F73" s="9">
+        <v>32785</v>
+      </c>
+      <c r="G73" s="9">
+        <v>53267</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I73" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J73" s="9">
+        <v>47261</v>
+      </c>
+      <c r="K73" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="L73" s="9">
+        <v>47110</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B74" t="s">
+        <v>115</v>
+      </c>
+      <c r="C74" s="8">
+        <v>59948</v>
+      </c>
+      <c r="D74" s="9">
+        <v>45058</v>
+      </c>
+      <c r="E74" s="9">
+        <v>40575</v>
+      </c>
+      <c r="F74" s="9">
+        <v>31129</v>
+      </c>
+      <c r="G74" s="9">
+        <v>51533</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I74" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J74" s="9">
+        <v>47292</v>
+      </c>
+      <c r="L74" s="9"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B75" t="s">
+        <v>114</v>
+      </c>
+      <c r="C75" s="8">
+        <v>59953</v>
+      </c>
+      <c r="D75" s="9">
+        <v>44927</v>
+      </c>
+      <c r="E75" s="9">
+        <v>40575</v>
+      </c>
+      <c r="F75" s="9">
+        <v>31881</v>
+      </c>
+      <c r="G75" s="9">
+        <v>52352</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I75" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J75" s="9">
+        <v>47232</v>
+      </c>
+      <c r="L75" s="9"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B76" t="s">
+        <v>130</v>
+      </c>
+      <c r="C76" s="8">
+        <v>70931</v>
+      </c>
+      <c r="D76" s="9">
+        <v>45323</v>
+      </c>
+      <c r="E76" s="9">
+        <v>42725</v>
+      </c>
+      <c r="F76" s="9">
+        <v>34433</v>
+      </c>
+      <c r="G76" s="9">
+        <v>54909</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I76" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J76" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L76" s="9"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B77" t="s">
+        <v>117</v>
+      </c>
+      <c r="C77" s="8">
+        <v>69529</v>
+      </c>
+      <c r="D77" s="9">
+        <v>45323</v>
+      </c>
+      <c r="E77" s="9">
+        <v>42562</v>
+      </c>
+      <c r="F77" s="9">
+        <v>33828</v>
+      </c>
+      <c r="G77" s="9">
+        <v>54302</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I77" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J77" s="9">
+        <v>46208</v>
+      </c>
+      <c r="L77" s="9"/>
+    </row>
+    <row r="78" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B78" t="s">
+        <v>119</v>
+      </c>
+      <c r="C78" s="8">
+        <v>71535</v>
+      </c>
+      <c r="D78" s="9">
+        <v>45058</v>
+      </c>
+      <c r="E78" s="9">
+        <v>43075</v>
+      </c>
+      <c r="F78" s="9">
+        <v>35456</v>
+      </c>
+      <c r="G78" s="9">
+        <v>55916</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I78" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J78" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L78" s="9"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B79" t="s">
+        <v>120</v>
+      </c>
+      <c r="C79" s="8">
+        <v>73314</v>
+      </c>
+      <c r="D79" s="9">
+        <v>44927</v>
+      </c>
+      <c r="E79" s="9">
+        <v>43419</v>
+      </c>
+      <c r="F79" s="9">
+        <v>35484</v>
+      </c>
+      <c r="G79" s="9">
+        <v>55944</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I79" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J79" s="9">
+        <v>46953</v>
+      </c>
+      <c r="L79" s="9"/>
+    </row>
+    <row r="80" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B80" t="s">
+        <v>116</v>
+      </c>
+      <c r="C80" s="8">
+        <v>70926</v>
+      </c>
+      <c r="D80" s="9">
+        <v>44927</v>
+      </c>
+      <c r="E80" s="9">
+        <v>42725</v>
+      </c>
+      <c r="F80" s="9">
+        <v>33865</v>
+      </c>
+      <c r="G80" s="9">
+        <v>54332</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I80" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J80" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L80" s="9"/>
+    </row>
+    <row r="81" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B81" t="s">
+        <v>118</v>
+      </c>
+      <c r="C81" s="8">
+        <v>73490</v>
+      </c>
+      <c r="D81" s="9">
+        <v>45058</v>
+      </c>
+      <c r="E81" s="9">
+        <v>43419</v>
+      </c>
+      <c r="F81" s="9">
+        <v>34616</v>
+      </c>
+      <c r="G81" s="9">
+        <v>55093</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I81" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J81" s="9">
+        <v>46916</v>
+      </c>
+      <c r="L81" s="9"/>
+    </row>
+    <row r="82" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B82" t="s">
+        <v>121</v>
+      </c>
+      <c r="C82" s="8">
+        <v>54038</v>
+      </c>
+      <c r="D82" s="9">
+        <v>45672</v>
+      </c>
+      <c r="E82" s="9">
+        <v>39814</v>
+      </c>
+      <c r="F82" s="9">
+        <v>32481</v>
+      </c>
+      <c r="G82" s="9">
+        <v>52963</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I82" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J82" s="9">
+        <v>47261</v>
+      </c>
+      <c r="K82" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="L82" s="9">
+        <v>47097</v>
+      </c>
+    </row>
+    <row r="83" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B83" t="s">
+        <v>123</v>
+      </c>
+      <c r="C83" s="8">
+        <v>59955</v>
+      </c>
+      <c r="D83" s="9">
+        <v>45823</v>
+      </c>
+      <c r="E83" s="9">
+        <v>40575</v>
+      </c>
+      <c r="F83" s="9">
+        <v>32183</v>
+      </c>
+      <c r="G83" s="9">
+        <v>52657</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I83" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J83" s="9">
+        <v>46937</v>
+      </c>
+      <c r="L83" s="9"/>
+    </row>
+    <row r="84" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B84" t="s">
+        <v>122</v>
+      </c>
+      <c r="C84" s="8">
+        <v>70435</v>
+      </c>
+      <c r="D84" s="9">
+        <v>45672</v>
+      </c>
+      <c r="E84" s="9">
+        <v>42675</v>
+      </c>
+      <c r="F84" s="9">
+        <v>34214</v>
+      </c>
+      <c r="G84" s="9">
+        <v>54697</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I84" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J84" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L84" s="9"/>
+    </row>
+    <row r="85" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B85" t="s">
+        <v>125</v>
+      </c>
+      <c r="C85" s="8">
+        <v>70428</v>
+      </c>
+      <c r="D85" s="9">
+        <v>45323</v>
+      </c>
+      <c r="E85" s="9">
+        <v>42675</v>
+      </c>
+      <c r="F85" s="9">
+        <v>35674</v>
+      </c>
+      <c r="G85" s="9">
+        <v>56158</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I85" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J85" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L85" s="9"/>
+    </row>
+    <row r="86" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B86" t="s">
+        <v>127</v>
+      </c>
+      <c r="C86" s="8">
+        <v>71566</v>
+      </c>
+      <c r="D86" s="9">
+        <v>45323</v>
+      </c>
+      <c r="E86" s="9">
+        <v>43075</v>
+      </c>
+      <c r="F86" s="9">
+        <v>35141</v>
+      </c>
+      <c r="G86" s="9">
+        <v>55610</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I86" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J86" s="9">
+        <v>46727</v>
+      </c>
+      <c r="L86" s="9"/>
+    </row>
+    <row r="87" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B87" t="s">
+        <v>126</v>
+      </c>
+      <c r="C87" s="8">
+        <v>70927</v>
+      </c>
+      <c r="D87" s="9">
+        <v>44927</v>
+      </c>
+      <c r="E87" s="9">
+        <v>42725</v>
+      </c>
+      <c r="F87" s="9">
+        <v>35342</v>
+      </c>
+      <c r="G87" s="9">
+        <v>55824</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I87" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J87" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L87" s="9"/>
+    </row>
+    <row r="88" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B88" t="s">
+        <v>124</v>
+      </c>
+      <c r="C88" s="8">
+        <v>73389</v>
+      </c>
+      <c r="D88" s="9">
+        <v>44927</v>
+      </c>
+      <c r="E88" s="9">
+        <v>43419</v>
+      </c>
+      <c r="F88" s="9">
+        <v>35491</v>
+      </c>
+      <c r="G88" s="9">
+        <v>55975</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I88" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J88" s="9">
+        <v>46663</v>
+      </c>
+      <c r="L88" s="9"/>
+    </row>
+    <row r="89" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B89" t="s">
+        <v>128</v>
+      </c>
+      <c r="C89" s="8">
+        <v>73415</v>
+      </c>
+      <c r="D89" s="9">
+        <v>45058</v>
+      </c>
+      <c r="E89" s="9">
+        <v>43419</v>
+      </c>
+      <c r="F89" s="9">
+        <v>36256</v>
+      </c>
+      <c r="G89" s="9">
+        <v>56735</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I89" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J89" s="9">
+        <v>46950</v>
+      </c>
+      <c r="L89" s="9"/>
+    </row>
+    <row r="90" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B90" t="s">
+        <v>129</v>
+      </c>
+      <c r="C90" s="8">
+        <v>56806</v>
+      </c>
+      <c r="D90" s="9">
+        <v>45992</v>
+      </c>
+      <c r="E90" s="9">
+        <v>40163</v>
+      </c>
+      <c r="F90" s="9">
+        <v>31749</v>
+      </c>
+      <c r="G90" s="9">
+        <v>52232</v>
+      </c>
+      <c r="H90" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I90" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J90" s="9">
+        <v>47203</v>
+      </c>
+      <c r="L90" s="9"/>
+    </row>
+    <row r="91" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B91" t="s">
+        <v>131</v>
+      </c>
+      <c r="C91" s="8">
+        <v>67506</v>
+      </c>
+      <c r="D91" s="9">
+        <v>45823</v>
+      </c>
+      <c r="E91" s="9">
+        <v>42430</v>
+      </c>
+      <c r="F91" s="9">
+        <v>32755</v>
+      </c>
+      <c r="G91" s="9">
+        <v>53236</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I91" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="J91" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L91" s="9"/>
+    </row>
+    <row r="92" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B92" t="s">
+        <v>130</v>
+      </c>
+      <c r="C92" s="8">
+        <v>70931</v>
+      </c>
+      <c r="D92" s="9">
+        <v>45992</v>
+      </c>
+      <c r="E92" s="9">
+        <v>42725</v>
+      </c>
+      <c r="F92" s="9">
+        <v>34433</v>
+      </c>
+      <c r="G92" s="9">
+        <v>54909</v>
+      </c>
+      <c r="H92" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I92" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J92" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L92" s="9"/>
+    </row>
+    <row r="93" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B93" t="s">
+        <v>135</v>
+      </c>
+      <c r="C93" s="8">
+        <v>69522</v>
+      </c>
+      <c r="D93" s="9">
+        <v>45323</v>
+      </c>
+      <c r="E93" s="9">
+        <v>42562</v>
+      </c>
+      <c r="F93" s="9">
+        <v>33653</v>
+      </c>
+      <c r="G93" s="9">
+        <v>54118</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I93" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J93" s="9">
+        <v>46208</v>
+      </c>
+      <c r="L93" s="9"/>
+    </row>
+    <row r="94" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B94" t="s">
+        <v>132</v>
+      </c>
+      <c r="C94" s="8">
+        <v>70437</v>
+      </c>
+      <c r="D94" s="9">
+        <v>44927</v>
+      </c>
+      <c r="E94" s="9">
+        <v>42675</v>
+      </c>
+      <c r="F94" s="9">
+        <v>34584</v>
+      </c>
+      <c r="G94" s="9">
+        <v>55062</v>
+      </c>
+      <c r="H94" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I94" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J94" s="9">
+        <v>46446</v>
+      </c>
+      <c r="L94" s="9"/>
+    </row>
+    <row r="95" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B95" t="s">
+        <v>136</v>
+      </c>
+      <c r="C95" s="8">
+        <v>73212</v>
+      </c>
+      <c r="D95" s="9">
+        <v>45058</v>
+      </c>
+      <c r="E95" s="9">
+        <v>43419</v>
+      </c>
+      <c r="F95" s="9">
+        <v>34470</v>
+      </c>
+      <c r="G95" s="9">
+        <v>54940</v>
+      </c>
+      <c r="H95" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I95" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J95" s="9">
+        <v>46916</v>
+      </c>
+      <c r="L95" s="9"/>
+    </row>
+    <row r="96" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B96" t="s">
+        <v>133</v>
+      </c>
+      <c r="C96" s="8">
+        <v>73392</v>
+      </c>
+      <c r="D96" s="9">
+        <v>44927</v>
+      </c>
+      <c r="E96" s="9">
+        <v>43419</v>
+      </c>
+      <c r="F96" s="9">
+        <v>36064</v>
+      </c>
+      <c r="G96" s="9">
+        <v>56523</v>
+      </c>
+      <c r="H96" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I96" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J96" s="9">
+        <v>47232</v>
+      </c>
+      <c r="L96" s="9"/>
+    </row>
+    <row r="97" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B97" t="s">
+        <v>134</v>
+      </c>
+      <c r="C97" s="8">
+        <v>73441</v>
+      </c>
+      <c r="D97" s="9">
+        <v>45058</v>
+      </c>
+      <c r="E97" s="9">
+        <v>43419</v>
+      </c>
+      <c r="F97" s="9">
+        <v>35232</v>
+      </c>
+      <c r="G97" s="9">
+        <v>55701</v>
+      </c>
+      <c r="H97" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I97" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="J97" s="9">
+        <v>46937</v>
+      </c>
+      <c r="L97" s="9"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="B1:L97" xr:uid="{C80BD5E5-FF43-4A8F-8AE4-D8E60832200D}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -5937,10 +9384,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
         <v>19</v>
-      </c>
-      <c r="B1" t="s">
-        <v>20</v>
       </c>
       <c r="C1">
         <v>4</v>
@@ -5948,10 +9395,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
         <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -5959,10 +9406,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
         <v>23</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -5970,10 +9417,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>7</v>
@@ -5981,10 +9428,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
         <v>27</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
       </c>
       <c r="C5">
         <v>8</v>
@@ -5992,10 +9439,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
         <v>29</v>
-      </c>
-      <c r="B6" t="s">
-        <v>30</v>
       </c>
       <c r="C6">
         <v>9</v>
@@ -6003,7 +9450,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>10</v>
@@ -6011,7 +9458,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8">
         <v>11</v>
@@ -6019,7 +9466,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>12</v>
